--- a/documentation/wiring-diagram/Dustie Wiring Chart.export.xlsx
+++ b/documentation/wiring-diagram/Dustie Wiring Chart.export.xlsx
@@ -1210,1641 +1210,1644 @@
     <t>TB2:4→</t>
   </si>
   <si>
+    <t>SPADE</t>
+  </si>
+  <si>
+    <t>→ J35:N</t>
+  </si>
+  <si>
+    <t>TB2:14→</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>→ TB3:1</t>
+  </si>
+  <si>
+    <t>K1:T1→</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>→ TB3:11</t>
+  </si>
+  <si>
+    <t>K1:T2→</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>→ PS5:L</t>
+  </si>
+  <si>
+    <t>TB3:10→</t>
+  </si>
+  <si>
+    <t>→ PS5:N</t>
+  </si>
+  <si>
+    <t>TB3:20→</t>
+  </si>
+  <si>
+    <t>→ PS6:L</t>
+  </si>
+  <si>
+    <t>TB3:8→</t>
+  </si>
+  <si>
+    <t>→ PS6:N</t>
+  </si>
+  <si>
+    <t>TB3:18→</t>
+  </si>
+  <si>
+    <t>→ PS4:L</t>
+  </si>
+  <si>
+    <t>TB3:6→</t>
+  </si>
+  <si>
+    <t>→ PS4:N</t>
+  </si>
+  <si>
+    <t>TB3:16→</t>
+  </si>
+  <si>
+    <t>→ J6:4</t>
+  </si>
+  <si>
+    <t>TB3:4→</t>
+  </si>
+  <si>
+    <t>→ J6:3</t>
+  </si>
+  <si>
+    <t>TB3:14→</t>
+  </si>
+  <si>
+    <t>→ VFD1:R</t>
+  </si>
+  <si>
+    <t>P6:4→</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>→ VFD1:S</t>
+  </si>
+  <si>
+    <t>P6:3→</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>→ J36:L</t>
+  </si>
+  <si>
+    <t>P35:L→</t>
+  </si>
+  <si>
+    <t>→ J36:N</t>
+  </si>
+  <si>
+    <t>P35:N→</t>
+  </si>
+  <si>
+    <t>→ TB5:1</t>
+  </si>
+  <si>
+    <t>PS1:V+→</t>
+  </si>
+  <si>
+    <t>Estop/Power Mgmt</t>
+  </si>
+  <si>
+    <t>24V_LOGIC</t>
+  </si>
+  <si>
+    <t>V+</t>
+  </si>
+  <si>
+    <t>🟦 Blue</t>
+  </si>
+  <si>
+    <t>→ TB5:9</t>
+  </si>
+  <si>
+    <t>PS1:V-→</t>
+  </si>
+  <si>
+    <t>0V_LOGIC</t>
+  </si>
+  <si>
+    <t>V-</t>
+  </si>
+  <si>
+    <t>🟦⬜️ Blue/White</t>
+  </si>
+  <si>
+    <t>→ S1:21</t>
+  </si>
+  <si>
+    <t>TB5:8→</t>
+  </si>
+  <si>
+    <t>→ S1:13</t>
+  </si>
+  <si>
+    <t>TB5:6→</t>
+  </si>
+  <si>
+    <t>→ J7:7</t>
+  </si>
+  <si>
+    <t>TB5:4→</t>
+  </si>
+  <si>
+    <t>→ J7:3</t>
+  </si>
+  <si>
+    <t>TB5:2→</t>
+  </si>
+  <si>
+    <t>→ PL1:X1</t>
+  </si>
+  <si>
+    <t>TB5:18→</t>
+  </si>
+  <si>
+    <t>ESTOP_INDICATOR</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>→ J7:6</t>
+  </si>
+  <si>
+    <t>TB5:16→</t>
+  </si>
+  <si>
+    <t>→ J7:2</t>
+  </si>
+  <si>
+    <t>TB5:14→</t>
+  </si>
+  <si>
+    <t>→ PL4:X2</t>
+  </si>
+  <si>
+    <t>TB5:12→</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>→ A2</t>
+  </si>
+  <si>
+    <t>TB5:10→</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>→ TB8:1</t>
+  </si>
+  <si>
+    <t>S1:22→</t>
+  </si>
+  <si>
+    <t>ESTOP_LOOP</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>→ J7:8</t>
+  </si>
+  <si>
+    <t>TB8:2→</t>
+  </si>
+  <si>
+    <t>→ PL1:X2</t>
+  </si>
+  <si>
+    <t>S1:14→</t>
+  </si>
+  <si>
+    <t>→ TB9:1</t>
+  </si>
+  <si>
+    <t>J7:5→</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>→ J7:4</t>
+  </si>
+  <si>
+    <t>TB9:2→</t>
+  </si>
+  <si>
+    <t>→ TB10:1</t>
+  </si>
+  <si>
+    <t>J7:1→</t>
+  </si>
+  <si>
+    <t>→ PB2:21</t>
+  </si>
+  <si>
+    <t>TB10:2→</t>
+  </si>
+  <si>
+    <t>→ TB6:1</t>
+  </si>
+  <si>
+    <t>PB2:22→</t>
+  </si>
+  <si>
+    <t>→ PB1:13</t>
+  </si>
+  <si>
+    <t>TB6:2→</t>
+  </si>
+  <si>
+    <t>→ K1:13</t>
+  </si>
+  <si>
+    <t>TB6:4→</t>
+  </si>
+  <si>
+    <t>→ TB7:1</t>
+  </si>
+  <si>
+    <t>PB1:14→</t>
+  </si>
+  <si>
+    <t>MACHINE_ENABLE</t>
+  </si>
+  <si>
+    <t>→ K1:14</t>
+  </si>
+  <si>
+    <t>TB7:4→</t>
+  </si>
+  <si>
+    <t>→ K1:A1</t>
+  </si>
+  <si>
+    <t>TB7:6→</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>→ PL4:X1</t>
+  </si>
+  <si>
+    <t>TB7:2→</t>
+  </si>
+  <si>
+    <t>→ P12:8</t>
+  </si>
+  <si>
+    <t>P7:8→</t>
+  </si>
+  <si>
+    <t>→ P12:7</t>
+  </si>
+  <si>
+    <t>P7:7→</t>
+  </si>
+  <si>
+    <t>→ P12:6</t>
+  </si>
+  <si>
+    <t>P7:6→</t>
+  </si>
+  <si>
+    <t>→ P12:5</t>
+  </si>
+  <si>
+    <t>P7:5→</t>
+  </si>
+  <si>
+    <t>→ S2:21</t>
+  </si>
+  <si>
+    <t>J12:8→</t>
+  </si>
+  <si>
+    <t>→ S2:13</t>
+  </si>
+  <si>
+    <t>J12:7→</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>→ J12:6</t>
+  </si>
+  <si>
+    <t>PL2:X2→</t>
+  </si>
+  <si>
+    <t>→ J12:5</t>
+  </si>
+  <si>
+    <t>S2:22→</t>
+  </si>
+  <si>
+    <t>→ PL2:X1</t>
+  </si>
+  <si>
+    <t>S2:14→</t>
+  </si>
+  <si>
+    <t>→ P12:4</t>
+  </si>
+  <si>
+    <t>P7:4→</t>
+  </si>
+  <si>
+    <t>→ P12:3</t>
+  </si>
+  <si>
+    <t>P7:3→</t>
+  </si>
+  <si>
+    <t>→ P12:2</t>
+  </si>
+  <si>
+    <t>P7:2→</t>
+  </si>
+  <si>
+    <t>→ P12:1</t>
+  </si>
+  <si>
+    <t>P7:1→</t>
+  </si>
+  <si>
+    <t>→ J13:4</t>
+  </si>
+  <si>
+    <t>P12:4→</t>
+  </si>
+  <si>
+    <t>→ J13:3</t>
+  </si>
+  <si>
+    <t>P12:3→</t>
+  </si>
+  <si>
+    <t>→ J13:2</t>
+  </si>
+  <si>
+    <t>P12:2→</t>
+  </si>
+  <si>
+    <t>→ J13:1</t>
+  </si>
+  <si>
+    <t>P12:1→</t>
+  </si>
+  <si>
+    <t>→ P17:4</t>
+  </si>
+  <si>
+    <t>P13:4→</t>
+  </si>
+  <si>
+    <t>Flex optional</t>
+  </si>
+  <si>
+    <t>→ P17:3</t>
+  </si>
+  <si>
+    <t>P13:3→</t>
+  </si>
+  <si>
+    <t>→ P17:2</t>
+  </si>
+  <si>
+    <t>P13:2→</t>
+  </si>
+  <si>
+    <t>→ P17:1</t>
+  </si>
+  <si>
+    <t>P13:1→</t>
+  </si>
+  <si>
+    <t>→ S3:21</t>
+  </si>
+  <si>
+    <t>J17:4→</t>
+  </si>
+  <si>
+    <t>→ S3:13</t>
+  </si>
+  <si>
+    <t>J17:3→</t>
+  </si>
+  <si>
+    <t>→ J17:2</t>
+  </si>
+  <si>
+    <t>PL3:X2→</t>
+  </si>
+  <si>
+    <t>→ J17:1</t>
+  </si>
+  <si>
+    <t>S3:22→</t>
+  </si>
+  <si>
+    <t>→ PL3:X1</t>
+  </si>
+  <si>
+    <t>S3:14→</t>
+  </si>
+  <si>
+    <t>→ TB11:1</t>
+  </si>
+  <si>
+    <t>PS4:V+1→</t>
+  </si>
+  <si>
+    <t>24V Power</t>
+  </si>
+  <si>
+    <t>V+1</t>
+  </si>
+  <si>
+    <t>→ TB11:13</t>
+  </si>
+  <si>
+    <t>PS4:V-1→</t>
+  </si>
+  <si>
+    <t>V-1</t>
+  </si>
+  <si>
+    <t>→ MESA:TB3:22</t>
+  </si>
+  <si>
+    <t>TB11:2→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB3:24</t>
+  </si>
+  <si>
+    <t>TB11:14→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB1:5</t>
+  </si>
+  <si>
+    <t>TB11:4→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB1:8</t>
+  </si>
+  <si>
+    <t>TB11:16→</t>
+  </si>
+  <si>
+    <t>→ FANS1:1</t>
+  </si>
+  <si>
+    <t>TB11:6→</t>
+  </si>
+  <si>
+    <t>FAN_PWR</t>
+  </si>
+  <si>
+    <t>FANS1</t>
+  </si>
+  <si>
+    <t>→ FANS1:2</t>
+  </si>
+  <si>
+    <t>TB11:18→</t>
+  </si>
+  <si>
+    <t>→ J2:1</t>
+  </si>
+  <si>
+    <t>TB11:8→</t>
+  </si>
+  <si>
+    <t>→ J2:2</t>
+  </si>
+  <si>
+    <t>TB11:20→</t>
+  </si>
+  <si>
+    <t>→ TI1:V+</t>
+  </si>
+  <si>
+    <t>TB11:10→</t>
+  </si>
+  <si>
+    <t>→ TI1:V-</t>
+  </si>
+  <si>
+    <t>TB11:22→</t>
+  </si>
+  <si>
+    <t>→ J4:2</t>
+  </si>
+  <si>
+    <t>MESA:TB6:17→</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>→ J4:1</t>
+  </si>
+  <si>
+    <t>TB11:24→</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>→ TI1:SIG</t>
+  </si>
+  <si>
+    <t>MESA:TB6:1→</t>
+  </si>
+  <si>
+    <t>TI1_VSENSE</t>
+  </si>
+  <si>
+    <t>SIG</t>
+  </si>
+  <si>
+    <t>→ P10:2</t>
+  </si>
+  <si>
+    <t>P2:2→</t>
+  </si>
+  <si>
+    <t>→ P10:1</t>
+  </si>
+  <si>
+    <t>P2:1→</t>
+  </si>
+  <si>
+    <t>→ TB51:1</t>
+  </si>
+  <si>
+    <t>J10:2→</t>
+  </si>
+  <si>
+    <t>→ TB52:1</t>
+  </si>
+  <si>
+    <t>J10:1→</t>
+  </si>
+  <si>
+    <t>→ J21:1</t>
+  </si>
+  <si>
+    <t>TB51:2→</t>
+  </si>
+  <si>
+    <t>→ J21:2</t>
+  </si>
+  <si>
+    <t>TB52:2→</t>
+  </si>
+  <si>
+    <t>→ LS1</t>
+  </si>
+  <si>
+    <t>TB51:3→</t>
+  </si>
+  <si>
+    <t>LIMIT_PWR</t>
+  </si>
+  <si>
+    <t>TB52:3→</t>
+  </si>
+  <si>
+    <t>LIMIT_GND</t>
+  </si>
+  <si>
+    <t>→ LS2</t>
+  </si>
+  <si>
+    <t>TB51:4→</t>
+  </si>
+  <si>
+    <t>TB52:4→</t>
+  </si>
+  <si>
+    <t>→ HS1</t>
+  </si>
+  <si>
+    <t>TB51:5→</t>
+  </si>
+  <si>
+    <t>TB52:5→</t>
+  </si>
+  <si>
+    <t>→ HS2</t>
+  </si>
+  <si>
+    <t>TB51:6→</t>
+  </si>
+  <si>
+    <t>TB52:6→</t>
+  </si>
+  <si>
+    <t>→ TP1</t>
+  </si>
+  <si>
+    <t>TB51:7→</t>
+  </si>
+  <si>
+    <t>PROBE_PWR</t>
+  </si>
+  <si>
+    <t>→ P20:2</t>
+  </si>
+  <si>
+    <t>P21:2→</t>
+  </si>
+  <si>
+    <t>→ P20:1</t>
+  </si>
+  <si>
+    <t>P21:1→</t>
+  </si>
+  <si>
+    <t>→ TB53:1</t>
+  </si>
+  <si>
+    <t>J20:2→</t>
+  </si>
+  <si>
+    <t>→ TB54:1</t>
+  </si>
+  <si>
+    <t>J20:1→</t>
+  </si>
+  <si>
+    <t>→ J25:1</t>
+  </si>
+  <si>
+    <t>TB53:2→</t>
+  </si>
+  <si>
+    <t>→ J25:2</t>
+  </si>
+  <si>
+    <t>TB54:2→</t>
+  </si>
+  <si>
+    <t>→ LS3</t>
+  </si>
+  <si>
+    <t>TB53:3→</t>
+  </si>
+  <si>
+    <t>TB54:3→</t>
+  </si>
+  <si>
+    <t>→ LS4</t>
+  </si>
+  <si>
+    <t>TB53:4→</t>
+  </si>
+  <si>
+    <t>TB54:4→</t>
+  </si>
+  <si>
+    <t>→ HS3</t>
+  </si>
+  <si>
+    <t>TB53:5→</t>
+  </si>
+  <si>
+    <t>TB54:5→</t>
+  </si>
+  <si>
+    <t>→ P29:2</t>
+  </si>
+  <si>
+    <t>P25:2→</t>
+  </si>
+  <si>
+    <t>→ P29:1</t>
+  </si>
+  <si>
+    <t>P25:1→</t>
+  </si>
+  <si>
+    <t>→ TB57:1</t>
+  </si>
+  <si>
+    <t>J29:2→</t>
+  </si>
+  <si>
+    <t>→ TB58:1</t>
+  </si>
+  <si>
+    <t>J29:1→</t>
+  </si>
+  <si>
+    <t>→ LS5</t>
+  </si>
+  <si>
+    <t>TB57:2→</t>
+  </si>
+  <si>
+    <t>TB58:2→</t>
+  </si>
+  <si>
+    <t>→ LS6</t>
+  </si>
+  <si>
+    <t>TB57:3→</t>
+  </si>
+  <si>
+    <t>TB58:3→</t>
+  </si>
+  <si>
+    <t>→ HS4</t>
+  </si>
+  <si>
+    <t>TB57:4→</t>
+  </si>
+  <si>
+    <t>TB58:4→</t>
+  </si>
+  <si>
+    <t>→ K2</t>
+  </si>
+  <si>
+    <t>P4:1→</t>
+  </si>
+  <si>
+    <t>Need suitable relay</t>
+  </si>
+  <si>
+    <t>P4:2→</t>
+  </si>
+  <si>
+    <t>→ J8:2</t>
+  </si>
+  <si>
+    <t>PS5:V+1→</t>
+  </si>
+  <si>
+    <t>48V Power</t>
+  </si>
+  <si>
+    <t>48V_LOGIC</t>
+  </si>
+  <si>
+    <t>🟧 Orange</t>
+  </si>
+  <si>
+    <t>→ J8:1</t>
+  </si>
+  <si>
+    <t>PS5:V-1→</t>
+  </si>
+  <si>
+    <t>🟫 Brown</t>
+  </si>
+  <si>
+    <t>→ J8:4</t>
+  </si>
+  <si>
+    <t>PS6:V+1→</t>
+  </si>
+  <si>
+    <t>→ J8:3</t>
+  </si>
+  <si>
+    <t>PS6:V-1→</t>
+  </si>
+  <si>
+    <t>→ SD2:DC+</t>
+  </si>
+  <si>
+    <t>PS6:V+2→</t>
+  </si>
+  <si>
+    <t>V+2</t>
+  </si>
+  <si>
+    <t>DC+</t>
+  </si>
+  <si>
+    <t>→ SD2:DC-</t>
+  </si>
+  <si>
+    <t>PS6:V-2→</t>
+  </si>
+  <si>
+    <t>V-2</t>
+  </si>
+  <si>
+    <t>DC-</t>
+  </si>
+  <si>
+    <t>PS6:V+3→</t>
+  </si>
+  <si>
+    <t>V+3</t>
+  </si>
+  <si>
+    <t>PS6:V-3→</t>
+  </si>
+  <si>
+    <t>V-3</t>
+  </si>
+  <si>
+    <t>→ P18:2</t>
+  </si>
+  <si>
+    <t>P8:2→</t>
+  </si>
+  <si>
+    <t>→ P18:1</t>
+  </si>
+  <si>
+    <t>P8:1→</t>
+  </si>
+  <si>
+    <t>→ P18:4</t>
+  </si>
+  <si>
+    <t>P8:4→</t>
+  </si>
+  <si>
+    <t>→ P18:3</t>
+  </si>
+  <si>
+    <t>P8:3→</t>
+  </si>
+  <si>
+    <t>→ J15:1</t>
+  </si>
+  <si>
+    <t>J18:2→</t>
+  </si>
+  <si>
+    <t>→ J15:2</t>
+  </si>
+  <si>
+    <t>J18:1→</t>
+  </si>
+  <si>
+    <t>→ J15:4</t>
+  </si>
+  <si>
+    <t>J18:4→</t>
+  </si>
+  <si>
+    <t>→ J15:3</t>
+  </si>
+  <si>
+    <t>J18:3→</t>
+  </si>
+  <si>
+    <t>→ P20:4</t>
+  </si>
+  <si>
+    <t>P15:2→</t>
+  </si>
+  <si>
+    <t>→ P20:3</t>
+  </si>
+  <si>
+    <t>P15:1→</t>
+  </si>
+  <si>
+    <t>→ P29:4</t>
+  </si>
+  <si>
+    <t>P15:4→</t>
+  </si>
+  <si>
+    <t>→ P29:3</t>
+  </si>
+  <si>
+    <t>P15:3→</t>
+  </si>
+  <si>
+    <t>→ TB55:1</t>
+  </si>
+  <si>
+    <t>J20:4→</t>
+  </si>
+  <si>
+    <t>→ TB56:1</t>
+  </si>
+  <si>
+    <t>J20:3→</t>
+  </si>
+  <si>
+    <t>→ IM1:VDC+</t>
+  </si>
+  <si>
+    <t>TB55:2→</t>
+  </si>
+  <si>
+    <t>STEP_IO_PWR</t>
+  </si>
+  <si>
+    <t>VDC+</t>
+  </si>
+  <si>
+    <t>→ IM1:GND</t>
+  </si>
+  <si>
+    <t>TB56:2→</t>
+  </si>
+  <si>
+    <t>STEP_IO_GND</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>→ IM2:VDC+</t>
+  </si>
+  <si>
+    <t>TB55:3→</t>
+  </si>
+  <si>
+    <t>→ IM2:GND</t>
+  </si>
+  <si>
+    <t>TB56:4→</t>
+  </si>
+  <si>
+    <t>→ IM3:VDC+</t>
+  </si>
+  <si>
+    <t>J29:4→</t>
+  </si>
+  <si>
+    <t>→ IM3:GND</t>
+  </si>
+  <si>
+    <t>J29:3→</t>
+  </si>
+  <si>
+    <t>→ J5:2</t>
+  </si>
+  <si>
+    <t>MESA:TB3:18→</t>
+  </si>
+  <si>
+    <t>Control Signals</t>
+  </si>
+  <si>
+    <t>SPINDLE_RS+</t>
+  </si>
+  <si>
+    <t>🧵 Aqua</t>
+  </si>
+  <si>
+    <t>→ J5:1</t>
+  </si>
+  <si>
+    <t>MESA:TB3:16→</t>
+  </si>
+  <si>
+    <t>SPINDLE_RS-</t>
+  </si>
+  <si>
+    <t>🩵 Teal</t>
+  </si>
+  <si>
+    <t>→ J1:1</t>
+  </si>
+  <si>
+    <t>MESA:TB2:2→</t>
+  </si>
+  <si>
+    <t>Y1_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:2</t>
+  </si>
+  <si>
+    <t>MESA:TB2:3→</t>
+  </si>
+  <si>
+    <t>Y1_STEP+</t>
+  </si>
+  <si>
+    <t>→ J1:3</t>
+  </si>
+  <si>
+    <t>MESA:TB2:4→</t>
+  </si>
+  <si>
+    <t>Y1_DIR-</t>
+  </si>
+  <si>
+    <t>🟩⬜️ Green/White</t>
+  </si>
+  <si>
+    <t>→ J1:4</t>
+  </si>
+  <si>
+    <t>MESA:TB2:5→</t>
+  </si>
+  <si>
+    <t>Y1_DIR+</t>
+  </si>
+  <si>
+    <t>🟩 Green</t>
+  </si>
+  <si>
+    <t>→ J1:5</t>
+  </si>
+  <si>
+    <t>MESA:TB2:8→</t>
+  </si>
+  <si>
+    <t>Y2_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:6</t>
+  </si>
+  <si>
+    <t>MESA:TB2:9→</t>
+  </si>
+  <si>
+    <t>Y2_STEP+</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>→ J1:7</t>
+  </si>
+  <si>
+    <t>MESA:TB2:10→</t>
+  </si>
+  <si>
+    <t>Y2_DIR-</t>
+  </si>
+  <si>
+    <t>→ J1:8</t>
+  </si>
+  <si>
+    <t>MESA:TB2:11→</t>
+  </si>
+  <si>
+    <t>Y2_DIR+</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>→ J1:9</t>
+  </si>
+  <si>
+    <t>MESA:TB2:14→</t>
+  </si>
+  <si>
+    <t>X_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:10</t>
+  </si>
+  <si>
+    <t>MESA:TB2:15→</t>
+  </si>
+  <si>
+    <t>X_STEP+</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>→ J1:11</t>
+  </si>
+  <si>
+    <t>MESA:TB2:16→</t>
+  </si>
+  <si>
+    <t>X_DIR-</t>
+  </si>
+  <si>
+    <t>→ J1:12</t>
+  </si>
+  <si>
+    <t>MESA:TB2:17→</t>
+  </si>
+  <si>
+    <t>X_DIR+</t>
+  </si>
+  <si>
+    <t>→ SD1:PUL-</t>
+  </si>
+  <si>
+    <t>MESA:TB2:20→</t>
+  </si>
+  <si>
+    <t>Z_STEP-</t>
+  </si>
+  <si>
+    <t>PUL-</t>
+  </si>
+  <si>
+    <t>→ SD1:PUL+</t>
+  </si>
+  <si>
+    <t>MESA:TB2:21→</t>
+  </si>
+  <si>
+    <t>Z_STEP+</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>PUL+</t>
+  </si>
+  <si>
+    <t>→ SD1:DIR-</t>
+  </si>
+  <si>
+    <t>MESA:TB2:22→</t>
+  </si>
+  <si>
+    <t>Z_DIR-</t>
+  </si>
+  <si>
+    <t>DIR-</t>
+  </si>
+  <si>
+    <t>→ SD1:DIR+</t>
+  </si>
+  <si>
+    <t>MESA:TB2:23→</t>
+  </si>
+  <si>
+    <t>Z_DIR+</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>DIR+</t>
+  </si>
+  <si>
+    <t>→ J3:8</t>
+  </si>
+  <si>
+    <t>SD1:A+→</t>
+  </si>
+  <si>
+    <t>Z_A+</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Double check colours/order</t>
+  </si>
+  <si>
+    <t>→ J3:7</t>
+  </si>
+  <si>
+    <t>SD1:A-→</t>
+  </si>
+  <si>
+    <t>Z_A-</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>→ J3:6</t>
+  </si>
+  <si>
+    <t>SD1:B+→</t>
+  </si>
+  <si>
+    <t>Z_B+</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>→ J3:5</t>
+  </si>
+  <si>
+    <t>SD1:B-→</t>
+  </si>
+  <si>
+    <t>Z_B-</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>→ J3:4</t>
+  </si>
+  <si>
+    <t>SD2:A+→</t>
+  </si>
+  <si>
+    <t>DUST_A+</t>
+  </si>
+  <si>
+    <t>→ J3:3</t>
+  </si>
+  <si>
+    <t>SD2:A-→</t>
+  </si>
+  <si>
+    <t>DUST_A-</t>
+  </si>
+  <si>
+    <t>→ J3:2</t>
+  </si>
+  <si>
+    <t>SD2:B+→</t>
+  </si>
+  <si>
+    <t>DUST_B+</t>
+  </si>
+  <si>
+    <t>→ J3:1</t>
+  </si>
+  <si>
+    <t>SD2:B-→</t>
+  </si>
+  <si>
+    <t>DUST_B-</t>
+  </si>
+  <si>
+    <t>→ J1:13</t>
+  </si>
+  <si>
+    <t>MESA:TB6:5→</t>
+  </si>
+  <si>
+    <t>Y_MIN</t>
+  </si>
+  <si>
+    <t>🩶 Grey</t>
+  </si>
+  <si>
+    <t>→ J1:14</t>
+  </si>
+  <si>
+    <t>MESA:TB6:6→</t>
+  </si>
+  <si>
+    <t>Y_MAX</t>
+  </si>
+  <si>
+    <t>→ J1:15</t>
+  </si>
+  <si>
+    <t>MESA:TB6:7→</t>
+  </si>
+  <si>
+    <t>Y1_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:16</t>
+  </si>
+  <si>
+    <t>MESA:TB6:8→</t>
+  </si>
+  <si>
+    <t>Y2_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:17</t>
+  </si>
+  <si>
+    <t>MESA:TB6:9→</t>
+  </si>
+  <si>
+    <t>X_MIN</t>
+  </si>
+  <si>
+    <t>→ J1:18</t>
+  </si>
+  <si>
+    <t>MESA:TB6:10→</t>
+  </si>
+  <si>
+    <t>X_MAX</t>
+  </si>
+  <si>
+    <t>→ J1:19</t>
+  </si>
+  <si>
+    <t>MESA:TB6:11→</t>
+  </si>
+  <si>
+    <t>X_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:20</t>
+  </si>
+  <si>
+    <t>MESA:TB6:12→</t>
+  </si>
+  <si>
+    <t>Z_MIN</t>
+  </si>
+  <si>
+    <t>→ J1:21</t>
+  </si>
+  <si>
+    <t>MESA:TB6:13→</t>
+  </si>
+  <si>
+    <t>Z_MAX</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>→ J1:22</t>
+  </si>
+  <si>
+    <t>MESA:TB6:14→</t>
+  </si>
+  <si>
+    <t>Z_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:23</t>
+  </si>
+  <si>
+    <t>MESA:TB6:15→</t>
+  </si>
+  <si>
+    <t>PROBE_IN</t>
+  </si>
+  <si>
+    <t>⬜️ White</t>
+  </si>
+  <si>
+    <t>→ FANS1:PWM</t>
+  </si>
+  <si>
+    <t>MESA:TB6:18→</t>
+  </si>
+  <si>
+    <t>FAN_PWM</t>
+  </si>
+  <si>
+    <t>PWM</t>
+  </si>
+  <si>
+    <t>→ J39:USB1</t>
+  </si>
+  <si>
+    <t>CPU1:USB1→</t>
+  </si>
+  <si>
+    <t>USB_HID</t>
+  </si>
+  <si>
+    <t>USB1</t>
+  </si>
+  <si>
+    <t>➖ not used</t>
+  </si>
+  <si>
+    <t>→ J38:USB1</t>
+  </si>
+  <si>
+    <t>CPU1:USB2→</t>
+  </si>
+  <si>
+    <t>USB_USER</t>
+  </si>
+  <si>
+    <t>USB2</t>
+  </si>
+  <si>
+    <t>Extend to monitor zone</t>
+  </si>
+  <si>
+    <t>→ J37:HDMI</t>
+  </si>
+  <si>
+    <t>CPU1:DP→</t>
+  </si>
+  <si>
+    <t>MONITOR</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>Add in dp/hdmi adapter</t>
+  </si>
+  <si>
+    <t>→ RF1:1</t>
+  </si>
+  <si>
+    <t>CPU1:RF→</t>
+  </si>
+  <si>
+    <t>WIFI_EXT</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>→ MESA:ETH</t>
+  </si>
+  <si>
+    <t>CPU1:ETH→</t>
+  </si>
+  <si>
+    <t>ETH_MESA</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>→ P11:8</t>
+  </si>
+  <si>
+    <t>P3:8→</t>
+  </si>
+  <si>
+    <t>→ P11:7</t>
+  </si>
+  <si>
+    <t>P3:7→</t>
+  </si>
+  <si>
+    <t>→ P11:6</t>
+  </si>
+  <si>
+    <t>P3:6→</t>
+  </si>
+  <si>
+    <t>→ P11:5</t>
+  </si>
+  <si>
+    <t>P3:5→</t>
+  </si>
+  <si>
+    <t>→ J18:1</t>
+  </si>
+  <si>
+    <t>J11:8→</t>
+  </si>
+  <si>
+    <t>→ J18:2</t>
+  </si>
+  <si>
+    <t>J11:7→</t>
+  </si>
+  <si>
+    <t>→ J18:3</t>
+  </si>
+  <si>
+    <t>J11:6→</t>
+  </si>
+  <si>
+    <t>→ J18:4</t>
+  </si>
+  <si>
+    <t>J11:5→</t>
+  </si>
+  <si>
+    <t>→ P30:8</t>
+  </si>
+  <si>
+    <t>P16:8→</t>
+  </si>
+  <si>
+    <t>→ P30:7</t>
+  </si>
+  <si>
+    <t>P16:7→</t>
+  </si>
+  <si>
+    <t>→ P30:6</t>
+  </si>
+  <si>
+    <t>P16:6→</t>
+  </si>
+  <si>
+    <t>→ P30:5</t>
+  </si>
+  <si>
+    <t>P16:5→</t>
+  </si>
+  <si>
+    <t>→ P11:4</t>
+  </si>
+  <si>
+    <t>P3:4→</t>
+  </si>
+  <si>
+    <t>→ P11:3</t>
+  </si>
+  <si>
+    <t>P3:3→</t>
+  </si>
+  <si>
+    <t>→ P11:2</t>
+  </si>
+  <si>
+    <t>P3:2→</t>
+  </si>
+  <si>
+    <t>→ P11:1</t>
+  </si>
+  <si>
+    <t>P3:1→</t>
+  </si>
+  <si>
+    <t>→ J16:4</t>
+  </si>
+  <si>
+    <t>J11:4→</t>
+  </si>
+  <si>
+    <t>→ J16:3</t>
+  </si>
+  <si>
+    <t>J11:3→</t>
+  </si>
+  <si>
+    <t>→ J16:2</t>
+  </si>
+  <si>
+    <t>J11:2→</t>
+  </si>
+  <si>
+    <t>→ J16:1</t>
+  </si>
+  <si>
+    <t>J11:1→</t>
+  </si>
+  <si>
+    <t>→ SM1</t>
+  </si>
+  <si>
+    <t>J30:8→</t>
+  </si>
+  <si>
+    <t>J30:7→</t>
+  </si>
+  <si>
+    <t>J30:6→</t>
+  </si>
+  <si>
+    <t>J30:5→</t>
+  </si>
+  <si>
+    <t>→ M1:1</t>
+  </si>
+  <si>
+    <t>VFD1:U→</t>
+  </si>
+  <si>
+    <t>SPINDLE_U</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
     <t>SOLDER</t>
   </si>
   <si>
-    <t>→ J35:N</t>
-  </si>
-  <si>
-    <t>TB2:14→</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>→ TB3:1</t>
-  </si>
-  <si>
-    <t>K1:T1→</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>→ TB3:11</t>
-  </si>
-  <si>
-    <t>K1:T2→</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>→ PS5:L</t>
-  </si>
-  <si>
-    <t>TB3:10→</t>
-  </si>
-  <si>
-    <t>→ PS5:N</t>
-  </si>
-  <si>
-    <t>TB3:20→</t>
-  </si>
-  <si>
-    <t>→ PS6:L</t>
-  </si>
-  <si>
-    <t>TB3:8→</t>
-  </si>
-  <si>
-    <t>→ PS6:N</t>
-  </si>
-  <si>
-    <t>TB3:18→</t>
-  </si>
-  <si>
-    <t>→ PS4:L</t>
-  </si>
-  <si>
-    <t>TB3:6→</t>
-  </si>
-  <si>
-    <t>→ PS4:N</t>
-  </si>
-  <si>
-    <t>TB3:16→</t>
-  </si>
-  <si>
-    <t>→ J6:4</t>
-  </si>
-  <si>
-    <t>TB3:4→</t>
-  </si>
-  <si>
-    <t>→ J6:3</t>
-  </si>
-  <si>
-    <t>TB3:14→</t>
-  </si>
-  <si>
-    <t>→ VFD1:R</t>
-  </si>
-  <si>
-    <t>P6:4→</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>→ VFD1:S</t>
-  </si>
-  <si>
-    <t>P6:3→</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>→ J36:L</t>
-  </si>
-  <si>
-    <t>P35:L→</t>
-  </si>
-  <si>
-    <t>→ J36:N</t>
-  </si>
-  <si>
-    <t>P35:N→</t>
-  </si>
-  <si>
-    <t>→ TB5:1</t>
-  </si>
-  <si>
-    <t>PS1:V+→</t>
-  </si>
-  <si>
-    <t>Estop/Power Mgmt</t>
-  </si>
-  <si>
-    <t>24V_LOGIC</t>
-  </si>
-  <si>
-    <t>V+</t>
-  </si>
-  <si>
-    <t>🟦 Blue</t>
-  </si>
-  <si>
-    <t>→ TB5:9</t>
-  </si>
-  <si>
-    <t>PS1:V-→</t>
-  </si>
-  <si>
-    <t>0V_LOGIC</t>
-  </si>
-  <si>
-    <t>V-</t>
-  </si>
-  <si>
-    <t>🟦⬜️ Blue/White</t>
-  </si>
-  <si>
-    <t>→ S1:21</t>
-  </si>
-  <si>
-    <t>TB5:8→</t>
-  </si>
-  <si>
-    <t>→ S1:13</t>
-  </si>
-  <si>
-    <t>TB5:6→</t>
-  </si>
-  <si>
-    <t>→ J7:7</t>
-  </si>
-  <si>
-    <t>TB5:4→</t>
-  </si>
-  <si>
-    <t>→ J7:3</t>
-  </si>
-  <si>
-    <t>TB5:2→</t>
-  </si>
-  <si>
-    <t>→ PL1:X1</t>
-  </si>
-  <si>
-    <t>TB5:18→</t>
-  </si>
-  <si>
-    <t>ESTOP_INDICATOR</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>→ J7:6</t>
-  </si>
-  <si>
-    <t>TB5:16→</t>
-  </si>
-  <si>
-    <t>→ J7:2</t>
-  </si>
-  <si>
-    <t>TB5:14→</t>
-  </si>
-  <si>
-    <t>→ PL4:X2</t>
-  </si>
-  <si>
-    <t>TB5:12→</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>→ A2</t>
-  </si>
-  <si>
-    <t>TB5:10→</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>→ TB8:1</t>
-  </si>
-  <si>
-    <t>S1:22→</t>
-  </si>
-  <si>
-    <t>ESTOP_LOOP</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>→ J7:8</t>
-  </si>
-  <si>
-    <t>TB8:2→</t>
-  </si>
-  <si>
-    <t>→ PL1:X2</t>
-  </si>
-  <si>
-    <t>S1:14→</t>
-  </si>
-  <si>
-    <t>→ TB9:1</t>
-  </si>
-  <si>
-    <t>J7:5→</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>→ J7:4</t>
-  </si>
-  <si>
-    <t>TB9:2→</t>
-  </si>
-  <si>
-    <t>→ TB10:1</t>
-  </si>
-  <si>
-    <t>J7:1→</t>
-  </si>
-  <si>
-    <t>→ PB2:21</t>
-  </si>
-  <si>
-    <t>TB10:2→</t>
-  </si>
-  <si>
-    <t>→ TB6:1</t>
-  </si>
-  <si>
-    <t>PB2:22→</t>
-  </si>
-  <si>
-    <t>→ PB1:13</t>
-  </si>
-  <si>
-    <t>TB6:2→</t>
-  </si>
-  <si>
-    <t>→ K1:13</t>
-  </si>
-  <si>
-    <t>TB6:4→</t>
-  </si>
-  <si>
-    <t>→ TB7:1</t>
-  </si>
-  <si>
-    <t>PB1:14→</t>
-  </si>
-  <si>
-    <t>MACHINE_ENABLE</t>
-  </si>
-  <si>
-    <t>→ K1:14</t>
-  </si>
-  <si>
-    <t>TB7:4→</t>
-  </si>
-  <si>
-    <t>→ K1:A1</t>
-  </si>
-  <si>
-    <t>TB7:6→</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>→ PL4:X1</t>
-  </si>
-  <si>
-    <t>TB7:2→</t>
-  </si>
-  <si>
-    <t>→ P12:8</t>
-  </si>
-  <si>
-    <t>P7:8→</t>
-  </si>
-  <si>
-    <t>→ P12:7</t>
-  </si>
-  <si>
-    <t>P7:7→</t>
-  </si>
-  <si>
-    <t>→ P12:6</t>
-  </si>
-  <si>
-    <t>P7:6→</t>
-  </si>
-  <si>
-    <t>→ P12:5</t>
-  </si>
-  <si>
-    <t>P7:5→</t>
-  </si>
-  <si>
-    <t>→ S2:21</t>
-  </si>
-  <si>
-    <t>J12:8→</t>
-  </si>
-  <si>
-    <t>→ S2:13</t>
-  </si>
-  <si>
-    <t>J12:7→</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>→ J12:6</t>
-  </si>
-  <si>
-    <t>PL2:X2→</t>
-  </si>
-  <si>
-    <t>→ J12:5</t>
-  </si>
-  <si>
-    <t>S2:22→</t>
-  </si>
-  <si>
-    <t>→ PL2:X1</t>
-  </si>
-  <si>
-    <t>S2:14→</t>
-  </si>
-  <si>
-    <t>→ P12:4</t>
-  </si>
-  <si>
-    <t>P7:4→</t>
-  </si>
-  <si>
-    <t>→ P12:3</t>
-  </si>
-  <si>
-    <t>P7:3→</t>
-  </si>
-  <si>
-    <t>→ P12:2</t>
-  </si>
-  <si>
-    <t>P7:2→</t>
-  </si>
-  <si>
-    <t>→ P12:1</t>
-  </si>
-  <si>
-    <t>P7:1→</t>
-  </si>
-  <si>
-    <t>→ J13:4</t>
-  </si>
-  <si>
-    <t>P12:4→</t>
-  </si>
-  <si>
-    <t>→ J13:3</t>
-  </si>
-  <si>
-    <t>P12:3→</t>
-  </si>
-  <si>
-    <t>→ J13:2</t>
-  </si>
-  <si>
-    <t>P12:2→</t>
-  </si>
-  <si>
-    <t>→ J13:1</t>
-  </si>
-  <si>
-    <t>P12:1→</t>
-  </si>
-  <si>
-    <t>→ P17:4</t>
-  </si>
-  <si>
-    <t>P13:4→</t>
-  </si>
-  <si>
-    <t>Flex optional</t>
-  </si>
-  <si>
-    <t>→ P17:3</t>
-  </si>
-  <si>
-    <t>P13:3→</t>
-  </si>
-  <si>
-    <t>→ P17:2</t>
-  </si>
-  <si>
-    <t>P13:2→</t>
-  </si>
-  <si>
-    <t>→ P17:1</t>
-  </si>
-  <si>
-    <t>P13:1→</t>
-  </si>
-  <si>
-    <t>→ S3:21</t>
-  </si>
-  <si>
-    <t>J17:4→</t>
-  </si>
-  <si>
-    <t>→ S3:13</t>
-  </si>
-  <si>
-    <t>J17:3→</t>
-  </si>
-  <si>
-    <t>→ J17:2</t>
-  </si>
-  <si>
-    <t>PL3:X2→</t>
-  </si>
-  <si>
-    <t>→ J17:1</t>
-  </si>
-  <si>
-    <t>S3:22→</t>
-  </si>
-  <si>
-    <t>→ PL3:X1</t>
-  </si>
-  <si>
-    <t>S3:14→</t>
-  </si>
-  <si>
-    <t>→ TB11:1</t>
-  </si>
-  <si>
-    <t>PS4:V+1→</t>
-  </si>
-  <si>
-    <t>24V Power</t>
-  </si>
-  <si>
-    <t>V+1</t>
-  </si>
-  <si>
-    <t>→ TB11:13</t>
-  </si>
-  <si>
-    <t>PS4:V-1→</t>
-  </si>
-  <si>
-    <t>V-1</t>
-  </si>
-  <si>
-    <t>→ MESA:TB3:22</t>
-  </si>
-  <si>
-    <t>TB11:2→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB3:24</t>
-  </si>
-  <si>
-    <t>TB11:14→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB1:5</t>
-  </si>
-  <si>
-    <t>TB11:4→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB1:8</t>
-  </si>
-  <si>
-    <t>TB11:16→</t>
-  </si>
-  <si>
-    <t>→ FANS1:1</t>
-  </si>
-  <si>
-    <t>TB11:6→</t>
-  </si>
-  <si>
-    <t>FAN_PWR</t>
-  </si>
-  <si>
-    <t>FANS1</t>
-  </si>
-  <si>
-    <t>→ FANS1:2</t>
-  </si>
-  <si>
-    <t>TB11:18→</t>
-  </si>
-  <si>
-    <t>→ J2:1</t>
-  </si>
-  <si>
-    <t>TB11:8→</t>
-  </si>
-  <si>
-    <t>→ J2:2</t>
-  </si>
-  <si>
-    <t>TB11:20→</t>
-  </si>
-  <si>
-    <t>→ TI1:V+</t>
-  </si>
-  <si>
-    <t>TB11:10→</t>
-  </si>
-  <si>
-    <t>→ TI1:V-</t>
-  </si>
-  <si>
-    <t>TB11:22→</t>
-  </si>
-  <si>
-    <t>→ J4:2</t>
-  </si>
-  <si>
-    <t>MESA:TB6:17→</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>→ J4:1</t>
-  </si>
-  <si>
-    <t>TB11:24→</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>→ TI1:SIG</t>
-  </si>
-  <si>
-    <t>MESA:TB6:1→</t>
-  </si>
-  <si>
-    <t>TI1_VSENSE</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>→ P10:2</t>
-  </si>
-  <si>
-    <t>P2:2→</t>
-  </si>
-  <si>
-    <t>→ P10:1</t>
-  </si>
-  <si>
-    <t>P2:1→</t>
-  </si>
-  <si>
-    <t>→ TB51:1</t>
-  </si>
-  <si>
-    <t>J10:2→</t>
-  </si>
-  <si>
-    <t>→ TB52:1</t>
-  </si>
-  <si>
-    <t>J10:1→</t>
-  </si>
-  <si>
-    <t>→ J21:1</t>
-  </si>
-  <si>
-    <t>TB51:2→</t>
-  </si>
-  <si>
-    <t>→ J21:2</t>
-  </si>
-  <si>
-    <t>TB52:2→</t>
-  </si>
-  <si>
-    <t>→ LS1</t>
-  </si>
-  <si>
-    <t>TB51:3→</t>
-  </si>
-  <si>
-    <t>LIMIT_PWR</t>
-  </si>
-  <si>
-    <t>TB52:3→</t>
-  </si>
-  <si>
-    <t>LIMIT_GND</t>
-  </si>
-  <si>
-    <t>→ LS2</t>
-  </si>
-  <si>
-    <t>TB51:4→</t>
-  </si>
-  <si>
-    <t>TB52:4→</t>
-  </si>
-  <si>
-    <t>→ HS1</t>
-  </si>
-  <si>
-    <t>TB51:5→</t>
-  </si>
-  <si>
-    <t>TB52:5→</t>
-  </si>
-  <si>
-    <t>→ HS2</t>
-  </si>
-  <si>
-    <t>TB51:6→</t>
-  </si>
-  <si>
-    <t>TB52:6→</t>
-  </si>
-  <si>
-    <t>→ TP1</t>
-  </si>
-  <si>
-    <t>TB51:7→</t>
-  </si>
-  <si>
-    <t>PROBE_PWR</t>
-  </si>
-  <si>
-    <t>→ P20:2</t>
-  </si>
-  <si>
-    <t>P21:2→</t>
-  </si>
-  <si>
-    <t>→ P20:1</t>
-  </si>
-  <si>
-    <t>P21:1→</t>
-  </si>
-  <si>
-    <t>→ TB53:1</t>
-  </si>
-  <si>
-    <t>J20:2→</t>
-  </si>
-  <si>
-    <t>→ TB54:1</t>
-  </si>
-  <si>
-    <t>J20:1→</t>
-  </si>
-  <si>
-    <t>→ J25:1</t>
-  </si>
-  <si>
-    <t>TB53:2→</t>
-  </si>
-  <si>
-    <t>→ J25:2</t>
-  </si>
-  <si>
-    <t>TB54:2→</t>
-  </si>
-  <si>
-    <t>→ LS3</t>
-  </si>
-  <si>
-    <t>TB53:3→</t>
-  </si>
-  <si>
-    <t>TB54:3→</t>
-  </si>
-  <si>
-    <t>→ LS4</t>
-  </si>
-  <si>
-    <t>TB53:4→</t>
-  </si>
-  <si>
-    <t>TB54:4→</t>
-  </si>
-  <si>
-    <t>→ HS3</t>
-  </si>
-  <si>
-    <t>TB53:5→</t>
-  </si>
-  <si>
-    <t>TB54:5→</t>
-  </si>
-  <si>
-    <t>→ P29:2</t>
-  </si>
-  <si>
-    <t>P25:2→</t>
-  </si>
-  <si>
-    <t>→ P29:1</t>
-  </si>
-  <si>
-    <t>P25:1→</t>
-  </si>
-  <si>
-    <t>→ TB57:1</t>
-  </si>
-  <si>
-    <t>J29:2→</t>
-  </si>
-  <si>
-    <t>→ TB58:1</t>
-  </si>
-  <si>
-    <t>J29:1→</t>
-  </si>
-  <si>
-    <t>→ LS5</t>
-  </si>
-  <si>
-    <t>TB57:2→</t>
-  </si>
-  <si>
-    <t>TB58:2→</t>
-  </si>
-  <si>
-    <t>→ LS6</t>
-  </si>
-  <si>
-    <t>TB57:3→</t>
-  </si>
-  <si>
-    <t>TB58:3→</t>
-  </si>
-  <si>
-    <t>→ HS4</t>
-  </si>
-  <si>
-    <t>TB57:4→</t>
-  </si>
-  <si>
-    <t>TB58:4→</t>
-  </si>
-  <si>
-    <t>→ K2</t>
-  </si>
-  <si>
-    <t>P4:1→</t>
-  </si>
-  <si>
-    <t>Need suitable relay</t>
-  </si>
-  <si>
-    <t>P4:2→</t>
-  </si>
-  <si>
-    <t>→ J8:2</t>
-  </si>
-  <si>
-    <t>PS5:V+1→</t>
-  </si>
-  <si>
-    <t>48V Power</t>
-  </si>
-  <si>
-    <t>48V_LOGIC</t>
-  </si>
-  <si>
-    <t>🟧 Orange</t>
-  </si>
-  <si>
-    <t>→ J8:1</t>
-  </si>
-  <si>
-    <t>PS5:V-1→</t>
-  </si>
-  <si>
-    <t>🟫 Brown</t>
-  </si>
-  <si>
-    <t>→ J8:4</t>
-  </si>
-  <si>
-    <t>PS6:V+1→</t>
-  </si>
-  <si>
-    <t>→ J8:3</t>
-  </si>
-  <si>
-    <t>PS6:V-1→</t>
-  </si>
-  <si>
-    <t>→ SD2:DC+</t>
-  </si>
-  <si>
-    <t>PS6:V+2→</t>
-  </si>
-  <si>
-    <t>V+2</t>
-  </si>
-  <si>
-    <t>DC+</t>
-  </si>
-  <si>
-    <t>→ SD2:DC-</t>
-  </si>
-  <si>
-    <t>PS6:V-2→</t>
-  </si>
-  <si>
-    <t>V-2</t>
-  </si>
-  <si>
-    <t>DC-</t>
-  </si>
-  <si>
-    <t>PS6:V+3→</t>
-  </si>
-  <si>
-    <t>V+3</t>
-  </si>
-  <si>
-    <t>PS6:V-3→</t>
-  </si>
-  <si>
-    <t>V-3</t>
-  </si>
-  <si>
-    <t>→ P18:2</t>
-  </si>
-  <si>
-    <t>P8:2→</t>
-  </si>
-  <si>
-    <t>→ P18:1</t>
-  </si>
-  <si>
-    <t>P8:1→</t>
-  </si>
-  <si>
-    <t>→ P18:4</t>
-  </si>
-  <si>
-    <t>P8:4→</t>
-  </si>
-  <si>
-    <t>→ P18:3</t>
-  </si>
-  <si>
-    <t>P8:3→</t>
-  </si>
-  <si>
-    <t>→ J15:1</t>
-  </si>
-  <si>
-    <t>J18:2→</t>
-  </si>
-  <si>
-    <t>→ J15:2</t>
-  </si>
-  <si>
-    <t>J18:1→</t>
-  </si>
-  <si>
-    <t>→ J15:4</t>
-  </si>
-  <si>
-    <t>J18:4→</t>
-  </si>
-  <si>
-    <t>→ J15:3</t>
-  </si>
-  <si>
-    <t>J18:3→</t>
-  </si>
-  <si>
-    <t>→ P20:4</t>
-  </si>
-  <si>
-    <t>P15:2→</t>
-  </si>
-  <si>
-    <t>→ P20:3</t>
-  </si>
-  <si>
-    <t>P15:1→</t>
-  </si>
-  <si>
-    <t>→ P29:4</t>
-  </si>
-  <si>
-    <t>P15:4→</t>
-  </si>
-  <si>
-    <t>→ P29:3</t>
-  </si>
-  <si>
-    <t>P15:3→</t>
-  </si>
-  <si>
-    <t>→ TB55:1</t>
-  </si>
-  <si>
-    <t>J20:4→</t>
-  </si>
-  <si>
-    <t>→ TB56:1</t>
-  </si>
-  <si>
-    <t>J20:3→</t>
-  </si>
-  <si>
-    <t>→ IM1:VDC+</t>
-  </si>
-  <si>
-    <t>TB55:2→</t>
-  </si>
-  <si>
-    <t>STEP_IO_PWR</t>
-  </si>
-  <si>
-    <t>VDC+</t>
-  </si>
-  <si>
-    <t>→ IM1:GND</t>
-  </si>
-  <si>
-    <t>TB56:2→</t>
-  </si>
-  <si>
-    <t>STEP_IO_GND</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>→ IM2:VDC+</t>
-  </si>
-  <si>
-    <t>TB55:3→</t>
-  </si>
-  <si>
-    <t>→ IM2:GND</t>
-  </si>
-  <si>
-    <t>TB56:4→</t>
-  </si>
-  <si>
-    <t>→ IM3:VDC+</t>
-  </si>
-  <si>
-    <t>J29:4→</t>
-  </si>
-  <si>
-    <t>→ IM3:GND</t>
-  </si>
-  <si>
-    <t>J29:3→</t>
-  </si>
-  <si>
-    <t>→ J5:2</t>
-  </si>
-  <si>
-    <t>MESA:TB3:18→</t>
-  </si>
-  <si>
-    <t>Control Signals</t>
-  </si>
-  <si>
-    <t>SPINDLE_RS+</t>
-  </si>
-  <si>
-    <t>🧵 Aqua</t>
-  </si>
-  <si>
-    <t>→ J5:1</t>
-  </si>
-  <si>
-    <t>MESA:TB3:16→</t>
-  </si>
-  <si>
-    <t>SPINDLE_RS-</t>
-  </si>
-  <si>
-    <t>🩵 Teal</t>
-  </si>
-  <si>
-    <t>→ J1:1</t>
-  </si>
-  <si>
-    <t>MESA:TB2:2→</t>
-  </si>
-  <si>
-    <t>Y1_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:2</t>
-  </si>
-  <si>
-    <t>MESA:TB2:3→</t>
-  </si>
-  <si>
-    <t>Y1_STEP+</t>
-  </si>
-  <si>
-    <t>→ J1:3</t>
-  </si>
-  <si>
-    <t>MESA:TB2:4→</t>
-  </si>
-  <si>
-    <t>Y1_DIR-</t>
-  </si>
-  <si>
-    <t>🟩⬜️ Green/White</t>
-  </si>
-  <si>
-    <t>→ J1:4</t>
-  </si>
-  <si>
-    <t>MESA:TB2:5→</t>
-  </si>
-  <si>
-    <t>Y1_DIR+</t>
-  </si>
-  <si>
-    <t>🟩 Green</t>
-  </si>
-  <si>
-    <t>→ J1:5</t>
-  </si>
-  <si>
-    <t>MESA:TB2:8→</t>
-  </si>
-  <si>
-    <t>Y2_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:6</t>
-  </si>
-  <si>
-    <t>MESA:TB2:9→</t>
-  </si>
-  <si>
-    <t>Y2_STEP+</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>→ J1:7</t>
-  </si>
-  <si>
-    <t>MESA:TB2:10→</t>
-  </si>
-  <si>
-    <t>Y2_DIR-</t>
-  </si>
-  <si>
-    <t>→ J1:8</t>
-  </si>
-  <si>
-    <t>MESA:TB2:11→</t>
-  </si>
-  <si>
-    <t>Y2_DIR+</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>→ J1:9</t>
-  </si>
-  <si>
-    <t>MESA:TB2:14→</t>
-  </si>
-  <si>
-    <t>X_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:10</t>
-  </si>
-  <si>
-    <t>MESA:TB2:15→</t>
-  </si>
-  <si>
-    <t>X_STEP+</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>→ J1:11</t>
-  </si>
-  <si>
-    <t>MESA:TB2:16→</t>
-  </si>
-  <si>
-    <t>X_DIR-</t>
-  </si>
-  <si>
-    <t>→ J1:12</t>
-  </si>
-  <si>
-    <t>MESA:TB2:17→</t>
-  </si>
-  <si>
-    <t>X_DIR+</t>
-  </si>
-  <si>
-    <t>→ SD1:PUL-</t>
-  </si>
-  <si>
-    <t>MESA:TB2:20→</t>
-  </si>
-  <si>
-    <t>Z_STEP-</t>
-  </si>
-  <si>
-    <t>PUL-</t>
-  </si>
-  <si>
-    <t>→ SD1:PUL+</t>
-  </si>
-  <si>
-    <t>MESA:TB2:21→</t>
-  </si>
-  <si>
-    <t>Z_STEP+</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>PUL+</t>
-  </si>
-  <si>
-    <t>→ SD1:DIR-</t>
-  </si>
-  <si>
-    <t>MESA:TB2:22→</t>
-  </si>
-  <si>
-    <t>Z_DIR-</t>
-  </si>
-  <si>
-    <t>DIR-</t>
-  </si>
-  <si>
-    <t>→ SD1:DIR+</t>
-  </si>
-  <si>
-    <t>MESA:TB2:23→</t>
-  </si>
-  <si>
-    <t>Z_DIR+</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>DIR+</t>
-  </si>
-  <si>
-    <t>→ J3:8</t>
-  </si>
-  <si>
-    <t>SD1:A+→</t>
-  </si>
-  <si>
-    <t>Z_A+</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Double check colours/order</t>
-  </si>
-  <si>
-    <t>→ J3:7</t>
-  </si>
-  <si>
-    <t>SD1:A-→</t>
-  </si>
-  <si>
-    <t>Z_A-</t>
-  </si>
-  <si>
-    <t>A-</t>
-  </si>
-  <si>
-    <t>→ J3:6</t>
-  </si>
-  <si>
-    <t>SD1:B+→</t>
-  </si>
-  <si>
-    <t>Z_B+</t>
-  </si>
-  <si>
-    <t>B+</t>
-  </si>
-  <si>
-    <t>→ J3:5</t>
-  </si>
-  <si>
-    <t>SD1:B-→</t>
-  </si>
-  <si>
-    <t>Z_B-</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>→ J3:4</t>
-  </si>
-  <si>
-    <t>SD2:A+→</t>
-  </si>
-  <si>
-    <t>DUST_A+</t>
-  </si>
-  <si>
-    <t>→ J3:3</t>
-  </si>
-  <si>
-    <t>SD2:A-→</t>
-  </si>
-  <si>
-    <t>DUST_A-</t>
-  </si>
-  <si>
-    <t>→ J3:2</t>
-  </si>
-  <si>
-    <t>SD2:B+→</t>
-  </si>
-  <si>
-    <t>DUST_B+</t>
-  </si>
-  <si>
-    <t>→ J3:1</t>
-  </si>
-  <si>
-    <t>SD2:B-→</t>
-  </si>
-  <si>
-    <t>DUST_B-</t>
-  </si>
-  <si>
-    <t>→ J1:13</t>
-  </si>
-  <si>
-    <t>MESA:TB6:5→</t>
-  </si>
-  <si>
-    <t>Y_MIN</t>
-  </si>
-  <si>
-    <t>🩶 Grey</t>
-  </si>
-  <si>
-    <t>→ J1:14</t>
-  </si>
-  <si>
-    <t>MESA:TB6:6→</t>
-  </si>
-  <si>
-    <t>Y_MAX</t>
-  </si>
-  <si>
-    <t>→ J1:15</t>
-  </si>
-  <si>
-    <t>MESA:TB6:7→</t>
-  </si>
-  <si>
-    <t>Y1_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:16</t>
-  </si>
-  <si>
-    <t>MESA:TB6:8→</t>
-  </si>
-  <si>
-    <t>Y2_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:17</t>
-  </si>
-  <si>
-    <t>MESA:TB6:9→</t>
-  </si>
-  <si>
-    <t>X_MIN</t>
-  </si>
-  <si>
-    <t>→ J1:18</t>
-  </si>
-  <si>
-    <t>MESA:TB6:10→</t>
-  </si>
-  <si>
-    <t>X_MAX</t>
-  </si>
-  <si>
-    <t>→ J1:19</t>
-  </si>
-  <si>
-    <t>MESA:TB6:11→</t>
-  </si>
-  <si>
-    <t>X_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:20</t>
-  </si>
-  <si>
-    <t>MESA:TB6:12→</t>
-  </si>
-  <si>
-    <t>Z_MIN</t>
-  </si>
-  <si>
-    <t>→ J1:21</t>
-  </si>
-  <si>
-    <t>MESA:TB6:13→</t>
-  </si>
-  <si>
-    <t>Z_MAX</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>→ J1:22</t>
-  </si>
-  <si>
-    <t>MESA:TB6:14→</t>
-  </si>
-  <si>
-    <t>Z_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:23</t>
-  </si>
-  <si>
-    <t>MESA:TB6:15→</t>
-  </si>
-  <si>
-    <t>PROBE_IN</t>
-  </si>
-  <si>
-    <t>⬜️ White</t>
-  </si>
-  <si>
-    <t>→ FANS1:PWM</t>
-  </si>
-  <si>
-    <t>MESA:TB6:18→</t>
-  </si>
-  <si>
-    <t>FAN_PWM</t>
-  </si>
-  <si>
-    <t>PWM</t>
-  </si>
-  <si>
-    <t>→ J39:USB1</t>
-  </si>
-  <si>
-    <t>CPU1:USB1→</t>
-  </si>
-  <si>
-    <t>USB_HID</t>
-  </si>
-  <si>
-    <t>USB1</t>
-  </si>
-  <si>
-    <t>➖ not used</t>
-  </si>
-  <si>
-    <t>→ J38:USB1</t>
-  </si>
-  <si>
-    <t>CPU1:USB2→</t>
-  </si>
-  <si>
-    <t>USB_USER</t>
-  </si>
-  <si>
-    <t>USB2</t>
-  </si>
-  <si>
-    <t>Extend to monitor zone</t>
-  </si>
-  <si>
-    <t>→ J37:HDMI</t>
-  </si>
-  <si>
-    <t>CPU1:DP→</t>
-  </si>
-  <si>
-    <t>MONITOR</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>Add in dp/hdmi adapter</t>
-  </si>
-  <si>
-    <t>→ RF1:1</t>
-  </si>
-  <si>
-    <t>CPU1:RF→</t>
-  </si>
-  <si>
-    <t>WIFI_EXT</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>→ MESA:ETH</t>
-  </si>
-  <si>
-    <t>CPU1:ETH→</t>
-  </si>
-  <si>
-    <t>ETH_MESA</t>
-  </si>
-  <si>
-    <t>ETH</t>
-  </si>
-  <si>
-    <t>→ P11:8</t>
-  </si>
-  <si>
-    <t>P3:8→</t>
-  </si>
-  <si>
-    <t>→ P11:7</t>
-  </si>
-  <si>
-    <t>P3:7→</t>
-  </si>
-  <si>
-    <t>→ P11:6</t>
-  </si>
-  <si>
-    <t>P3:6→</t>
-  </si>
-  <si>
-    <t>→ P11:5</t>
-  </si>
-  <si>
-    <t>P3:5→</t>
-  </si>
-  <si>
-    <t>→ J18:1</t>
-  </si>
-  <si>
-    <t>J11:8→</t>
-  </si>
-  <si>
-    <t>→ J18:2</t>
-  </si>
-  <si>
-    <t>J11:7→</t>
-  </si>
-  <si>
-    <t>→ J18:3</t>
-  </si>
-  <si>
-    <t>J11:6→</t>
-  </si>
-  <si>
-    <t>→ J18:4</t>
-  </si>
-  <si>
-    <t>J11:5→</t>
-  </si>
-  <si>
-    <t>→ P30:8</t>
-  </si>
-  <si>
-    <t>P16:8→</t>
-  </si>
-  <si>
-    <t>→ P30:7</t>
-  </si>
-  <si>
-    <t>P16:7→</t>
-  </si>
-  <si>
-    <t>→ P30:6</t>
-  </si>
-  <si>
-    <t>P16:6→</t>
-  </si>
-  <si>
-    <t>→ P30:5</t>
-  </si>
-  <si>
-    <t>P16:5→</t>
-  </si>
-  <si>
-    <t>→ P11:4</t>
-  </si>
-  <si>
-    <t>P3:4→</t>
-  </si>
-  <si>
-    <t>→ P11:3</t>
-  </si>
-  <si>
-    <t>P3:3→</t>
-  </si>
-  <si>
-    <t>→ P11:2</t>
-  </si>
-  <si>
-    <t>P3:2→</t>
-  </si>
-  <si>
-    <t>→ P11:1</t>
-  </si>
-  <si>
-    <t>P3:1→</t>
-  </si>
-  <si>
-    <t>→ J16:4</t>
-  </si>
-  <si>
-    <t>J11:4→</t>
-  </si>
-  <si>
-    <t>→ J16:3</t>
-  </si>
-  <si>
-    <t>J11:3→</t>
-  </si>
-  <si>
-    <t>→ J16:2</t>
-  </si>
-  <si>
-    <t>J11:2→</t>
-  </si>
-  <si>
-    <t>→ J16:1</t>
-  </si>
-  <si>
-    <t>J11:1→</t>
-  </si>
-  <si>
-    <t>→ SM1</t>
-  </si>
-  <si>
-    <t>J30:8→</t>
-  </si>
-  <si>
-    <t>J30:7→</t>
-  </si>
-  <si>
-    <t>J30:6→</t>
-  </si>
-  <si>
-    <t>J30:5→</t>
-  </si>
-  <si>
-    <t>→ M1:1</t>
-  </si>
-  <si>
-    <t>VFD1:U→</t>
-  </si>
-  <si>
-    <t>SPINDLE_U</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
     <t>→ M1:2</t>
   </si>
   <si>
@@ -3467,9 +3470,6 @@
   </si>
   <si>
     <t>TB4:3→</t>
-  </si>
-  <si>
-    <t>SPADE</t>
   </si>
   <si>
     <t>→ PS5:GND</t>
@@ -24703,7 +24703,7 @@
         <v>1</v>
       </c>
       <c r="N233" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O233" s="33">
         <v>10</v>
@@ -24736,14 +24736,14 @@
         <v>407</v>
       </c>
       <c r="F234" t="s" s="20">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="G234" t="s" s="20">
         <v>296</v>
       </c>
       <c r="H234" s="20"/>
       <c r="I234" t="s" s="20">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J234" t="s" s="20">
         <v>329</v>
@@ -24756,7 +24756,7 @@
         <v>2</v>
       </c>
       <c r="N234" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O234" s="33">
         <v>10</v>
@@ -24789,14 +24789,14 @@
         <v>407</v>
       </c>
       <c r="F235" t="s" s="20">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G235" t="s" s="20">
         <v>296</v>
       </c>
       <c r="H235" s="20"/>
       <c r="I235" t="s" s="20">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J235" t="s" s="20">
         <v>329</v>
@@ -24809,7 +24809,7 @@
         <v>3</v>
       </c>
       <c r="N235" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O235" s="33">
         <v>10</v>
@@ -28355,7 +28355,7 @@
       </c>
       <c r="H302" s="20"/>
       <c r="I302" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J302" t="s" s="20">
         <v>329</v>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="L302" s="20"/>
       <c r="M302" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N302" t="s" s="20">
         <v>329</v>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H313" s="20"/>
       <c r="I313" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J313" t="s" s="20">
         <v>329</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="L313" s="20"/>
       <c r="M313" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N313" t="s" s="20">
         <v>329</v>
@@ -29279,7 +29279,7 @@
       </c>
       <c r="H320" s="20"/>
       <c r="I320" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J320" t="s" s="20">
         <v>329</v>
@@ -29289,7 +29289,7 @@
       </c>
       <c r="L320" s="20"/>
       <c r="M320" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N320" t="s" s="20">
         <v>329</v>
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H326" s="20"/>
       <c r="I326" t="s" s="20">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J326" t="s" s="20">
         <v>329</v>
@@ -30096,20 +30096,20 @@
         <v>P0:PE→</v>
       </c>
       <c r="D336" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E336" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F336" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G336" t="s" s="20">
         <v>153</v>
       </c>
       <c r="H336" s="20"/>
       <c r="I336" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J336" t="s" s="20">
         <v>328</v>
@@ -30149,13 +30149,13 @@
         <v>TB1:2→</v>
       </c>
       <c r="D337" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E337" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F337" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G337" t="s" s="20">
         <v>259</v>
@@ -30202,13 +30202,13 @@
         <v>TB4:3→</v>
       </c>
       <c r="D338" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E338" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F338" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G338" t="s" s="20">
         <v>271</v>
@@ -30225,10 +30225,10 @@
       </c>
       <c r="L338" s="20"/>
       <c r="M338" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N338" t="s" s="20">
-        <v>1132</v>
+        <v>379</v>
       </c>
       <c r="O338" s="33">
         <v>10</v>
@@ -30255,13 +30255,13 @@
         <v>TB4:18→</v>
       </c>
       <c r="D339" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E339" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F339" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G339" t="s" s="20">
         <v>271</v>
@@ -30308,13 +30308,13 @@
         <v>TB4:16→</v>
       </c>
       <c r="D340" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E340" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F340" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G340" t="s" s="20">
         <v>271</v>
@@ -30361,13 +30361,13 @@
         <v>TB4:14→</v>
       </c>
       <c r="D341" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E341" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F341" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G341" t="s" s="20">
         <v>271</v>
@@ -30414,13 +30414,13 @@
         <v>TB4:12→</v>
       </c>
       <c r="D342" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E342" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F342" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G342" t="s" s="20">
         <v>271</v>
@@ -30467,13 +30467,13 @@
         <v>TB4:10→</v>
       </c>
       <c r="D343" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E343" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F343" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G343" t="s" s="20">
         <v>271</v>
@@ -30520,13 +30520,13 @@
         <v>TB4:8→</v>
       </c>
       <c r="D344" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E344" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F344" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G344" t="s" s="20">
         <v>271</v>
@@ -30573,13 +30573,13 @@
         <v>TB4:6→</v>
       </c>
       <c r="D345" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E345" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F345" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G345" t="s" s="20">
         <v>271</v>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="L345" s="20"/>
       <c r="M345" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N345" t="s" s="20">
         <v>328</v>
@@ -30626,13 +30626,13 @@
         <v>TB4:4→</v>
       </c>
       <c r="D346" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E346" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F346" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G346" t="s" s="20">
         <v>271</v>
@@ -30649,10 +30649,10 @@
       </c>
       <c r="L346" s="20"/>
       <c r="M346" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N346" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O346" s="33">
         <v>10</v>
@@ -30679,13 +30679,13 @@
         <v>TB4:20→</v>
       </c>
       <c r="D347" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E347" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F347" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G347" t="s" s="20">
         <v>271</v>
@@ -30734,13 +30734,13 @@
         <v>TB4:2→</v>
       </c>
       <c r="D348" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E348" t="s" s="19">
         <v>28</v>
       </c>
       <c r="F348" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G348" t="s" s="20">
         <v>271</v>
@@ -30789,13 +30789,13 @@
         <v>P6:2→</v>
       </c>
       <c r="D349" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E349" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F349" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G349" t="s" s="20">
         <v>188</v>
@@ -30815,7 +30815,7 @@
         <v>706</v>
       </c>
       <c r="N349" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O349" s="33">
         <v>10</v>
@@ -30842,13 +30842,13 @@
         <v>P6:1→</v>
       </c>
       <c r="D350" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E350" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F350" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G350" t="s" s="20">
         <v>188</v>
@@ -30868,7 +30868,7 @@
         <v>4</v>
       </c>
       <c r="N350" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O350" s="33">
         <v>10</v>
@@ -30895,13 +30895,13 @@
         <v>P1:GND→</v>
       </c>
       <c r="D351" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E351" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F351" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G351" t="s" s="20">
         <v>159</v>
@@ -30921,7 +30921,7 @@
         <v>706</v>
       </c>
       <c r="N351" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O351" s="33">
         <v>14</v>
@@ -30948,13 +30948,13 @@
         <v>J9:GND→</v>
       </c>
       <c r="D352" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E352" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F352" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G352" t="s" s="20">
         <v>120</v>
@@ -30974,7 +30974,7 @@
         <v>706</v>
       </c>
       <c r="N352" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O352" s="33">
         <v>14</v>
@@ -31001,13 +31001,13 @@
         <v>P14:GND→</v>
       </c>
       <c r="D353" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E353" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F353" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G353" t="s" s="20">
         <v>165</v>
@@ -31027,7 +31027,7 @@
         <v>706</v>
       </c>
       <c r="N353" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O353" s="33">
         <v>14</v>
@@ -31054,13 +31054,13 @@
         <v>J19:GND→</v>
       </c>
       <c r="D354" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E354" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F354" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G354" t="s" s="20">
         <v>89</v>
@@ -31080,7 +31080,7 @@
         <v>9</v>
       </c>
       <c r="N354" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O354" s="33">
         <v>14</v>
@@ -31107,13 +31107,13 @@
         <v>P24:9→</v>
       </c>
       <c r="D355" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E355" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F355" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G355" t="s" s="20">
         <v>174</v>
@@ -31133,7 +31133,7 @@
         <v>9</v>
       </c>
       <c r="N355" t="s" s="20">
-        <v>379</v>
+        <v>924</v>
       </c>
       <c r="O355" s="33">
         <v>14</v>
@@ -31160,20 +31160,20 @@
         <v>P35:PE→</v>
       </c>
       <c r="D356" t="s" s="21">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E356" t="s" s="19">
         <v>407</v>
       </c>
       <c r="F356" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G356" t="s" s="20">
         <v>181</v>
       </c>
       <c r="H356" s="20"/>
       <c r="I356" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J356" t="s" s="20">
         <v>328</v>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="L356" s="20"/>
       <c r="M356" t="s" s="20">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N356" t="s" s="20">
         <v>328</v>

--- a/documentation/wiring-diagram/Dustie Wiring Chart.export.xlsx
+++ b/documentation/wiring-diagram/Dustie Wiring Chart.export.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2187">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -1210,2266 +1210,2269 @@
     <t>TB2:4→</t>
   </si>
   <si>
+    <t>BLADE</t>
+  </si>
+  <si>
+    <t>→ J35:N</t>
+  </si>
+  <si>
+    <t>TB2:14→</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>→ TB3:1</t>
+  </si>
+  <si>
+    <t>K1:T1→</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>→ TB3:11</t>
+  </si>
+  <si>
+    <t>K1:T2→</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>→ PS5:L</t>
+  </si>
+  <si>
+    <t>TB3:10→</t>
+  </si>
+  <si>
+    <t>→ PS5:N</t>
+  </si>
+  <si>
+    <t>TB3:20→</t>
+  </si>
+  <si>
+    <t>→ PS6:L</t>
+  </si>
+  <si>
+    <t>TB3:8→</t>
+  </si>
+  <si>
+    <t>→ PS6:N</t>
+  </si>
+  <si>
+    <t>TB3:18→</t>
+  </si>
+  <si>
+    <t>→ PS4:L</t>
+  </si>
+  <si>
+    <t>TB3:6→</t>
+  </si>
+  <si>
+    <t>→ PS4:N</t>
+  </si>
+  <si>
+    <t>TB3:16→</t>
+  </si>
+  <si>
+    <t>→ J6:4</t>
+  </si>
+  <si>
+    <t>TB3:4→</t>
+  </si>
+  <si>
+    <t>→ J6:3</t>
+  </si>
+  <si>
+    <t>TB3:14→</t>
+  </si>
+  <si>
+    <t>→ VFD1:R</t>
+  </si>
+  <si>
+    <t>P6:4→</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>→ VFD1:S</t>
+  </si>
+  <si>
+    <t>P6:3→</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>→ J36:L</t>
+  </si>
+  <si>
+    <t>P35:L→</t>
+  </si>
+  <si>
+    <t>→ J36:N</t>
+  </si>
+  <si>
+    <t>P35:N→</t>
+  </si>
+  <si>
+    <t>→ TB5:1</t>
+  </si>
+  <si>
+    <t>PS1:V+→</t>
+  </si>
+  <si>
+    <t>Estop/Power Mgmt</t>
+  </si>
+  <si>
+    <t>24V_LOGIC</t>
+  </si>
+  <si>
+    <t>V+</t>
+  </si>
+  <si>
+    <t>🟦 Blue</t>
+  </si>
+  <si>
+    <t>→ TB5:9</t>
+  </si>
+  <si>
+    <t>PS1:V-→</t>
+  </si>
+  <si>
+    <t>0V_LOGIC</t>
+  </si>
+  <si>
+    <t>V-</t>
+  </si>
+  <si>
+    <t>🟦⬜️ Blue/White</t>
+  </si>
+  <si>
+    <t>→ S1:21</t>
+  </si>
+  <si>
+    <t>TB5:8→</t>
+  </si>
+  <si>
+    <t>→ S1:13</t>
+  </si>
+  <si>
+    <t>TB5:6→</t>
+  </si>
+  <si>
+    <t>→ J7:7</t>
+  </si>
+  <si>
+    <t>TB5:4→</t>
+  </si>
+  <si>
+    <t>→ J7:3</t>
+  </si>
+  <si>
+    <t>TB5:2→</t>
+  </si>
+  <si>
+    <t>→ PL1:X1</t>
+  </si>
+  <si>
+    <t>TB5:18→</t>
+  </si>
+  <si>
+    <t>ESTOP_INDICATOR</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>→ J7:6</t>
+  </si>
+  <si>
+    <t>TB5:16→</t>
+  </si>
+  <si>
+    <t>→ J7:2</t>
+  </si>
+  <si>
+    <t>TB5:14→</t>
+  </si>
+  <si>
+    <t>→ PL4:X2</t>
+  </si>
+  <si>
+    <t>TB5:12→</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>→ A2</t>
+  </si>
+  <si>
+    <t>TB5:10→</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>→ TB8:1</t>
+  </si>
+  <si>
+    <t>S1:22→</t>
+  </si>
+  <si>
+    <t>ESTOP_LOOP</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>→ J7:8</t>
+  </si>
+  <si>
+    <t>TB8:2→</t>
+  </si>
+  <si>
+    <t>→ PL1:X2</t>
+  </si>
+  <si>
+    <t>S1:14→</t>
+  </si>
+  <si>
+    <t>→ TB9:1</t>
+  </si>
+  <si>
+    <t>J7:5→</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>→ J7:4</t>
+  </si>
+  <si>
+    <t>TB9:2→</t>
+  </si>
+  <si>
+    <t>→ TB10:1</t>
+  </si>
+  <si>
+    <t>J7:1→</t>
+  </si>
+  <si>
+    <t>→ PB2:21</t>
+  </si>
+  <si>
+    <t>TB10:2→</t>
+  </si>
+  <si>
+    <t>→ TB6:1</t>
+  </si>
+  <si>
+    <t>PB2:22→</t>
+  </si>
+  <si>
+    <t>→ PB1:13</t>
+  </si>
+  <si>
+    <t>TB6:2→</t>
+  </si>
+  <si>
+    <t>→ K1:13</t>
+  </si>
+  <si>
+    <t>TB6:4→</t>
+  </si>
+  <si>
+    <t>→ TB7:1</t>
+  </si>
+  <si>
+    <t>PB1:14→</t>
+  </si>
+  <si>
+    <t>MACHINE_ENABLE</t>
+  </si>
+  <si>
+    <t>→ K1:14</t>
+  </si>
+  <si>
+    <t>TB7:4→</t>
+  </si>
+  <si>
+    <t>→ K1:A1</t>
+  </si>
+  <si>
+    <t>TB7:6→</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>→ PL4:X1</t>
+  </si>
+  <si>
+    <t>TB7:2→</t>
+  </si>
+  <si>
+    <t>→ P12:8</t>
+  </si>
+  <si>
+    <t>P7:8→</t>
+  </si>
+  <si>
+    <t>→ P12:7</t>
+  </si>
+  <si>
+    <t>P7:7→</t>
+  </si>
+  <si>
+    <t>→ P12:6</t>
+  </si>
+  <si>
+    <t>P7:6→</t>
+  </si>
+  <si>
+    <t>→ P12:5</t>
+  </si>
+  <si>
+    <t>P7:5→</t>
+  </si>
+  <si>
+    <t>→ S2:21</t>
+  </si>
+  <si>
+    <t>J12:8→</t>
+  </si>
+  <si>
+    <t>→ S2:13</t>
+  </si>
+  <si>
+    <t>J12:7→</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>→ J12:6</t>
+  </si>
+  <si>
+    <t>PL2:X2→</t>
+  </si>
+  <si>
+    <t>→ J12:5</t>
+  </si>
+  <si>
+    <t>S2:22→</t>
+  </si>
+  <si>
+    <t>→ PL2:X1</t>
+  </si>
+  <si>
+    <t>S2:14→</t>
+  </si>
+  <si>
+    <t>→ P12:4</t>
+  </si>
+  <si>
+    <t>P7:4→</t>
+  </si>
+  <si>
+    <t>→ P12:3</t>
+  </si>
+  <si>
+    <t>P7:3→</t>
+  </si>
+  <si>
+    <t>→ P12:2</t>
+  </si>
+  <si>
+    <t>P7:2→</t>
+  </si>
+  <si>
+    <t>→ P12:1</t>
+  </si>
+  <si>
+    <t>P7:1→</t>
+  </si>
+  <si>
+    <t>→ J13:4</t>
+  </si>
+  <si>
+    <t>P12:4→</t>
+  </si>
+  <si>
+    <t>→ J13:3</t>
+  </si>
+  <si>
+    <t>P12:3→</t>
+  </si>
+  <si>
+    <t>→ J13:2</t>
+  </si>
+  <si>
+    <t>P12:2→</t>
+  </si>
+  <si>
+    <t>→ J13:1</t>
+  </si>
+  <si>
+    <t>P12:1→</t>
+  </si>
+  <si>
+    <t>→ P17:4</t>
+  </si>
+  <si>
+    <t>P13:4→</t>
+  </si>
+  <si>
+    <t>Flex optional</t>
+  </si>
+  <si>
+    <t>→ P17:3</t>
+  </si>
+  <si>
+    <t>P13:3→</t>
+  </si>
+  <si>
+    <t>→ P17:2</t>
+  </si>
+  <si>
+    <t>P13:2→</t>
+  </si>
+  <si>
+    <t>→ P17:1</t>
+  </si>
+  <si>
+    <t>P13:1→</t>
+  </si>
+  <si>
+    <t>→ S3:21</t>
+  </si>
+  <si>
+    <t>J17:4→</t>
+  </si>
+  <si>
+    <t>→ S3:13</t>
+  </si>
+  <si>
+    <t>J17:3→</t>
+  </si>
+  <si>
+    <t>→ J17:2</t>
+  </si>
+  <si>
+    <t>PL3:X2→</t>
+  </si>
+  <si>
+    <t>→ J17:1</t>
+  </si>
+  <si>
+    <t>S3:22→</t>
+  </si>
+  <si>
+    <t>→ PL3:X1</t>
+  </si>
+  <si>
+    <t>S3:14→</t>
+  </si>
+  <si>
+    <t>→ TB11:1</t>
+  </si>
+  <si>
+    <t>PS4:V+1→</t>
+  </si>
+  <si>
+    <t>24V Power</t>
+  </si>
+  <si>
+    <t>V+1</t>
+  </si>
+  <si>
+    <t>→ TB11:13</t>
+  </si>
+  <si>
+    <t>PS4:V-1→</t>
+  </si>
+  <si>
+    <t>V-1</t>
+  </si>
+  <si>
+    <t>→ MESA:TB3:22</t>
+  </si>
+  <si>
+    <t>TB11:2→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB3:24</t>
+  </si>
+  <si>
+    <t>TB11:14→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB1:5</t>
+  </si>
+  <si>
+    <t>TB11:4→</t>
+  </si>
+  <si>
+    <t>→ MESA:TB1:8</t>
+  </si>
+  <si>
+    <t>TB11:16→</t>
+  </si>
+  <si>
+    <t>→ FANS1:1</t>
+  </si>
+  <si>
+    <t>TB11:6→</t>
+  </si>
+  <si>
+    <t>FAN_PWR</t>
+  </si>
+  <si>
+    <t>FANS1</t>
+  </si>
+  <si>
+    <t>→ FANS1:2</t>
+  </si>
+  <si>
+    <t>TB11:18→</t>
+  </si>
+  <si>
+    <t>→ J2:1</t>
+  </si>
+  <si>
+    <t>TB11:8→</t>
+  </si>
+  <si>
+    <t>→ J2:2</t>
+  </si>
+  <si>
+    <t>TB11:20→</t>
+  </si>
+  <si>
+    <t>→ TI1:V+</t>
+  </si>
+  <si>
+    <t>TB11:10→</t>
+  </si>
+  <si>
+    <t>→ TI1:V-</t>
+  </si>
+  <si>
+    <t>TB11:22→</t>
+  </si>
+  <si>
+    <t>→ J4:2</t>
+  </si>
+  <si>
+    <t>MESA:TB6:17→</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>→ J4:1</t>
+  </si>
+  <si>
+    <t>TB11:24→</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>→ TI1:SIG</t>
+  </si>
+  <si>
+    <t>MESA:TB6:1→</t>
+  </si>
+  <si>
+    <t>TI1_VSENSE</t>
+  </si>
+  <si>
+    <t>SIG</t>
+  </si>
+  <si>
+    <t>→ P10:2</t>
+  </si>
+  <si>
+    <t>P2:2→</t>
+  </si>
+  <si>
+    <t>→ P10:1</t>
+  </si>
+  <si>
+    <t>P2:1→</t>
+  </si>
+  <si>
+    <t>→ TB51:1</t>
+  </si>
+  <si>
+    <t>J10:2→</t>
+  </si>
+  <si>
+    <t>→ TB52:1</t>
+  </si>
+  <si>
+    <t>J10:1→</t>
+  </si>
+  <si>
+    <t>→ J21:1</t>
+  </si>
+  <si>
+    <t>TB51:2→</t>
+  </si>
+  <si>
+    <t>→ J21:2</t>
+  </si>
+  <si>
+    <t>TB52:2→</t>
+  </si>
+  <si>
+    <t>→ LS1</t>
+  </si>
+  <si>
+    <t>TB51:3→</t>
+  </si>
+  <si>
+    <t>LIMIT_PWR</t>
+  </si>
+  <si>
+    <t>TB52:3→</t>
+  </si>
+  <si>
+    <t>LIMIT_GND</t>
+  </si>
+  <si>
+    <t>→ LS2</t>
+  </si>
+  <si>
+    <t>TB51:4→</t>
+  </si>
+  <si>
+    <t>TB52:4→</t>
+  </si>
+  <si>
+    <t>→ HS1</t>
+  </si>
+  <si>
+    <t>TB51:5→</t>
+  </si>
+  <si>
+    <t>TB52:5→</t>
+  </si>
+  <si>
+    <t>→ HS2</t>
+  </si>
+  <si>
+    <t>TB51:6→</t>
+  </si>
+  <si>
+    <t>TB52:6→</t>
+  </si>
+  <si>
+    <t>→ TP1</t>
+  </si>
+  <si>
+    <t>TB51:7→</t>
+  </si>
+  <si>
+    <t>PROBE_PWR</t>
+  </si>
+  <si>
+    <t>→ P20:2</t>
+  </si>
+  <si>
+    <t>P21:2→</t>
+  </si>
+  <si>
+    <t>→ P20:1</t>
+  </si>
+  <si>
+    <t>P21:1→</t>
+  </si>
+  <si>
+    <t>→ TB53:1</t>
+  </si>
+  <si>
+    <t>J20:2→</t>
+  </si>
+  <si>
+    <t>→ TB54:1</t>
+  </si>
+  <si>
+    <t>J20:1→</t>
+  </si>
+  <si>
+    <t>→ J25:1</t>
+  </si>
+  <si>
+    <t>TB53:2→</t>
+  </si>
+  <si>
+    <t>→ J25:2</t>
+  </si>
+  <si>
+    <t>TB54:2→</t>
+  </si>
+  <si>
+    <t>→ LS3</t>
+  </si>
+  <si>
+    <t>TB53:3→</t>
+  </si>
+  <si>
+    <t>TB54:3→</t>
+  </si>
+  <si>
+    <t>→ LS4</t>
+  </si>
+  <si>
+    <t>TB53:4→</t>
+  </si>
+  <si>
+    <t>TB54:4→</t>
+  </si>
+  <si>
+    <t>→ HS3</t>
+  </si>
+  <si>
+    <t>TB53:5→</t>
+  </si>
+  <si>
+    <t>TB54:5→</t>
+  </si>
+  <si>
+    <t>→ P29:2</t>
+  </si>
+  <si>
+    <t>P25:2→</t>
+  </si>
+  <si>
+    <t>→ P29:1</t>
+  </si>
+  <si>
+    <t>P25:1→</t>
+  </si>
+  <si>
+    <t>→ TB57:1</t>
+  </si>
+  <si>
+    <t>J29:2→</t>
+  </si>
+  <si>
+    <t>→ TB58:1</t>
+  </si>
+  <si>
+    <t>J29:1→</t>
+  </si>
+  <si>
+    <t>→ LS5</t>
+  </si>
+  <si>
+    <t>TB57:2→</t>
+  </si>
+  <si>
+    <t>TB58:2→</t>
+  </si>
+  <si>
+    <t>→ LS6</t>
+  </si>
+  <si>
+    <t>TB57:3→</t>
+  </si>
+  <si>
+    <t>TB58:3→</t>
+  </si>
+  <si>
+    <t>→ HS4</t>
+  </si>
+  <si>
+    <t>TB57:4→</t>
+  </si>
+  <si>
+    <t>TB58:4→</t>
+  </si>
+  <si>
+    <t>→ K2</t>
+  </si>
+  <si>
+    <t>P4:1→</t>
+  </si>
+  <si>
+    <t>Need suitable relay</t>
+  </si>
+  <si>
+    <t>P4:2→</t>
+  </si>
+  <si>
+    <t>→ J8:2</t>
+  </si>
+  <si>
+    <t>PS5:V+1→</t>
+  </si>
+  <si>
+    <t>48V Power</t>
+  </si>
+  <si>
+    <t>48V_LOGIC</t>
+  </si>
+  <si>
+    <t>🟧 Orange</t>
+  </si>
+  <si>
+    <t>→ J8:1</t>
+  </si>
+  <si>
+    <t>PS5:V-1→</t>
+  </si>
+  <si>
+    <t>🟫 Brown</t>
+  </si>
+  <si>
+    <t>→ J8:4</t>
+  </si>
+  <si>
+    <t>PS6:V+1→</t>
+  </si>
+  <si>
+    <t>→ J8:3</t>
+  </si>
+  <si>
+    <t>PS6:V-1→</t>
+  </si>
+  <si>
+    <t>→ SD2:DC+</t>
+  </si>
+  <si>
+    <t>PS6:V+2→</t>
+  </si>
+  <si>
+    <t>V+2</t>
+  </si>
+  <si>
+    <t>DC+</t>
+  </si>
+  <si>
+    <t>→ SD2:DC-</t>
+  </si>
+  <si>
+    <t>PS6:V-2→</t>
+  </si>
+  <si>
+    <t>V-2</t>
+  </si>
+  <si>
+    <t>DC-</t>
+  </si>
+  <si>
+    <t>PS6:V+3→</t>
+  </si>
+  <si>
+    <t>V+3</t>
+  </si>
+  <si>
+    <t>PS6:V-3→</t>
+  </si>
+  <si>
+    <t>V-3</t>
+  </si>
+  <si>
+    <t>→ P18:2</t>
+  </si>
+  <si>
+    <t>P8:2→</t>
+  </si>
+  <si>
+    <t>→ P18:1</t>
+  </si>
+  <si>
+    <t>P8:1→</t>
+  </si>
+  <si>
+    <t>→ P18:4</t>
+  </si>
+  <si>
+    <t>P8:4→</t>
+  </si>
+  <si>
+    <t>→ P18:3</t>
+  </si>
+  <si>
+    <t>P8:3→</t>
+  </si>
+  <si>
+    <t>→ J15:1</t>
+  </si>
+  <si>
+    <t>J18:2→</t>
+  </si>
+  <si>
+    <t>→ J15:2</t>
+  </si>
+  <si>
+    <t>J18:1→</t>
+  </si>
+  <si>
+    <t>→ J15:4</t>
+  </si>
+  <si>
+    <t>J18:4→</t>
+  </si>
+  <si>
+    <t>→ J15:3</t>
+  </si>
+  <si>
+    <t>J18:3→</t>
+  </si>
+  <si>
+    <t>→ P20:4</t>
+  </si>
+  <si>
+    <t>P15:2→</t>
+  </si>
+  <si>
+    <t>→ P20:3</t>
+  </si>
+  <si>
+    <t>P15:1→</t>
+  </si>
+  <si>
+    <t>→ P29:4</t>
+  </si>
+  <si>
+    <t>P15:4→</t>
+  </si>
+  <si>
+    <t>→ P29:3</t>
+  </si>
+  <si>
+    <t>P15:3→</t>
+  </si>
+  <si>
+    <t>→ TB55:1</t>
+  </si>
+  <si>
+    <t>J20:4→</t>
+  </si>
+  <si>
+    <t>→ TB56:1</t>
+  </si>
+  <si>
+    <t>J20:3→</t>
+  </si>
+  <si>
+    <t>→ IM1:VDC+</t>
+  </si>
+  <si>
+    <t>TB55:2→</t>
+  </si>
+  <si>
+    <t>STEP_IO_PWR</t>
+  </si>
+  <si>
+    <t>VDC+</t>
+  </si>
+  <si>
+    <t>→ IM1:GND</t>
+  </si>
+  <si>
+    <t>TB56:2→</t>
+  </si>
+  <si>
+    <t>STEP_IO_GND</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>→ IM2:VDC+</t>
+  </si>
+  <si>
+    <t>TB55:3→</t>
+  </si>
+  <si>
+    <t>→ IM2:GND</t>
+  </si>
+  <si>
+    <t>TB56:4→</t>
+  </si>
+  <si>
+    <t>→ IM3:VDC+</t>
+  </si>
+  <si>
+    <t>J29:4→</t>
+  </si>
+  <si>
+    <t>→ IM3:GND</t>
+  </si>
+  <si>
+    <t>J29:3→</t>
+  </si>
+  <si>
+    <t>→ J5:2</t>
+  </si>
+  <si>
+    <t>MESA:TB3:18→</t>
+  </si>
+  <si>
+    <t>Control Signals</t>
+  </si>
+  <si>
+    <t>SPINDLE_RS+</t>
+  </si>
+  <si>
+    <t>🧵 Aqua</t>
+  </si>
+  <si>
+    <t>→ J5:1</t>
+  </si>
+  <si>
+    <t>MESA:TB3:16→</t>
+  </si>
+  <si>
+    <t>SPINDLE_RS-</t>
+  </si>
+  <si>
+    <t>🩵 Teal</t>
+  </si>
+  <si>
+    <t>→ J1:1</t>
+  </si>
+  <si>
+    <t>MESA:TB2:2→</t>
+  </si>
+  <si>
+    <t>Y1_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:2</t>
+  </si>
+  <si>
+    <t>MESA:TB2:3→</t>
+  </si>
+  <si>
+    <t>Y1_STEP+</t>
+  </si>
+  <si>
+    <t>→ J1:3</t>
+  </si>
+  <si>
+    <t>MESA:TB2:4→</t>
+  </si>
+  <si>
+    <t>Y1_DIR-</t>
+  </si>
+  <si>
+    <t>🟩⬜️ Green/White</t>
+  </si>
+  <si>
+    <t>→ J1:4</t>
+  </si>
+  <si>
+    <t>MESA:TB2:5→</t>
+  </si>
+  <si>
+    <t>Y1_DIR+</t>
+  </si>
+  <si>
+    <t>🟩 Green</t>
+  </si>
+  <si>
+    <t>→ J1:5</t>
+  </si>
+  <si>
+    <t>MESA:TB2:8→</t>
+  </si>
+  <si>
+    <t>Y2_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:6</t>
+  </si>
+  <si>
+    <t>MESA:TB2:9→</t>
+  </si>
+  <si>
+    <t>Y2_STEP+</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>→ J1:7</t>
+  </si>
+  <si>
+    <t>MESA:TB2:10→</t>
+  </si>
+  <si>
+    <t>Y2_DIR-</t>
+  </si>
+  <si>
+    <t>→ J1:8</t>
+  </si>
+  <si>
+    <t>MESA:TB2:11→</t>
+  </si>
+  <si>
+    <t>Y2_DIR+</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>→ J1:9</t>
+  </si>
+  <si>
+    <t>MESA:TB2:14→</t>
+  </si>
+  <si>
+    <t>X_STEP-</t>
+  </si>
+  <si>
+    <t>→ J1:10</t>
+  </si>
+  <si>
+    <t>MESA:TB2:15→</t>
+  </si>
+  <si>
+    <t>X_STEP+</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>→ J1:11</t>
+  </si>
+  <si>
+    <t>MESA:TB2:16→</t>
+  </si>
+  <si>
+    <t>X_DIR-</t>
+  </si>
+  <si>
+    <t>→ J1:12</t>
+  </si>
+  <si>
+    <t>MESA:TB2:17→</t>
+  </si>
+  <si>
+    <t>X_DIR+</t>
+  </si>
+  <si>
+    <t>→ SD1:PUL-</t>
+  </si>
+  <si>
+    <t>MESA:TB2:20→</t>
+  </si>
+  <si>
+    <t>Z_STEP-</t>
+  </si>
+  <si>
+    <t>PUL-</t>
+  </si>
+  <si>
+    <t>→ SD1:PUL+</t>
+  </si>
+  <si>
+    <t>MESA:TB2:21→</t>
+  </si>
+  <si>
+    <t>Z_STEP+</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>PUL+</t>
+  </si>
+  <si>
+    <t>→ SD1:DIR-</t>
+  </si>
+  <si>
+    <t>MESA:TB2:22→</t>
+  </si>
+  <si>
+    <t>Z_DIR-</t>
+  </si>
+  <si>
+    <t>DIR-</t>
+  </si>
+  <si>
+    <t>→ SD1:DIR+</t>
+  </si>
+  <si>
+    <t>MESA:TB2:23→</t>
+  </si>
+  <si>
+    <t>Z_DIR+</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>DIR+</t>
+  </si>
+  <si>
+    <t>→ J3:8</t>
+  </si>
+  <si>
+    <t>SD1:A+→</t>
+  </si>
+  <si>
+    <t>Z_A+</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Double check colours/order</t>
+  </si>
+  <si>
+    <t>→ J3:7</t>
+  </si>
+  <si>
+    <t>SD1:A-→</t>
+  </si>
+  <si>
+    <t>Z_A-</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>→ J3:6</t>
+  </si>
+  <si>
+    <t>SD1:B+→</t>
+  </si>
+  <si>
+    <t>Z_B+</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>→ J3:5</t>
+  </si>
+  <si>
+    <t>SD1:B-→</t>
+  </si>
+  <si>
+    <t>Z_B-</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>→ J3:4</t>
+  </si>
+  <si>
+    <t>SD2:A+→</t>
+  </si>
+  <si>
+    <t>DUST_A+</t>
+  </si>
+  <si>
+    <t>→ J3:3</t>
+  </si>
+  <si>
+    <t>SD2:A-→</t>
+  </si>
+  <si>
+    <t>DUST_A-</t>
+  </si>
+  <si>
+    <t>→ J3:2</t>
+  </si>
+  <si>
+    <t>SD2:B+→</t>
+  </si>
+  <si>
+    <t>DUST_B+</t>
+  </si>
+  <si>
+    <t>→ J3:1</t>
+  </si>
+  <si>
+    <t>SD2:B-→</t>
+  </si>
+  <si>
+    <t>DUST_B-</t>
+  </si>
+  <si>
+    <t>→ J1:13</t>
+  </si>
+  <si>
+    <t>MESA:TB6:5→</t>
+  </si>
+  <si>
+    <t>Y_MIN</t>
+  </si>
+  <si>
+    <t>🩶 Grey</t>
+  </si>
+  <si>
+    <t>→ J1:14</t>
+  </si>
+  <si>
+    <t>MESA:TB6:6→</t>
+  </si>
+  <si>
+    <t>Y_MAX</t>
+  </si>
+  <si>
+    <t>→ J1:15</t>
+  </si>
+  <si>
+    <t>MESA:TB6:7→</t>
+  </si>
+  <si>
+    <t>Y1_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:16</t>
+  </si>
+  <si>
+    <t>MESA:TB6:8→</t>
+  </si>
+  <si>
+    <t>Y2_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:17</t>
+  </si>
+  <si>
+    <t>MESA:TB6:9→</t>
+  </si>
+  <si>
+    <t>X_MIN</t>
+  </si>
+  <si>
+    <t>→ J1:18</t>
+  </si>
+  <si>
+    <t>MESA:TB6:10→</t>
+  </si>
+  <si>
+    <t>X_MAX</t>
+  </si>
+  <si>
+    <t>→ J1:19</t>
+  </si>
+  <si>
+    <t>MESA:TB6:11→</t>
+  </si>
+  <si>
+    <t>X_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:20</t>
+  </si>
+  <si>
+    <t>MESA:TB6:12→</t>
+  </si>
+  <si>
+    <t>Z_MIN</t>
+  </si>
+  <si>
+    <t>→ J1:21</t>
+  </si>
+  <si>
+    <t>MESA:TB6:13→</t>
+  </si>
+  <si>
+    <t>Z_MAX</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>→ J1:22</t>
+  </si>
+  <si>
+    <t>MESA:TB6:14→</t>
+  </si>
+  <si>
+    <t>Z_HOME</t>
+  </si>
+  <si>
+    <t>→ J1:23</t>
+  </si>
+  <si>
+    <t>MESA:TB6:15→</t>
+  </si>
+  <si>
+    <t>PROBE_IN</t>
+  </si>
+  <si>
+    <t>⬜️ White</t>
+  </si>
+  <si>
+    <t>→ FANS1:PWM</t>
+  </si>
+  <si>
+    <t>MESA:TB6:18→</t>
+  </si>
+  <si>
+    <t>FAN_PWM</t>
+  </si>
+  <si>
+    <t>PWM</t>
+  </si>
+  <si>
+    <t>→ J39:USB1</t>
+  </si>
+  <si>
+    <t>CPU1:USB1→</t>
+  </si>
+  <si>
+    <t>USB_HID</t>
+  </si>
+  <si>
+    <t>USB1</t>
+  </si>
+  <si>
+    <t>➖ not used</t>
+  </si>
+  <si>
+    <t>→ J38:USB1</t>
+  </si>
+  <si>
+    <t>CPU1:USB2→</t>
+  </si>
+  <si>
+    <t>USB_USER</t>
+  </si>
+  <si>
+    <t>USB2</t>
+  </si>
+  <si>
+    <t>Extend to monitor zone</t>
+  </si>
+  <si>
+    <t>→ J37:HDMI</t>
+  </si>
+  <si>
+    <t>CPU1:DP→</t>
+  </si>
+  <si>
+    <t>MONITOR</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>Add in dp/hdmi adapter</t>
+  </si>
+  <si>
+    <t>→ RF1:1</t>
+  </si>
+  <si>
+    <t>CPU1:RF→</t>
+  </si>
+  <si>
+    <t>WIFI_EXT</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>→ MESA:ETH</t>
+  </si>
+  <si>
+    <t>CPU1:ETH→</t>
+  </si>
+  <si>
+    <t>ETH_MESA</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>→ P11:8</t>
+  </si>
+  <si>
+    <t>P3:8→</t>
+  </si>
+  <si>
+    <t>→ P11:7</t>
+  </si>
+  <si>
+    <t>P3:7→</t>
+  </si>
+  <si>
+    <t>→ P11:6</t>
+  </si>
+  <si>
+    <t>P3:6→</t>
+  </si>
+  <si>
+    <t>→ P11:5</t>
+  </si>
+  <si>
+    <t>P3:5→</t>
+  </si>
+  <si>
+    <t>→ J18:1</t>
+  </si>
+  <si>
+    <t>J11:8→</t>
+  </si>
+  <si>
+    <t>→ J18:2</t>
+  </si>
+  <si>
+    <t>J11:7→</t>
+  </si>
+  <si>
+    <t>→ J18:3</t>
+  </si>
+  <si>
+    <t>J11:6→</t>
+  </si>
+  <si>
+    <t>→ J18:4</t>
+  </si>
+  <si>
+    <t>J11:5→</t>
+  </si>
+  <si>
+    <t>→ P30:8</t>
+  </si>
+  <si>
+    <t>P16:8→</t>
+  </si>
+  <si>
+    <t>→ P30:7</t>
+  </si>
+  <si>
+    <t>P16:7→</t>
+  </si>
+  <si>
+    <t>→ P30:6</t>
+  </si>
+  <si>
+    <t>P16:6→</t>
+  </si>
+  <si>
+    <t>→ P30:5</t>
+  </si>
+  <si>
+    <t>P16:5→</t>
+  </si>
+  <si>
+    <t>→ P11:4</t>
+  </si>
+  <si>
+    <t>P3:4→</t>
+  </si>
+  <si>
+    <t>→ P11:3</t>
+  </si>
+  <si>
+    <t>P3:3→</t>
+  </si>
+  <si>
+    <t>→ P11:2</t>
+  </si>
+  <si>
+    <t>P3:2→</t>
+  </si>
+  <si>
+    <t>→ P11:1</t>
+  </si>
+  <si>
+    <t>P3:1→</t>
+  </si>
+  <si>
+    <t>→ J16:4</t>
+  </si>
+  <si>
+    <t>J11:4→</t>
+  </si>
+  <si>
+    <t>→ J16:3</t>
+  </si>
+  <si>
+    <t>J11:3→</t>
+  </si>
+  <si>
+    <t>→ J16:2</t>
+  </si>
+  <si>
+    <t>J11:2→</t>
+  </si>
+  <si>
+    <t>→ J16:1</t>
+  </si>
+  <si>
+    <t>J11:1→</t>
+  </si>
+  <si>
+    <t>→ SM1</t>
+  </si>
+  <si>
+    <t>J30:8→</t>
+  </si>
+  <si>
+    <t>J30:7→</t>
+  </si>
+  <si>
+    <t>J30:6→</t>
+  </si>
+  <si>
+    <t>J30:5→</t>
+  </si>
+  <si>
+    <t>→ M1:1</t>
+  </si>
+  <si>
+    <t>VFD1:U→</t>
+  </si>
+  <si>
+    <t>SPINDLE_U</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>SOLDER</t>
+  </si>
+  <si>
+    <t>→ M1:2</t>
+  </si>
+  <si>
+    <t>VFD1:V→</t>
+  </si>
+  <si>
+    <t>SPINDLE_V</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>→ M1:3</t>
+  </si>
+  <si>
+    <t>VFD1:W→</t>
+  </si>
+  <si>
+    <t>SPINDLE_W</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>→ P30:4</t>
+  </si>
+  <si>
+    <t>P16:4→</t>
+  </si>
+  <si>
+    <t>→ P30:3</t>
+  </si>
+  <si>
+    <t>P16:3→</t>
+  </si>
+  <si>
+    <t>→ P30:2</t>
+  </si>
+  <si>
+    <t>P16:2→</t>
+  </si>
+  <si>
+    <t>→ P30:1</t>
+  </si>
+  <si>
+    <t>P16:1→</t>
+  </si>
+  <si>
+    <t>→ P9:1</t>
+  </si>
+  <si>
+    <t>P1:1→</t>
+  </si>
+  <si>
+    <t>→ P9:2</t>
+  </si>
+  <si>
+    <t>P1:2→</t>
+  </si>
+  <si>
+    <t>→ P9:3</t>
+  </si>
+  <si>
+    <t>P1:3→</t>
+  </si>
+  <si>
+    <t>→ P9:4</t>
+  </si>
+  <si>
+    <t>P1:4→</t>
+  </si>
+  <si>
+    <t>→ P9:5</t>
+  </si>
+  <si>
+    <t>P1:5→</t>
+  </si>
+  <si>
+    <t>→ P9:6</t>
+  </si>
+  <si>
+    <t>P1:6→</t>
+  </si>
+  <si>
+    <t>→ P9:7</t>
+  </si>
+  <si>
+    <t>P1:7→</t>
+  </si>
+  <si>
+    <t>→ P9:8</t>
+  </si>
+  <si>
+    <t>P1:8→</t>
+  </si>
+  <si>
+    <t>→ P9:9</t>
+  </si>
+  <si>
+    <t>P1:9→</t>
+  </si>
+  <si>
+    <t>→ P9:10</t>
+  </si>
+  <si>
+    <t>P1:10→</t>
+  </si>
+  <si>
+    <t>→ P9:11</t>
+  </si>
+  <si>
+    <t>P1:11→</t>
+  </si>
+  <si>
+    <t>→ P9:12</t>
+  </si>
+  <si>
+    <t>P1:12→</t>
+  </si>
+  <si>
+    <t>→ J14:1</t>
+  </si>
+  <si>
+    <t>J9:1→</t>
+  </si>
+  <si>
+    <t>→ J14:2</t>
+  </si>
+  <si>
+    <t>J9:2→</t>
+  </si>
+  <si>
+    <t>→ J14:3</t>
+  </si>
+  <si>
+    <t>J9:3→</t>
+  </si>
+  <si>
+    <t>→ J14:4</t>
+  </si>
+  <si>
+    <t>J9:4→</t>
+  </si>
+  <si>
+    <t>→ J14:5</t>
+  </si>
+  <si>
+    <t>J9:5→</t>
+  </si>
+  <si>
+    <t>→ J14:6</t>
+  </si>
+  <si>
+    <t>J9:6→</t>
+  </si>
+  <si>
+    <t>→ J14:7</t>
+  </si>
+  <si>
+    <t>J9:7→</t>
+  </si>
+  <si>
+    <t>→ J14:8</t>
+  </si>
+  <si>
+    <t>J9:8→</t>
+  </si>
+  <si>
+    <t>→ J14:9</t>
+  </si>
+  <si>
+    <t>J9:9→</t>
+  </si>
+  <si>
+    <t>→ J14:10</t>
+  </si>
+  <si>
+    <t>J9:10→</t>
+  </si>
+  <si>
+    <t>→ J14:11</t>
+  </si>
+  <si>
+    <t>J9:11→</t>
+  </si>
+  <si>
+    <t>→ J14:12</t>
+  </si>
+  <si>
+    <t>J9:12→</t>
+  </si>
+  <si>
+    <t>→ P19:1</t>
+  </si>
+  <si>
+    <t>P14:1→</t>
+  </si>
+  <si>
+    <t>→ P19:2</t>
+  </si>
+  <si>
+    <t>P14:2→</t>
+  </si>
+  <si>
+    <t>→ P19:3</t>
+  </si>
+  <si>
+    <t>P14:3→</t>
+  </si>
+  <si>
+    <t>→ P19:4</t>
+  </si>
+  <si>
+    <t>P14:4→</t>
+  </si>
+  <si>
+    <t>→ P19:5</t>
+  </si>
+  <si>
+    <t>P14:5→</t>
+  </si>
+  <si>
+    <t>→ P19:6</t>
+  </si>
+  <si>
+    <t>P14:6→</t>
+  </si>
+  <si>
+    <t>→ P19:7</t>
+  </si>
+  <si>
+    <t>P14:7→</t>
+  </si>
+  <si>
+    <t>→ P19:8</t>
+  </si>
+  <si>
+    <t>P14:8→</t>
+  </si>
+  <si>
+    <t>→ P19:9</t>
+  </si>
+  <si>
+    <t>P14:9→</t>
+  </si>
+  <si>
+    <t>→ P19:10</t>
+  </si>
+  <si>
+    <t>P14:10→</t>
+  </si>
+  <si>
+    <t>→ P19:11</t>
+  </si>
+  <si>
+    <t>P14:11→</t>
+  </si>
+  <si>
+    <t>→ P19:12</t>
+  </si>
+  <si>
+    <t>P14:12→</t>
+  </si>
+  <si>
+    <t>→ IM1:PUL-</t>
+  </si>
+  <si>
+    <t>J19:1→</t>
+  </si>
+  <si>
+    <t>→ IM1:PUL+</t>
+  </si>
+  <si>
+    <t>J19:2→</t>
+  </si>
+  <si>
+    <t>→ IM1:DIR-</t>
+  </si>
+  <si>
+    <t>J19:3→</t>
+  </si>
+  <si>
+    <t>→ IM1:DIR+</t>
+  </si>
+  <si>
+    <t>J19:4→</t>
+  </si>
+  <si>
+    <t>→ IM2:PUL-</t>
+  </si>
+  <si>
+    <t>J19:5→</t>
+  </si>
+  <si>
+    <t>→ IM2:PUL+</t>
+  </si>
+  <si>
+    <t>J19:6→</t>
+  </si>
+  <si>
+    <t>→ IM2:DIR-</t>
+  </si>
+  <si>
+    <t>J19:7→</t>
+  </si>
+  <si>
+    <t>→ IM2:DIR+</t>
+  </si>
+  <si>
+    <t>J19:8→</t>
+  </si>
+  <si>
+    <t>→ J24:1</t>
+  </si>
+  <si>
+    <t>J19:9→</t>
+  </si>
+  <si>
+    <t>→ J24:2</t>
+  </si>
+  <si>
+    <t>J19:10→</t>
+  </si>
+  <si>
+    <t>→ J24:3</t>
+  </si>
+  <si>
+    <t>J19:11→</t>
+  </si>
+  <si>
+    <t>→ J24:4</t>
+  </si>
+  <si>
+    <t>J19:12→</t>
+  </si>
+  <si>
+    <t>→ P28:1</t>
+  </si>
+  <si>
+    <t>P24:1→</t>
+  </si>
+  <si>
+    <t>→ P28:2</t>
+  </si>
+  <si>
+    <t>P24:2→</t>
+  </si>
+  <si>
+    <t>→ P28:3</t>
+  </si>
+  <si>
+    <t>P24:3→</t>
+  </si>
+  <si>
+    <t>→ P28:4</t>
+  </si>
+  <si>
+    <t>P24:4→</t>
+  </si>
+  <si>
+    <t>→ IM3:PUL-</t>
+  </si>
+  <si>
+    <t>J28:1→</t>
+  </si>
+  <si>
+    <t>→ IM3:PUL+</t>
+  </si>
+  <si>
+    <t>J28:2→</t>
+  </si>
+  <si>
+    <t>→ IM3:DIR-</t>
+  </si>
+  <si>
+    <t>J28:3→</t>
+  </si>
+  <si>
+    <t>→ IM3:DIR+</t>
+  </si>
+  <si>
+    <t>J28:4→</t>
+  </si>
+  <si>
+    <t>→ P9:13</t>
+  </si>
+  <si>
+    <t>P1:13→</t>
+  </si>
+  <si>
+    <t>→ P9:14</t>
+  </si>
+  <si>
+    <t>P1:14→</t>
+  </si>
+  <si>
+    <t>→ P9:15</t>
+  </si>
+  <si>
+    <t>P1:15→</t>
+  </si>
+  <si>
+    <t>→ P9:16</t>
+  </si>
+  <si>
+    <t>P1:16→</t>
+  </si>
+  <si>
+    <t>→ P9:17</t>
+  </si>
+  <si>
+    <t>P1:17→</t>
+  </si>
+  <si>
+    <t>→ P9:18</t>
+  </si>
+  <si>
+    <t>P1:18→</t>
+  </si>
+  <si>
+    <t>→ P9:19</t>
+  </si>
+  <si>
+    <t>P1:19→</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>→ P9:20</t>
+  </si>
+  <si>
+    <t>P1:20→</t>
+  </si>
+  <si>
+    <t>→ P9:21</t>
+  </si>
+  <si>
+    <t>P1:21→</t>
+  </si>
+  <si>
+    <t>→ P9:22</t>
+  </si>
+  <si>
+    <t>P1:22→</t>
+  </si>
+  <si>
+    <t>→ P9:23</t>
+  </si>
+  <si>
+    <t>P1:23→</t>
+  </si>
+  <si>
+    <t>J9:13→</t>
+  </si>
+  <si>
+    <t>J9:14→</t>
+  </si>
+  <si>
+    <t>J9:15→</t>
+  </si>
+  <si>
+    <t>J9:16→</t>
+  </si>
+  <si>
+    <t>→ J14:17</t>
+  </si>
+  <si>
+    <t>J9:17→</t>
+  </si>
+  <si>
+    <t>→ J14:18</t>
+  </si>
+  <si>
+    <t>J9:18→</t>
+  </si>
+  <si>
+    <t>→ J14:19</t>
+  </si>
+  <si>
+    <t>J9:19→</t>
+  </si>
+  <si>
+    <t>→ J14:20</t>
+  </si>
+  <si>
+    <t>J9:20→</t>
+  </si>
+  <si>
+    <t>→ J14:21</t>
+  </si>
+  <si>
+    <t>J9:21→</t>
+  </si>
+  <si>
+    <t>→ J14:22</t>
+  </si>
+  <si>
+    <t>J9:22→</t>
+  </si>
+  <si>
+    <t>J9:23→</t>
+  </si>
+  <si>
+    <t>→ P19:17</t>
+  </si>
+  <si>
+    <t>P14:17→</t>
+  </si>
+  <si>
+    <t>→ P19:18</t>
+  </si>
+  <si>
+    <t>P14:18→</t>
+  </si>
+  <si>
+    <t>→ P19:19</t>
+  </si>
+  <si>
+    <t>P14:19→</t>
+  </si>
+  <si>
+    <t>→ P19:20</t>
+  </si>
+  <si>
+    <t>P14:20→</t>
+  </si>
+  <si>
+    <t>→ P19:21</t>
+  </si>
+  <si>
+    <t>P14:21→</t>
+  </si>
+  <si>
+    <t>→ P19:22</t>
+  </si>
+  <si>
+    <t>P14:22→</t>
+  </si>
+  <si>
+    <t>J19:17→</t>
+  </si>
+  <si>
+    <t>J19:18→</t>
+  </si>
+  <si>
+    <t>J19:19→</t>
+  </si>
+  <si>
+    <t>→ J24:5</t>
+  </si>
+  <si>
+    <t>J19:20→</t>
+  </si>
+  <si>
+    <t>→ J24:6</t>
+  </si>
+  <si>
+    <t>J19:21→</t>
+  </si>
+  <si>
+    <t>→ J24:7</t>
+  </si>
+  <si>
+    <t>J19:22→</t>
+  </si>
+  <si>
+    <t>→ P28:5</t>
+  </si>
+  <si>
+    <t>P24:5→</t>
+  </si>
+  <si>
+    <t>→ P28:6</t>
+  </si>
+  <si>
+    <t>P24:6→</t>
+  </si>
+  <si>
+    <t>→ P28:7</t>
+  </si>
+  <si>
+    <t>P24:7→</t>
+  </si>
+  <si>
+    <t>→ LS5:5</t>
+  </si>
+  <si>
+    <t>J28:5→</t>
+  </si>
+  <si>
+    <t>→ LS6:6</t>
+  </si>
+  <si>
+    <t>J28:6→</t>
+  </si>
+  <si>
+    <t>→ HS4:7</t>
+  </si>
+  <si>
+    <t>J28:7→</t>
+  </si>
+  <si>
+    <t>→ TB1:1</t>
+  </si>
+  <si>
+    <t>P0:PE→</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>→ TB4:1</t>
+  </si>
+  <si>
+    <t>TB1:2→</t>
+  </si>
+  <si>
+    <t>→ F1:PE</t>
+  </si>
+  <si>
+    <t>TB4:3→</t>
+  </si>
+  <si>
     <t>SPADE</t>
-  </si>
-  <si>
-    <t>→ J35:N</t>
-  </si>
-  <si>
-    <t>TB2:14→</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>→ TB3:1</t>
-  </si>
-  <si>
-    <t>K1:T1→</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>→ TB3:11</t>
-  </si>
-  <si>
-    <t>K1:T2→</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>→ PS5:L</t>
-  </si>
-  <si>
-    <t>TB3:10→</t>
-  </si>
-  <si>
-    <t>→ PS5:N</t>
-  </si>
-  <si>
-    <t>TB3:20→</t>
-  </si>
-  <si>
-    <t>→ PS6:L</t>
-  </si>
-  <si>
-    <t>TB3:8→</t>
-  </si>
-  <si>
-    <t>→ PS6:N</t>
-  </si>
-  <si>
-    <t>TB3:18→</t>
-  </si>
-  <si>
-    <t>→ PS4:L</t>
-  </si>
-  <si>
-    <t>TB3:6→</t>
-  </si>
-  <si>
-    <t>→ PS4:N</t>
-  </si>
-  <si>
-    <t>TB3:16→</t>
-  </si>
-  <si>
-    <t>→ J6:4</t>
-  </si>
-  <si>
-    <t>TB3:4→</t>
-  </si>
-  <si>
-    <t>→ J6:3</t>
-  </si>
-  <si>
-    <t>TB3:14→</t>
-  </si>
-  <si>
-    <t>→ VFD1:R</t>
-  </si>
-  <si>
-    <t>P6:4→</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>→ VFD1:S</t>
-  </si>
-  <si>
-    <t>P6:3→</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>→ J36:L</t>
-  </si>
-  <si>
-    <t>P35:L→</t>
-  </si>
-  <si>
-    <t>→ J36:N</t>
-  </si>
-  <si>
-    <t>P35:N→</t>
-  </si>
-  <si>
-    <t>→ TB5:1</t>
-  </si>
-  <si>
-    <t>PS1:V+→</t>
-  </si>
-  <si>
-    <t>Estop/Power Mgmt</t>
-  </si>
-  <si>
-    <t>24V_LOGIC</t>
-  </si>
-  <si>
-    <t>V+</t>
-  </si>
-  <si>
-    <t>🟦 Blue</t>
-  </si>
-  <si>
-    <t>→ TB5:9</t>
-  </si>
-  <si>
-    <t>PS1:V-→</t>
-  </si>
-  <si>
-    <t>0V_LOGIC</t>
-  </si>
-  <si>
-    <t>V-</t>
-  </si>
-  <si>
-    <t>🟦⬜️ Blue/White</t>
-  </si>
-  <si>
-    <t>→ S1:21</t>
-  </si>
-  <si>
-    <t>TB5:8→</t>
-  </si>
-  <si>
-    <t>→ S1:13</t>
-  </si>
-  <si>
-    <t>TB5:6→</t>
-  </si>
-  <si>
-    <t>→ J7:7</t>
-  </si>
-  <si>
-    <t>TB5:4→</t>
-  </si>
-  <si>
-    <t>→ J7:3</t>
-  </si>
-  <si>
-    <t>TB5:2→</t>
-  </si>
-  <si>
-    <t>→ PL1:X1</t>
-  </si>
-  <si>
-    <t>TB5:18→</t>
-  </si>
-  <si>
-    <t>ESTOP_INDICATOR</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>→ J7:6</t>
-  </si>
-  <si>
-    <t>TB5:16→</t>
-  </si>
-  <si>
-    <t>→ J7:2</t>
-  </si>
-  <si>
-    <t>TB5:14→</t>
-  </si>
-  <si>
-    <t>→ PL4:X2</t>
-  </si>
-  <si>
-    <t>TB5:12→</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>→ A2</t>
-  </si>
-  <si>
-    <t>TB5:10→</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>→ TB8:1</t>
-  </si>
-  <si>
-    <t>S1:22→</t>
-  </si>
-  <si>
-    <t>ESTOP_LOOP</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>→ J7:8</t>
-  </si>
-  <si>
-    <t>TB8:2→</t>
-  </si>
-  <si>
-    <t>→ PL1:X2</t>
-  </si>
-  <si>
-    <t>S1:14→</t>
-  </si>
-  <si>
-    <t>→ TB9:1</t>
-  </si>
-  <si>
-    <t>J7:5→</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>→ J7:4</t>
-  </si>
-  <si>
-    <t>TB9:2→</t>
-  </si>
-  <si>
-    <t>→ TB10:1</t>
-  </si>
-  <si>
-    <t>J7:1→</t>
-  </si>
-  <si>
-    <t>→ PB2:21</t>
-  </si>
-  <si>
-    <t>TB10:2→</t>
-  </si>
-  <si>
-    <t>→ TB6:1</t>
-  </si>
-  <si>
-    <t>PB2:22→</t>
-  </si>
-  <si>
-    <t>→ PB1:13</t>
-  </si>
-  <si>
-    <t>TB6:2→</t>
-  </si>
-  <si>
-    <t>→ K1:13</t>
-  </si>
-  <si>
-    <t>TB6:4→</t>
-  </si>
-  <si>
-    <t>→ TB7:1</t>
-  </si>
-  <si>
-    <t>PB1:14→</t>
-  </si>
-  <si>
-    <t>MACHINE_ENABLE</t>
-  </si>
-  <si>
-    <t>→ K1:14</t>
-  </si>
-  <si>
-    <t>TB7:4→</t>
-  </si>
-  <si>
-    <t>→ K1:A1</t>
-  </si>
-  <si>
-    <t>TB7:6→</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>→ PL4:X1</t>
-  </si>
-  <si>
-    <t>TB7:2→</t>
-  </si>
-  <si>
-    <t>→ P12:8</t>
-  </si>
-  <si>
-    <t>P7:8→</t>
-  </si>
-  <si>
-    <t>→ P12:7</t>
-  </si>
-  <si>
-    <t>P7:7→</t>
-  </si>
-  <si>
-    <t>→ P12:6</t>
-  </si>
-  <si>
-    <t>P7:6→</t>
-  </si>
-  <si>
-    <t>→ P12:5</t>
-  </si>
-  <si>
-    <t>P7:5→</t>
-  </si>
-  <si>
-    <t>→ S2:21</t>
-  </si>
-  <si>
-    <t>J12:8→</t>
-  </si>
-  <si>
-    <t>→ S2:13</t>
-  </si>
-  <si>
-    <t>J12:7→</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>→ J12:6</t>
-  </si>
-  <si>
-    <t>PL2:X2→</t>
-  </si>
-  <si>
-    <t>→ J12:5</t>
-  </si>
-  <si>
-    <t>S2:22→</t>
-  </si>
-  <si>
-    <t>→ PL2:X1</t>
-  </si>
-  <si>
-    <t>S2:14→</t>
-  </si>
-  <si>
-    <t>→ P12:4</t>
-  </si>
-  <si>
-    <t>P7:4→</t>
-  </si>
-  <si>
-    <t>→ P12:3</t>
-  </si>
-  <si>
-    <t>P7:3→</t>
-  </si>
-  <si>
-    <t>→ P12:2</t>
-  </si>
-  <si>
-    <t>P7:2→</t>
-  </si>
-  <si>
-    <t>→ P12:1</t>
-  </si>
-  <si>
-    <t>P7:1→</t>
-  </si>
-  <si>
-    <t>→ J13:4</t>
-  </si>
-  <si>
-    <t>P12:4→</t>
-  </si>
-  <si>
-    <t>→ J13:3</t>
-  </si>
-  <si>
-    <t>P12:3→</t>
-  </si>
-  <si>
-    <t>→ J13:2</t>
-  </si>
-  <si>
-    <t>P12:2→</t>
-  </si>
-  <si>
-    <t>→ J13:1</t>
-  </si>
-  <si>
-    <t>P12:1→</t>
-  </si>
-  <si>
-    <t>→ P17:4</t>
-  </si>
-  <si>
-    <t>P13:4→</t>
-  </si>
-  <si>
-    <t>Flex optional</t>
-  </si>
-  <si>
-    <t>→ P17:3</t>
-  </si>
-  <si>
-    <t>P13:3→</t>
-  </si>
-  <si>
-    <t>→ P17:2</t>
-  </si>
-  <si>
-    <t>P13:2→</t>
-  </si>
-  <si>
-    <t>→ P17:1</t>
-  </si>
-  <si>
-    <t>P13:1→</t>
-  </si>
-  <si>
-    <t>→ S3:21</t>
-  </si>
-  <si>
-    <t>J17:4→</t>
-  </si>
-  <si>
-    <t>→ S3:13</t>
-  </si>
-  <si>
-    <t>J17:3→</t>
-  </si>
-  <si>
-    <t>→ J17:2</t>
-  </si>
-  <si>
-    <t>PL3:X2→</t>
-  </si>
-  <si>
-    <t>→ J17:1</t>
-  </si>
-  <si>
-    <t>S3:22→</t>
-  </si>
-  <si>
-    <t>→ PL3:X1</t>
-  </si>
-  <si>
-    <t>S3:14→</t>
-  </si>
-  <si>
-    <t>→ TB11:1</t>
-  </si>
-  <si>
-    <t>PS4:V+1→</t>
-  </si>
-  <si>
-    <t>24V Power</t>
-  </si>
-  <si>
-    <t>V+1</t>
-  </si>
-  <si>
-    <t>→ TB11:13</t>
-  </si>
-  <si>
-    <t>PS4:V-1→</t>
-  </si>
-  <si>
-    <t>V-1</t>
-  </si>
-  <si>
-    <t>→ MESA:TB3:22</t>
-  </si>
-  <si>
-    <t>TB11:2→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB3:24</t>
-  </si>
-  <si>
-    <t>TB11:14→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB1:5</t>
-  </si>
-  <si>
-    <t>TB11:4→</t>
-  </si>
-  <si>
-    <t>→ MESA:TB1:8</t>
-  </si>
-  <si>
-    <t>TB11:16→</t>
-  </si>
-  <si>
-    <t>→ FANS1:1</t>
-  </si>
-  <si>
-    <t>TB11:6→</t>
-  </si>
-  <si>
-    <t>FAN_PWR</t>
-  </si>
-  <si>
-    <t>FANS1</t>
-  </si>
-  <si>
-    <t>→ FANS1:2</t>
-  </si>
-  <si>
-    <t>TB11:18→</t>
-  </si>
-  <si>
-    <t>→ J2:1</t>
-  </si>
-  <si>
-    <t>TB11:8→</t>
-  </si>
-  <si>
-    <t>→ J2:2</t>
-  </si>
-  <si>
-    <t>TB11:20→</t>
-  </si>
-  <si>
-    <t>→ TI1:V+</t>
-  </si>
-  <si>
-    <t>TB11:10→</t>
-  </si>
-  <si>
-    <t>→ TI1:V-</t>
-  </si>
-  <si>
-    <t>TB11:22→</t>
-  </si>
-  <si>
-    <t>→ J4:2</t>
-  </si>
-  <si>
-    <t>MESA:TB6:17→</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>→ J4:1</t>
-  </si>
-  <si>
-    <t>TB11:24→</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>→ TI1:SIG</t>
-  </si>
-  <si>
-    <t>MESA:TB6:1→</t>
-  </si>
-  <si>
-    <t>TI1_VSENSE</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>→ P10:2</t>
-  </si>
-  <si>
-    <t>P2:2→</t>
-  </si>
-  <si>
-    <t>→ P10:1</t>
-  </si>
-  <si>
-    <t>P2:1→</t>
-  </si>
-  <si>
-    <t>→ TB51:1</t>
-  </si>
-  <si>
-    <t>J10:2→</t>
-  </si>
-  <si>
-    <t>→ TB52:1</t>
-  </si>
-  <si>
-    <t>J10:1→</t>
-  </si>
-  <si>
-    <t>→ J21:1</t>
-  </si>
-  <si>
-    <t>TB51:2→</t>
-  </si>
-  <si>
-    <t>→ J21:2</t>
-  </si>
-  <si>
-    <t>TB52:2→</t>
-  </si>
-  <si>
-    <t>→ LS1</t>
-  </si>
-  <si>
-    <t>TB51:3→</t>
-  </si>
-  <si>
-    <t>LIMIT_PWR</t>
-  </si>
-  <si>
-    <t>TB52:3→</t>
-  </si>
-  <si>
-    <t>LIMIT_GND</t>
-  </si>
-  <si>
-    <t>→ LS2</t>
-  </si>
-  <si>
-    <t>TB51:4→</t>
-  </si>
-  <si>
-    <t>TB52:4→</t>
-  </si>
-  <si>
-    <t>→ HS1</t>
-  </si>
-  <si>
-    <t>TB51:5→</t>
-  </si>
-  <si>
-    <t>TB52:5→</t>
-  </si>
-  <si>
-    <t>→ HS2</t>
-  </si>
-  <si>
-    <t>TB51:6→</t>
-  </si>
-  <si>
-    <t>TB52:6→</t>
-  </si>
-  <si>
-    <t>→ TP1</t>
-  </si>
-  <si>
-    <t>TB51:7→</t>
-  </si>
-  <si>
-    <t>PROBE_PWR</t>
-  </si>
-  <si>
-    <t>→ P20:2</t>
-  </si>
-  <si>
-    <t>P21:2→</t>
-  </si>
-  <si>
-    <t>→ P20:1</t>
-  </si>
-  <si>
-    <t>P21:1→</t>
-  </si>
-  <si>
-    <t>→ TB53:1</t>
-  </si>
-  <si>
-    <t>J20:2→</t>
-  </si>
-  <si>
-    <t>→ TB54:1</t>
-  </si>
-  <si>
-    <t>J20:1→</t>
-  </si>
-  <si>
-    <t>→ J25:1</t>
-  </si>
-  <si>
-    <t>TB53:2→</t>
-  </si>
-  <si>
-    <t>→ J25:2</t>
-  </si>
-  <si>
-    <t>TB54:2→</t>
-  </si>
-  <si>
-    <t>→ LS3</t>
-  </si>
-  <si>
-    <t>TB53:3→</t>
-  </si>
-  <si>
-    <t>TB54:3→</t>
-  </si>
-  <si>
-    <t>→ LS4</t>
-  </si>
-  <si>
-    <t>TB53:4→</t>
-  </si>
-  <si>
-    <t>TB54:4→</t>
-  </si>
-  <si>
-    <t>→ HS3</t>
-  </si>
-  <si>
-    <t>TB53:5→</t>
-  </si>
-  <si>
-    <t>TB54:5→</t>
-  </si>
-  <si>
-    <t>→ P29:2</t>
-  </si>
-  <si>
-    <t>P25:2→</t>
-  </si>
-  <si>
-    <t>→ P29:1</t>
-  </si>
-  <si>
-    <t>P25:1→</t>
-  </si>
-  <si>
-    <t>→ TB57:1</t>
-  </si>
-  <si>
-    <t>J29:2→</t>
-  </si>
-  <si>
-    <t>→ TB58:1</t>
-  </si>
-  <si>
-    <t>J29:1→</t>
-  </si>
-  <si>
-    <t>→ LS5</t>
-  </si>
-  <si>
-    <t>TB57:2→</t>
-  </si>
-  <si>
-    <t>TB58:2→</t>
-  </si>
-  <si>
-    <t>→ LS6</t>
-  </si>
-  <si>
-    <t>TB57:3→</t>
-  </si>
-  <si>
-    <t>TB58:3→</t>
-  </si>
-  <si>
-    <t>→ HS4</t>
-  </si>
-  <si>
-    <t>TB57:4→</t>
-  </si>
-  <si>
-    <t>TB58:4→</t>
-  </si>
-  <si>
-    <t>→ K2</t>
-  </si>
-  <si>
-    <t>P4:1→</t>
-  </si>
-  <si>
-    <t>Need suitable relay</t>
-  </si>
-  <si>
-    <t>P4:2→</t>
-  </si>
-  <si>
-    <t>→ J8:2</t>
-  </si>
-  <si>
-    <t>PS5:V+1→</t>
-  </si>
-  <si>
-    <t>48V Power</t>
-  </si>
-  <si>
-    <t>48V_LOGIC</t>
-  </si>
-  <si>
-    <t>🟧 Orange</t>
-  </si>
-  <si>
-    <t>→ J8:1</t>
-  </si>
-  <si>
-    <t>PS5:V-1→</t>
-  </si>
-  <si>
-    <t>🟫 Brown</t>
-  </si>
-  <si>
-    <t>→ J8:4</t>
-  </si>
-  <si>
-    <t>PS6:V+1→</t>
-  </si>
-  <si>
-    <t>→ J8:3</t>
-  </si>
-  <si>
-    <t>PS6:V-1→</t>
-  </si>
-  <si>
-    <t>→ SD2:DC+</t>
-  </si>
-  <si>
-    <t>PS6:V+2→</t>
-  </si>
-  <si>
-    <t>V+2</t>
-  </si>
-  <si>
-    <t>DC+</t>
-  </si>
-  <si>
-    <t>→ SD2:DC-</t>
-  </si>
-  <si>
-    <t>PS6:V-2→</t>
-  </si>
-  <si>
-    <t>V-2</t>
-  </si>
-  <si>
-    <t>DC-</t>
-  </si>
-  <si>
-    <t>PS6:V+3→</t>
-  </si>
-  <si>
-    <t>V+3</t>
-  </si>
-  <si>
-    <t>PS6:V-3→</t>
-  </si>
-  <si>
-    <t>V-3</t>
-  </si>
-  <si>
-    <t>→ P18:2</t>
-  </si>
-  <si>
-    <t>P8:2→</t>
-  </si>
-  <si>
-    <t>→ P18:1</t>
-  </si>
-  <si>
-    <t>P8:1→</t>
-  </si>
-  <si>
-    <t>→ P18:4</t>
-  </si>
-  <si>
-    <t>P8:4→</t>
-  </si>
-  <si>
-    <t>→ P18:3</t>
-  </si>
-  <si>
-    <t>P8:3→</t>
-  </si>
-  <si>
-    <t>→ J15:1</t>
-  </si>
-  <si>
-    <t>J18:2→</t>
-  </si>
-  <si>
-    <t>→ J15:2</t>
-  </si>
-  <si>
-    <t>J18:1→</t>
-  </si>
-  <si>
-    <t>→ J15:4</t>
-  </si>
-  <si>
-    <t>J18:4→</t>
-  </si>
-  <si>
-    <t>→ J15:3</t>
-  </si>
-  <si>
-    <t>J18:3→</t>
-  </si>
-  <si>
-    <t>→ P20:4</t>
-  </si>
-  <si>
-    <t>P15:2→</t>
-  </si>
-  <si>
-    <t>→ P20:3</t>
-  </si>
-  <si>
-    <t>P15:1→</t>
-  </si>
-  <si>
-    <t>→ P29:4</t>
-  </si>
-  <si>
-    <t>P15:4→</t>
-  </si>
-  <si>
-    <t>→ P29:3</t>
-  </si>
-  <si>
-    <t>P15:3→</t>
-  </si>
-  <si>
-    <t>→ TB55:1</t>
-  </si>
-  <si>
-    <t>J20:4→</t>
-  </si>
-  <si>
-    <t>→ TB56:1</t>
-  </si>
-  <si>
-    <t>J20:3→</t>
-  </si>
-  <si>
-    <t>→ IM1:VDC+</t>
-  </si>
-  <si>
-    <t>TB55:2→</t>
-  </si>
-  <si>
-    <t>STEP_IO_PWR</t>
-  </si>
-  <si>
-    <t>VDC+</t>
-  </si>
-  <si>
-    <t>→ IM1:GND</t>
-  </si>
-  <si>
-    <t>TB56:2→</t>
-  </si>
-  <si>
-    <t>STEP_IO_GND</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>→ IM2:VDC+</t>
-  </si>
-  <si>
-    <t>TB55:3→</t>
-  </si>
-  <si>
-    <t>→ IM2:GND</t>
-  </si>
-  <si>
-    <t>TB56:4→</t>
-  </si>
-  <si>
-    <t>→ IM3:VDC+</t>
-  </si>
-  <si>
-    <t>J29:4→</t>
-  </si>
-  <si>
-    <t>→ IM3:GND</t>
-  </si>
-  <si>
-    <t>J29:3→</t>
-  </si>
-  <si>
-    <t>→ J5:2</t>
-  </si>
-  <si>
-    <t>MESA:TB3:18→</t>
-  </si>
-  <si>
-    <t>Control Signals</t>
-  </si>
-  <si>
-    <t>SPINDLE_RS+</t>
-  </si>
-  <si>
-    <t>🧵 Aqua</t>
-  </si>
-  <si>
-    <t>→ J5:1</t>
-  </si>
-  <si>
-    <t>MESA:TB3:16→</t>
-  </si>
-  <si>
-    <t>SPINDLE_RS-</t>
-  </si>
-  <si>
-    <t>🩵 Teal</t>
-  </si>
-  <si>
-    <t>→ J1:1</t>
-  </si>
-  <si>
-    <t>MESA:TB2:2→</t>
-  </si>
-  <si>
-    <t>Y1_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:2</t>
-  </si>
-  <si>
-    <t>MESA:TB2:3→</t>
-  </si>
-  <si>
-    <t>Y1_STEP+</t>
-  </si>
-  <si>
-    <t>→ J1:3</t>
-  </si>
-  <si>
-    <t>MESA:TB2:4→</t>
-  </si>
-  <si>
-    <t>Y1_DIR-</t>
-  </si>
-  <si>
-    <t>🟩⬜️ Green/White</t>
-  </si>
-  <si>
-    <t>→ J1:4</t>
-  </si>
-  <si>
-    <t>MESA:TB2:5→</t>
-  </si>
-  <si>
-    <t>Y1_DIR+</t>
-  </si>
-  <si>
-    <t>🟩 Green</t>
-  </si>
-  <si>
-    <t>→ J1:5</t>
-  </si>
-  <si>
-    <t>MESA:TB2:8→</t>
-  </si>
-  <si>
-    <t>Y2_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:6</t>
-  </si>
-  <si>
-    <t>MESA:TB2:9→</t>
-  </si>
-  <si>
-    <t>Y2_STEP+</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>→ J1:7</t>
-  </si>
-  <si>
-    <t>MESA:TB2:10→</t>
-  </si>
-  <si>
-    <t>Y2_DIR-</t>
-  </si>
-  <si>
-    <t>→ J1:8</t>
-  </si>
-  <si>
-    <t>MESA:TB2:11→</t>
-  </si>
-  <si>
-    <t>Y2_DIR+</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>→ J1:9</t>
-  </si>
-  <si>
-    <t>MESA:TB2:14→</t>
-  </si>
-  <si>
-    <t>X_STEP-</t>
-  </si>
-  <si>
-    <t>→ J1:10</t>
-  </si>
-  <si>
-    <t>MESA:TB2:15→</t>
-  </si>
-  <si>
-    <t>X_STEP+</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>→ J1:11</t>
-  </si>
-  <si>
-    <t>MESA:TB2:16→</t>
-  </si>
-  <si>
-    <t>X_DIR-</t>
-  </si>
-  <si>
-    <t>→ J1:12</t>
-  </si>
-  <si>
-    <t>MESA:TB2:17→</t>
-  </si>
-  <si>
-    <t>X_DIR+</t>
-  </si>
-  <si>
-    <t>→ SD1:PUL-</t>
-  </si>
-  <si>
-    <t>MESA:TB2:20→</t>
-  </si>
-  <si>
-    <t>Z_STEP-</t>
-  </si>
-  <si>
-    <t>PUL-</t>
-  </si>
-  <si>
-    <t>→ SD1:PUL+</t>
-  </si>
-  <si>
-    <t>MESA:TB2:21→</t>
-  </si>
-  <si>
-    <t>Z_STEP+</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>PUL+</t>
-  </si>
-  <si>
-    <t>→ SD1:DIR-</t>
-  </si>
-  <si>
-    <t>MESA:TB2:22→</t>
-  </si>
-  <si>
-    <t>Z_DIR-</t>
-  </si>
-  <si>
-    <t>DIR-</t>
-  </si>
-  <si>
-    <t>→ SD1:DIR+</t>
-  </si>
-  <si>
-    <t>MESA:TB2:23→</t>
-  </si>
-  <si>
-    <t>Z_DIR+</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>DIR+</t>
-  </si>
-  <si>
-    <t>→ J3:8</t>
-  </si>
-  <si>
-    <t>SD1:A+→</t>
-  </si>
-  <si>
-    <t>Z_A+</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Double check colours/order</t>
-  </si>
-  <si>
-    <t>→ J3:7</t>
-  </si>
-  <si>
-    <t>SD1:A-→</t>
-  </si>
-  <si>
-    <t>Z_A-</t>
-  </si>
-  <si>
-    <t>A-</t>
-  </si>
-  <si>
-    <t>→ J3:6</t>
-  </si>
-  <si>
-    <t>SD1:B+→</t>
-  </si>
-  <si>
-    <t>Z_B+</t>
-  </si>
-  <si>
-    <t>B+</t>
-  </si>
-  <si>
-    <t>→ J3:5</t>
-  </si>
-  <si>
-    <t>SD1:B-→</t>
-  </si>
-  <si>
-    <t>Z_B-</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>→ J3:4</t>
-  </si>
-  <si>
-    <t>SD2:A+→</t>
-  </si>
-  <si>
-    <t>DUST_A+</t>
-  </si>
-  <si>
-    <t>→ J3:3</t>
-  </si>
-  <si>
-    <t>SD2:A-→</t>
-  </si>
-  <si>
-    <t>DUST_A-</t>
-  </si>
-  <si>
-    <t>→ J3:2</t>
-  </si>
-  <si>
-    <t>SD2:B+→</t>
-  </si>
-  <si>
-    <t>DUST_B+</t>
-  </si>
-  <si>
-    <t>→ J3:1</t>
-  </si>
-  <si>
-    <t>SD2:B-→</t>
-  </si>
-  <si>
-    <t>DUST_B-</t>
-  </si>
-  <si>
-    <t>→ J1:13</t>
-  </si>
-  <si>
-    <t>MESA:TB6:5→</t>
-  </si>
-  <si>
-    <t>Y_MIN</t>
-  </si>
-  <si>
-    <t>🩶 Grey</t>
-  </si>
-  <si>
-    <t>→ J1:14</t>
-  </si>
-  <si>
-    <t>MESA:TB6:6→</t>
-  </si>
-  <si>
-    <t>Y_MAX</t>
-  </si>
-  <si>
-    <t>→ J1:15</t>
-  </si>
-  <si>
-    <t>MESA:TB6:7→</t>
-  </si>
-  <si>
-    <t>Y1_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:16</t>
-  </si>
-  <si>
-    <t>MESA:TB6:8→</t>
-  </si>
-  <si>
-    <t>Y2_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:17</t>
-  </si>
-  <si>
-    <t>MESA:TB6:9→</t>
-  </si>
-  <si>
-    <t>X_MIN</t>
-  </si>
-  <si>
-    <t>→ J1:18</t>
-  </si>
-  <si>
-    <t>MESA:TB6:10→</t>
-  </si>
-  <si>
-    <t>X_MAX</t>
-  </si>
-  <si>
-    <t>→ J1:19</t>
-  </si>
-  <si>
-    <t>MESA:TB6:11→</t>
-  </si>
-  <si>
-    <t>X_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:20</t>
-  </si>
-  <si>
-    <t>MESA:TB6:12→</t>
-  </si>
-  <si>
-    <t>Z_MIN</t>
-  </si>
-  <si>
-    <t>→ J1:21</t>
-  </si>
-  <si>
-    <t>MESA:TB6:13→</t>
-  </si>
-  <si>
-    <t>Z_MAX</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>→ J1:22</t>
-  </si>
-  <si>
-    <t>MESA:TB6:14→</t>
-  </si>
-  <si>
-    <t>Z_HOME</t>
-  </si>
-  <si>
-    <t>→ J1:23</t>
-  </si>
-  <si>
-    <t>MESA:TB6:15→</t>
-  </si>
-  <si>
-    <t>PROBE_IN</t>
-  </si>
-  <si>
-    <t>⬜️ White</t>
-  </si>
-  <si>
-    <t>→ FANS1:PWM</t>
-  </si>
-  <si>
-    <t>MESA:TB6:18→</t>
-  </si>
-  <si>
-    <t>FAN_PWM</t>
-  </si>
-  <si>
-    <t>PWM</t>
-  </si>
-  <si>
-    <t>→ J39:USB1</t>
-  </si>
-  <si>
-    <t>CPU1:USB1→</t>
-  </si>
-  <si>
-    <t>USB_HID</t>
-  </si>
-  <si>
-    <t>USB1</t>
-  </si>
-  <si>
-    <t>➖ not used</t>
-  </si>
-  <si>
-    <t>→ J38:USB1</t>
-  </si>
-  <si>
-    <t>CPU1:USB2→</t>
-  </si>
-  <si>
-    <t>USB_USER</t>
-  </si>
-  <si>
-    <t>USB2</t>
-  </si>
-  <si>
-    <t>Extend to monitor zone</t>
-  </si>
-  <si>
-    <t>→ J37:HDMI</t>
-  </si>
-  <si>
-    <t>CPU1:DP→</t>
-  </si>
-  <si>
-    <t>MONITOR</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>Add in dp/hdmi adapter</t>
-  </si>
-  <si>
-    <t>→ RF1:1</t>
-  </si>
-  <si>
-    <t>CPU1:RF→</t>
-  </si>
-  <si>
-    <t>WIFI_EXT</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>→ MESA:ETH</t>
-  </si>
-  <si>
-    <t>CPU1:ETH→</t>
-  </si>
-  <si>
-    <t>ETH_MESA</t>
-  </si>
-  <si>
-    <t>ETH</t>
-  </si>
-  <si>
-    <t>→ P11:8</t>
-  </si>
-  <si>
-    <t>P3:8→</t>
-  </si>
-  <si>
-    <t>→ P11:7</t>
-  </si>
-  <si>
-    <t>P3:7→</t>
-  </si>
-  <si>
-    <t>→ P11:6</t>
-  </si>
-  <si>
-    <t>P3:6→</t>
-  </si>
-  <si>
-    <t>→ P11:5</t>
-  </si>
-  <si>
-    <t>P3:5→</t>
-  </si>
-  <si>
-    <t>→ J18:1</t>
-  </si>
-  <si>
-    <t>J11:8→</t>
-  </si>
-  <si>
-    <t>→ J18:2</t>
-  </si>
-  <si>
-    <t>J11:7→</t>
-  </si>
-  <si>
-    <t>→ J18:3</t>
-  </si>
-  <si>
-    <t>J11:6→</t>
-  </si>
-  <si>
-    <t>→ J18:4</t>
-  </si>
-  <si>
-    <t>J11:5→</t>
-  </si>
-  <si>
-    <t>→ P30:8</t>
-  </si>
-  <si>
-    <t>P16:8→</t>
-  </si>
-  <si>
-    <t>→ P30:7</t>
-  </si>
-  <si>
-    <t>P16:7→</t>
-  </si>
-  <si>
-    <t>→ P30:6</t>
-  </si>
-  <si>
-    <t>P16:6→</t>
-  </si>
-  <si>
-    <t>→ P30:5</t>
-  </si>
-  <si>
-    <t>P16:5→</t>
-  </si>
-  <si>
-    <t>→ P11:4</t>
-  </si>
-  <si>
-    <t>P3:4→</t>
-  </si>
-  <si>
-    <t>→ P11:3</t>
-  </si>
-  <si>
-    <t>P3:3→</t>
-  </si>
-  <si>
-    <t>→ P11:2</t>
-  </si>
-  <si>
-    <t>P3:2→</t>
-  </si>
-  <si>
-    <t>→ P11:1</t>
-  </si>
-  <si>
-    <t>P3:1→</t>
-  </si>
-  <si>
-    <t>→ J16:4</t>
-  </si>
-  <si>
-    <t>J11:4→</t>
-  </si>
-  <si>
-    <t>→ J16:3</t>
-  </si>
-  <si>
-    <t>J11:3→</t>
-  </si>
-  <si>
-    <t>→ J16:2</t>
-  </si>
-  <si>
-    <t>J11:2→</t>
-  </si>
-  <si>
-    <t>→ J16:1</t>
-  </si>
-  <si>
-    <t>J11:1→</t>
-  </si>
-  <si>
-    <t>→ SM1</t>
-  </si>
-  <si>
-    <t>J30:8→</t>
-  </si>
-  <si>
-    <t>J30:7→</t>
-  </si>
-  <si>
-    <t>J30:6→</t>
-  </si>
-  <si>
-    <t>J30:5→</t>
-  </si>
-  <si>
-    <t>→ M1:1</t>
-  </si>
-  <si>
-    <t>VFD1:U→</t>
-  </si>
-  <si>
-    <t>SPINDLE_U</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>SOLDER</t>
-  </si>
-  <si>
-    <t>→ M1:2</t>
-  </si>
-  <si>
-    <t>VFD1:V→</t>
-  </si>
-  <si>
-    <t>SPINDLE_V</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>→ M1:3</t>
-  </si>
-  <si>
-    <t>VFD1:W→</t>
-  </si>
-  <si>
-    <t>SPINDLE_W</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>→ P30:4</t>
-  </si>
-  <si>
-    <t>P16:4→</t>
-  </si>
-  <si>
-    <t>→ P30:3</t>
-  </si>
-  <si>
-    <t>P16:3→</t>
-  </si>
-  <si>
-    <t>→ P30:2</t>
-  </si>
-  <si>
-    <t>P16:2→</t>
-  </si>
-  <si>
-    <t>→ P30:1</t>
-  </si>
-  <si>
-    <t>P16:1→</t>
-  </si>
-  <si>
-    <t>→ P9:1</t>
-  </si>
-  <si>
-    <t>P1:1→</t>
-  </si>
-  <si>
-    <t>→ P9:2</t>
-  </si>
-  <si>
-    <t>P1:2→</t>
-  </si>
-  <si>
-    <t>→ P9:3</t>
-  </si>
-  <si>
-    <t>P1:3→</t>
-  </si>
-  <si>
-    <t>→ P9:4</t>
-  </si>
-  <si>
-    <t>P1:4→</t>
-  </si>
-  <si>
-    <t>→ P9:5</t>
-  </si>
-  <si>
-    <t>P1:5→</t>
-  </si>
-  <si>
-    <t>→ P9:6</t>
-  </si>
-  <si>
-    <t>P1:6→</t>
-  </si>
-  <si>
-    <t>→ P9:7</t>
-  </si>
-  <si>
-    <t>P1:7→</t>
-  </si>
-  <si>
-    <t>→ P9:8</t>
-  </si>
-  <si>
-    <t>P1:8→</t>
-  </si>
-  <si>
-    <t>→ P9:9</t>
-  </si>
-  <si>
-    <t>P1:9→</t>
-  </si>
-  <si>
-    <t>→ P9:10</t>
-  </si>
-  <si>
-    <t>P1:10→</t>
-  </si>
-  <si>
-    <t>→ P9:11</t>
-  </si>
-  <si>
-    <t>P1:11→</t>
-  </si>
-  <si>
-    <t>→ P9:12</t>
-  </si>
-  <si>
-    <t>P1:12→</t>
-  </si>
-  <si>
-    <t>→ J14:1</t>
-  </si>
-  <si>
-    <t>J9:1→</t>
-  </si>
-  <si>
-    <t>→ J14:2</t>
-  </si>
-  <si>
-    <t>J9:2→</t>
-  </si>
-  <si>
-    <t>→ J14:3</t>
-  </si>
-  <si>
-    <t>J9:3→</t>
-  </si>
-  <si>
-    <t>→ J14:4</t>
-  </si>
-  <si>
-    <t>J9:4→</t>
-  </si>
-  <si>
-    <t>→ J14:5</t>
-  </si>
-  <si>
-    <t>J9:5→</t>
-  </si>
-  <si>
-    <t>→ J14:6</t>
-  </si>
-  <si>
-    <t>J9:6→</t>
-  </si>
-  <si>
-    <t>→ J14:7</t>
-  </si>
-  <si>
-    <t>J9:7→</t>
-  </si>
-  <si>
-    <t>→ J14:8</t>
-  </si>
-  <si>
-    <t>J9:8→</t>
-  </si>
-  <si>
-    <t>→ J14:9</t>
-  </si>
-  <si>
-    <t>J9:9→</t>
-  </si>
-  <si>
-    <t>→ J14:10</t>
-  </si>
-  <si>
-    <t>J9:10→</t>
-  </si>
-  <si>
-    <t>→ J14:11</t>
-  </si>
-  <si>
-    <t>J9:11→</t>
-  </si>
-  <si>
-    <t>→ J14:12</t>
-  </si>
-  <si>
-    <t>J9:12→</t>
-  </si>
-  <si>
-    <t>→ P19:1</t>
-  </si>
-  <si>
-    <t>P14:1→</t>
-  </si>
-  <si>
-    <t>→ P19:2</t>
-  </si>
-  <si>
-    <t>P14:2→</t>
-  </si>
-  <si>
-    <t>→ P19:3</t>
-  </si>
-  <si>
-    <t>P14:3→</t>
-  </si>
-  <si>
-    <t>→ P19:4</t>
-  </si>
-  <si>
-    <t>P14:4→</t>
-  </si>
-  <si>
-    <t>→ P19:5</t>
-  </si>
-  <si>
-    <t>P14:5→</t>
-  </si>
-  <si>
-    <t>→ P19:6</t>
-  </si>
-  <si>
-    <t>P14:6→</t>
-  </si>
-  <si>
-    <t>→ P19:7</t>
-  </si>
-  <si>
-    <t>P14:7→</t>
-  </si>
-  <si>
-    <t>→ P19:8</t>
-  </si>
-  <si>
-    <t>P14:8→</t>
-  </si>
-  <si>
-    <t>→ P19:9</t>
-  </si>
-  <si>
-    <t>P14:9→</t>
-  </si>
-  <si>
-    <t>→ P19:10</t>
-  </si>
-  <si>
-    <t>P14:10→</t>
-  </si>
-  <si>
-    <t>→ P19:11</t>
-  </si>
-  <si>
-    <t>P14:11→</t>
-  </si>
-  <si>
-    <t>→ P19:12</t>
-  </si>
-  <si>
-    <t>P14:12→</t>
-  </si>
-  <si>
-    <t>→ IM1:PUL-</t>
-  </si>
-  <si>
-    <t>J19:1→</t>
-  </si>
-  <si>
-    <t>→ IM1:PUL+</t>
-  </si>
-  <si>
-    <t>J19:2→</t>
-  </si>
-  <si>
-    <t>→ IM1:DIR-</t>
-  </si>
-  <si>
-    <t>J19:3→</t>
-  </si>
-  <si>
-    <t>→ IM1:DIR+</t>
-  </si>
-  <si>
-    <t>J19:4→</t>
-  </si>
-  <si>
-    <t>→ IM2:PUL-</t>
-  </si>
-  <si>
-    <t>J19:5→</t>
-  </si>
-  <si>
-    <t>→ IM2:PUL+</t>
-  </si>
-  <si>
-    <t>J19:6→</t>
-  </si>
-  <si>
-    <t>→ IM2:DIR-</t>
-  </si>
-  <si>
-    <t>J19:7→</t>
-  </si>
-  <si>
-    <t>→ IM2:DIR+</t>
-  </si>
-  <si>
-    <t>J19:8→</t>
-  </si>
-  <si>
-    <t>→ J24:1</t>
-  </si>
-  <si>
-    <t>J19:9→</t>
-  </si>
-  <si>
-    <t>→ J24:2</t>
-  </si>
-  <si>
-    <t>J19:10→</t>
-  </si>
-  <si>
-    <t>→ J24:3</t>
-  </si>
-  <si>
-    <t>J19:11→</t>
-  </si>
-  <si>
-    <t>→ J24:4</t>
-  </si>
-  <si>
-    <t>J19:12→</t>
-  </si>
-  <si>
-    <t>→ P28:1</t>
-  </si>
-  <si>
-    <t>P24:1→</t>
-  </si>
-  <si>
-    <t>→ P28:2</t>
-  </si>
-  <si>
-    <t>P24:2→</t>
-  </si>
-  <si>
-    <t>→ P28:3</t>
-  </si>
-  <si>
-    <t>P24:3→</t>
-  </si>
-  <si>
-    <t>→ P28:4</t>
-  </si>
-  <si>
-    <t>P24:4→</t>
-  </si>
-  <si>
-    <t>→ IM3:PUL-</t>
-  </si>
-  <si>
-    <t>J28:1→</t>
-  </si>
-  <si>
-    <t>→ IM3:PUL+</t>
-  </si>
-  <si>
-    <t>J28:2→</t>
-  </si>
-  <si>
-    <t>→ IM3:DIR-</t>
-  </si>
-  <si>
-    <t>J28:3→</t>
-  </si>
-  <si>
-    <t>→ IM3:DIR+</t>
-  </si>
-  <si>
-    <t>J28:4→</t>
-  </si>
-  <si>
-    <t>→ P9:13</t>
-  </si>
-  <si>
-    <t>P1:13→</t>
-  </si>
-  <si>
-    <t>→ P9:14</t>
-  </si>
-  <si>
-    <t>P1:14→</t>
-  </si>
-  <si>
-    <t>→ P9:15</t>
-  </si>
-  <si>
-    <t>P1:15→</t>
-  </si>
-  <si>
-    <t>→ P9:16</t>
-  </si>
-  <si>
-    <t>P1:16→</t>
-  </si>
-  <si>
-    <t>→ P9:17</t>
-  </si>
-  <si>
-    <t>P1:17→</t>
-  </si>
-  <si>
-    <t>→ P9:18</t>
-  </si>
-  <si>
-    <t>P1:18→</t>
-  </si>
-  <si>
-    <t>→ P9:19</t>
-  </si>
-  <si>
-    <t>P1:19→</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>→ P9:20</t>
-  </si>
-  <si>
-    <t>P1:20→</t>
-  </si>
-  <si>
-    <t>→ P9:21</t>
-  </si>
-  <si>
-    <t>P1:21→</t>
-  </si>
-  <si>
-    <t>→ P9:22</t>
-  </si>
-  <si>
-    <t>P1:22→</t>
-  </si>
-  <si>
-    <t>→ P9:23</t>
-  </si>
-  <si>
-    <t>P1:23→</t>
-  </si>
-  <si>
-    <t>J9:13→</t>
-  </si>
-  <si>
-    <t>J9:14→</t>
-  </si>
-  <si>
-    <t>J9:15→</t>
-  </si>
-  <si>
-    <t>J9:16→</t>
-  </si>
-  <si>
-    <t>→ J14:17</t>
-  </si>
-  <si>
-    <t>J9:17→</t>
-  </si>
-  <si>
-    <t>→ J14:18</t>
-  </si>
-  <si>
-    <t>J9:18→</t>
-  </si>
-  <si>
-    <t>→ J14:19</t>
-  </si>
-  <si>
-    <t>J9:19→</t>
-  </si>
-  <si>
-    <t>→ J14:20</t>
-  </si>
-  <si>
-    <t>J9:20→</t>
-  </si>
-  <si>
-    <t>→ J14:21</t>
-  </si>
-  <si>
-    <t>J9:21→</t>
-  </si>
-  <si>
-    <t>→ J14:22</t>
-  </si>
-  <si>
-    <t>J9:22→</t>
-  </si>
-  <si>
-    <t>J9:23→</t>
-  </si>
-  <si>
-    <t>→ P19:17</t>
-  </si>
-  <si>
-    <t>P14:17→</t>
-  </si>
-  <si>
-    <t>→ P19:18</t>
-  </si>
-  <si>
-    <t>P14:18→</t>
-  </si>
-  <si>
-    <t>→ P19:19</t>
-  </si>
-  <si>
-    <t>P14:19→</t>
-  </si>
-  <si>
-    <t>→ P19:20</t>
-  </si>
-  <si>
-    <t>P14:20→</t>
-  </si>
-  <si>
-    <t>→ P19:21</t>
-  </si>
-  <si>
-    <t>P14:21→</t>
-  </si>
-  <si>
-    <t>→ P19:22</t>
-  </si>
-  <si>
-    <t>P14:22→</t>
-  </si>
-  <si>
-    <t>J19:17→</t>
-  </si>
-  <si>
-    <t>J19:18→</t>
-  </si>
-  <si>
-    <t>J19:19→</t>
-  </si>
-  <si>
-    <t>→ J24:5</t>
-  </si>
-  <si>
-    <t>J19:20→</t>
-  </si>
-  <si>
-    <t>→ J24:6</t>
-  </si>
-  <si>
-    <t>J19:21→</t>
-  </si>
-  <si>
-    <t>→ J24:7</t>
-  </si>
-  <si>
-    <t>J19:22→</t>
-  </si>
-  <si>
-    <t>→ P28:5</t>
-  </si>
-  <si>
-    <t>P24:5→</t>
-  </si>
-  <si>
-    <t>→ P28:6</t>
-  </si>
-  <si>
-    <t>P24:6→</t>
-  </si>
-  <si>
-    <t>→ P28:7</t>
-  </si>
-  <si>
-    <t>P24:7→</t>
-  </si>
-  <si>
-    <t>→ LS5:5</t>
-  </si>
-  <si>
-    <t>J28:5→</t>
-  </si>
-  <si>
-    <t>→ LS6:6</t>
-  </si>
-  <si>
-    <t>J28:6→</t>
-  </si>
-  <si>
-    <t>→ HS4:7</t>
-  </si>
-  <si>
-    <t>J28:7→</t>
-  </si>
-  <si>
-    <t>→ TB1:1</t>
-  </si>
-  <si>
-    <t>P0:PE→</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>→ TB4:1</t>
-  </si>
-  <si>
-    <t>TB1:2→</t>
-  </si>
-  <si>
-    <t>→ F1:PE</t>
-  </si>
-  <si>
-    <t>TB4:3→</t>
   </si>
   <si>
     <t>→ PS5:GND</t>
@@ -8740,7 +8743,7 @@
     </row>
     <row r="13">
       <c r="B13" t="s" s="3">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -8748,10 +8751,10 @@
     <row r="14">
       <c r="B14" s="4"/>
       <c r="C14" t="s" s="4">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D14" t="s" s="5">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
@@ -17944,7 +17947,7 @@
       </c>
       <c r="L105" s="20"/>
       <c r="M105" s="35"/>
-      <c r="N105" s="20"/>
+      <c r="N105" s="35"/>
       <c r="O105" s="35"/>
       <c r="P105" t="b" s="34">
         <v>0</v>
@@ -17991,7 +17994,7 @@
       </c>
       <c r="L106" s="20"/>
       <c r="M106" s="35"/>
-      <c r="N106" s="20"/>
+      <c r="N106" s="35"/>
       <c r="O106" s="35"/>
       <c r="P106" t="b" s="34">
         <v>0</v>
@@ -18038,7 +18041,7 @@
       </c>
       <c r="L107" s="20"/>
       <c r="M107" s="35"/>
-      <c r="N107" s="20"/>
+      <c r="N107" s="35"/>
       <c r="O107" s="35"/>
       <c r="P107" t="b" s="34">
         <v>0</v>
@@ -18085,7 +18088,7 @@
       </c>
       <c r="L108" s="20"/>
       <c r="M108" s="35"/>
-      <c r="N108" s="20"/>
+      <c r="N108" s="35"/>
       <c r="O108" s="35"/>
       <c r="P108" t="b" s="34">
         <v>0</v>
@@ -18132,7 +18135,7 @@
       </c>
       <c r="L109" s="20"/>
       <c r="M109" s="35"/>
-      <c r="N109" s="20"/>
+      <c r="N109" s="35"/>
       <c r="O109" s="35"/>
       <c r="P109" t="b" s="34">
         <v>0</v>
@@ -18179,7 +18182,7 @@
       </c>
       <c r="L110" s="20"/>
       <c r="M110" s="35"/>
-      <c r="N110" s="20"/>
+      <c r="N110" s="35"/>
       <c r="O110" s="35"/>
       <c r="P110" t="b" s="34">
         <v>0</v>
@@ -18226,7 +18229,7 @@
       </c>
       <c r="L111" s="20"/>
       <c r="M111" s="35"/>
-      <c r="N111" s="20"/>
+      <c r="N111" s="35"/>
       <c r="O111" s="35"/>
       <c r="P111" t="b" s="34">
         <v>0</v>
@@ -18273,7 +18276,7 @@
       </c>
       <c r="L112" s="20"/>
       <c r="M112" s="35"/>
-      <c r="N112" s="20"/>
+      <c r="N112" s="35"/>
       <c r="O112" s="35"/>
       <c r="P112" t="b" s="34">
         <v>0</v>
@@ -24496,7 +24499,7 @@
       </c>
       <c r="L229" s="20"/>
       <c r="M229" s="35"/>
-      <c r="N229" s="20"/>
+      <c r="N229" s="35"/>
       <c r="O229" s="33">
         <v>18</v>
       </c>
@@ -24547,7 +24550,7 @@
       </c>
       <c r="L230" s="20"/>
       <c r="M230" s="35"/>
-      <c r="N230" s="20"/>
+      <c r="N230" s="35"/>
       <c r="O230" s="33">
         <v>18</v>
       </c>
@@ -24598,7 +24601,7 @@
       </c>
       <c r="L231" s="20"/>
       <c r="M231" s="35"/>
-      <c r="N231" s="20"/>
+      <c r="N231" s="35"/>
       <c r="O231" s="33">
         <v>18</v>
       </c>
@@ -24649,7 +24652,7 @@
       </c>
       <c r="L232" s="20"/>
       <c r="M232" s="35"/>
-      <c r="N232" s="20"/>
+      <c r="N232" s="35"/>
       <c r="O232" s="33">
         <v>18</v>
       </c>
@@ -30228,7 +30231,7 @@
         <v>1128</v>
       </c>
       <c r="N338" t="s" s="20">
-        <v>379</v>
+        <v>1133</v>
       </c>
       <c r="O338" s="33">
         <v>10</v>
@@ -30701,10 +30704,10 @@
         <v>144</v>
       </c>
       <c r="L347" t="s" s="20">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="M347" t="s" s="20">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="N347" t="s" s="20">
         <v>346</v>
@@ -30753,13 +30756,13 @@
         <v>329</v>
       </c>
       <c r="K348" t="s" s="20">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="L348" t="s" s="20">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="M348" t="s" s="20">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N348" t="s" s="20">
         <v>346</v>
@@ -31210,8 +31213,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J233 N3:N104 N113:N228 N233:N356 J234:J356">
-      <formula1>",Ferrule,Spade,Ring,Solder,Other"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J356 N3:N356">
+      <formula1>",Ferrule,Spade,Blade,Ring,Solder,Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R356">
       <formula1>",🟥 Red,⬛️ Black,🟩 Green,🟩⬜️ Green/White,🟦 Blue,🟦⬜️ Blue/White,🟧 Orange,🟫 Brown,⬜️ White,🩶 Grey,🧵 Aqua,🩵 Teal,➖ not used"</formula1>
@@ -31245,7 +31248,7 @@
   <sheetData>
     <row r="1" ht="29" customHeight="1">
       <c r="A1" t="s" s="7">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -31257,16 +31260,16 @@
         <v>306</v>
       </c>
       <c r="B2" t="s" s="8">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C2" t="s" s="37">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D2" t="s" s="37">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E2" t="s" s="38">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="3" ht="8.75" customHeight="1" hidden="1">
@@ -31274,7 +31277,7 @@
         <v>W·001</v>
       </c>
       <c r="B3" t="s" s="40">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C3" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·001\nNEWLINE:AC_L1_IN\nNEWLINE:→ TB1:5\nTEXT: \nTEXT:W·001\nNEWLINE:AC_L1_IN\nNEWLINE:P0:L1→\n" | $HOME/.local/bin/labelle --output browser --style bold --batch</v>
@@ -31291,7 +31294,7 @@
         <v>W·002</v>
       </c>
       <c r="B4" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C4" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·002\nNEWLINE:AC_L2_IN\nNEWLINE:→ TB1:3\nTEXT: \nTEXT:W·002\nNEWLINE:AC_L2_IN\nNEWLINE:P0:L2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31308,7 +31311,7 @@
         <v>W·003</v>
       </c>
       <c r="B5" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·003\nNEWLINE:AC_L1_IN\nNEWLINE:→ Q1:1\nTEXT: \nTEXT:W·003\nNEWLINE:AC_L1_IN\nNEWLINE:TB1:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31325,7 +31328,7 @@
         <v>W·004</v>
       </c>
       <c r="B6" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·004\nNEWLINE:AC_L2_IN\nNEWLINE:→ Q1:3\nTEXT: \nTEXT:W·004\nNEWLINE:AC_L2_IN\nNEWLINE:TB1:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31342,7 +31345,7 @@
         <v>W·005</v>
       </c>
       <c r="B7" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C7" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·005\nNEWLINE:AC_L1_FUSED\nNEWLINE:→ F1:1\nTEXT: \nTEXT:W·005\nNEWLINE:AC_L1_FUSED\nNEWLINE:Q1:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31359,7 +31362,7 @@
         <v>W·006</v>
       </c>
       <c r="B8" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C8" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·006\nNEWLINE:AC_L2_FUSED\nNEWLINE:→ F1:2\nTEXT: \nTEXT:W·006\nNEWLINE:AC_L2_FUSED\nNEWLINE:Q1:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31376,7 +31379,7 @@
         <v>W·007</v>
       </c>
       <c r="B9" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C9" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·007\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ TB2:1\nTEXT: \nTEXT:W·007\nNEWLINE:AC_L1_FILTERED\nNEWLINE:F1:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31393,7 +31396,7 @@
         <v>W·008</v>
       </c>
       <c r="B10" t="s" s="40">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C10" t="str" s="41">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·008\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ TB2:11\nTEXT: \nTEXT:W·008\nNEWLINE:AC_L2_FILTERED\nNEWLINE:F1:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31410,7 +31413,7 @@
         <v>W·009</v>
       </c>
       <c r="B11" t="s" s="43">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C11" t="str" s="44">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·009\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ PS1:L\nTEXT: \nTEXT:W·009\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB2:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31427,7 +31430,7 @@
         <v>W·010</v>
       </c>
       <c r="B12" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C12" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·010\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ PS1:N\nTEXT: \nTEXT:W·010\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB2:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31444,7 +31447,7 @@
         <v>W·011</v>
       </c>
       <c r="B13" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C13" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·011\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ K1:L1\nTEXT: \nTEXT:W·011\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB2:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31461,7 +31464,7 @@
         <v>W·012</v>
       </c>
       <c r="B14" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C14" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·012\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ K1:L2\nTEXT: \nTEXT:W·012\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB2:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31478,7 +31481,7 @@
         <v>W·013</v>
       </c>
       <c r="B15" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C15" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·013\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ PS2:L\nTEXT: \nTEXT:W·013\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB2:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31495,7 +31498,7 @@
         <v>W·014</v>
       </c>
       <c r="B16" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C16" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·014\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ PS2:N\nTEXT: \nTEXT:W·014\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB2:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31512,7 +31515,7 @@
         <v>W·015</v>
       </c>
       <c r="B17" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C17" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·015\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ J35:L\nTEXT: \nTEXT:W·015\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB2:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31529,7 +31532,7 @@
         <v>W·016</v>
       </c>
       <c r="B18" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C18" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·016\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ J35:N\nTEXT: \nTEXT:W·016\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB2:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31546,7 +31549,7 @@
         <v>W·021</v>
       </c>
       <c r="B19" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C19" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·021\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ TB3:1\nTEXT: \nTEXT:W·021\nNEWLINE:AC_L1_FILTERED\nNEWLINE:K1:T1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31563,7 +31566,7 @@
         <v>W·022</v>
       </c>
       <c r="B20" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C20" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·022\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ TB3:11\nTEXT: \nTEXT:W·022\nNEWLINE:AC_L2_FILTERED\nNEWLINE:K1:T2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31580,7 +31583,7 @@
         <v>W·023</v>
       </c>
       <c r="B21" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C21" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·023\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ PS5:L\nTEXT: \nTEXT:W·023\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB3:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31597,7 +31600,7 @@
         <v>W·024</v>
       </c>
       <c r="B22" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C22" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·024\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ PS5:N\nTEXT: \nTEXT:W·024\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB3:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31614,7 +31617,7 @@
         <v>W·025</v>
       </c>
       <c r="B23" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C23" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·025\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ PS6:L\nTEXT: \nTEXT:W·025\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB3:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31631,7 +31634,7 @@
         <v>W·026</v>
       </c>
       <c r="B24" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C24" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·026\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ PS6:N\nTEXT: \nTEXT:W·026\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB3:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31648,7 +31651,7 @@
         <v>W·027</v>
       </c>
       <c r="B25" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C25" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·027\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ PS4:L\nTEXT: \nTEXT:W·027\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB3:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31665,7 +31668,7 @@
         <v>W·028</v>
       </c>
       <c r="B26" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C26" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·028\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ PS4:N\nTEXT: \nTEXT:W·028\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB3:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31682,7 +31685,7 @@
         <v>W·029</v>
       </c>
       <c r="B27" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C27" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·029\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ J6:4\nTEXT: \nTEXT:W·029\nNEWLINE:AC_L1_FILTERED\nNEWLINE:TB3:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31699,7 +31702,7 @@
         <v>W·030</v>
       </c>
       <c r="B28" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C28" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·030\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ J6:3\nTEXT: \nTEXT:W·030\nNEWLINE:AC_L2_FILTERED\nNEWLINE:TB3:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31716,7 +31719,7 @@
         <v>W·051</v>
       </c>
       <c r="B29" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C29" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·051\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ VFD1:R\nTEXT: \nTEXT:W·051\nNEWLINE:AC_L1_FILTERED\nNEWLINE:P6:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31733,7 +31736,7 @@
         <v>W·052</v>
       </c>
       <c r="B30" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C30" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·052\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ VFD1:S\nTEXT: \nTEXT:W·052\nNEWLINE:AC_L2_FILTERED\nNEWLINE:P6:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31750,7 +31753,7 @@
         <v>W·053</v>
       </c>
       <c r="B31" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C31" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·053\nNEWLINE:AC_L1_FILTERED\nNEWLINE:→ J36:L\nTEXT: \nTEXT:W·053\nNEWLINE:AC_L1_FILTERED\nNEWLINE:P35:L→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31767,7 +31770,7 @@
         <v>W·054</v>
       </c>
       <c r="B32" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C32" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·054\nNEWLINE:AC_L2_FILTERED\nNEWLINE:→ J36:N\nTEXT: \nTEXT:W·054\nNEWLINE:AC_L2_FILTERED\nNEWLINE:P35:N→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31784,7 +31787,7 @@
         <v>W·101</v>
       </c>
       <c r="B33" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C33" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·101\nNEWLINE:24V_LOGIC\nNEWLINE:→ TB5:1\nTEXT: \nTEXT:W·101\nNEWLINE:24V_LOGIC\nNEWLINE:PS1:V+→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31801,7 +31804,7 @@
         <v>W·102</v>
       </c>
       <c r="B34" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C34" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·102\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB5:9\nTEXT: \nTEXT:W·102\nNEWLINE:0V_LOGIC\nNEWLINE:PS1:V-→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31818,7 +31821,7 @@
         <v>W·103</v>
       </c>
       <c r="B35" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C35" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·103\nNEWLINE:24V_LOGIC\nNEWLINE:→ S1:21\nTEXT: \nTEXT:W·103\nNEWLINE:24V_LOGIC\nNEWLINE:TB5:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31835,7 +31838,7 @@
         <v>W·104</v>
       </c>
       <c r="B36" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C36" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·104\nNEWLINE:24V_LOGIC\nNEWLINE:→ S1:13\nTEXT: \nTEXT:W·104\nNEWLINE:24V_LOGIC\nNEWLINE:TB5:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31852,7 +31855,7 @@
         <v>W·105</v>
       </c>
       <c r="B37" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C37" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·105\nNEWLINE:24V_LOGIC\nNEWLINE:→ J7:7\nTEXT: \nTEXT:W·105\nNEWLINE:24V_LOGIC\nNEWLINE:TB5:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31869,7 +31872,7 @@
         <v>W·106</v>
       </c>
       <c r="B38" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C38" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·106\nNEWLINE:24V_LOGIC\nNEWLINE:→ J7:3\nTEXT: \nTEXT:W·106\nNEWLINE:24V_LOGIC\nNEWLINE:TB5:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31886,7 +31889,7 @@
         <v>W·107</v>
       </c>
       <c r="B39" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C39" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·107\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ PL1:X1\nTEXT: \nTEXT:W·107\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:TB5:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31903,7 +31906,7 @@
         <v>W·108</v>
       </c>
       <c r="B40" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C40" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·108\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ J7:6\nTEXT: \nTEXT:W·108\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:TB5:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31920,7 +31923,7 @@
         <v>W·109</v>
       </c>
       <c r="B41" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C41" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·109\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ J7:2\nTEXT: \nTEXT:W·109\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:TB5:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31937,7 +31940,7 @@
         <v>W·110</v>
       </c>
       <c r="B42" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C42" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·110\nNEWLINE:0V_LOGIC\nNEWLINE:→ PL4:X2\nTEXT: \nTEXT:W·110\nNEWLINE:0V_LOGIC\nNEWLINE:TB5:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31954,7 +31957,7 @@
         <v>W·111</v>
       </c>
       <c r="B43" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C43" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·111\nNEWLINE:0V_LOGIC\nNEWLINE:→ A2\nTEXT: \nTEXT:W·111\nNEWLINE:0V_LOGIC\nNEWLINE:TB5:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31971,7 +31974,7 @@
         <v>W·112</v>
       </c>
       <c r="B44" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C44" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·112\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ TB8:1\nTEXT: \nTEXT:W·112\nNEWLINE:ESTOP_LOOP\nNEWLINE:S1:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -31988,7 +31991,7 @@
         <v>W·113</v>
       </c>
       <c r="B45" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C45" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·113\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J7:8\nTEXT: \nTEXT:W·113\nNEWLINE:ESTOP_LOOP\nNEWLINE:TB8:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32005,7 +32008,7 @@
         <v>W·114</v>
       </c>
       <c r="B46" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C46" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·114\nNEWLINE:24V_LOGIC\nNEWLINE:→ PL1:X2\nTEXT: \nTEXT:W·114\nNEWLINE:24V_LOGIC\nNEWLINE:S1:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32022,7 +32025,7 @@
         <v>W·115</v>
       </c>
       <c r="B47" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C47" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·115\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ TB9:1\nTEXT: \nTEXT:W·115\nNEWLINE:ESTOP_LOOP\nNEWLINE:J7:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32039,7 +32042,7 @@
         <v>W·116</v>
       </c>
       <c r="B48" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C48" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·116\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J7:4\nTEXT: \nTEXT:W·116\nNEWLINE:ESTOP_LOOP\nNEWLINE:TB9:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32056,7 +32059,7 @@
         <v>W·117</v>
       </c>
       <c r="B49" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C49" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·117\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ TB10:1\nTEXT: \nTEXT:W·117\nNEWLINE:ESTOP_LOOP\nNEWLINE:J7:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32073,7 +32076,7 @@
         <v>W·118</v>
       </c>
       <c r="B50" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C50" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·118\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ PB2:21\nTEXT: \nTEXT:W·118\nNEWLINE:ESTOP_LOOP\nNEWLINE:TB10:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32090,7 +32093,7 @@
         <v>W·119</v>
       </c>
       <c r="B51" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C51" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·119\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ TB6:1\nTEXT: \nTEXT:W·119\nNEWLINE:ESTOP_LOOP\nNEWLINE:PB2:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32107,7 +32110,7 @@
         <v>W·120</v>
       </c>
       <c r="B52" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C52" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·120\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ PB1:13\nTEXT: \nTEXT:W·120\nNEWLINE:ESTOP_LOOP\nNEWLINE:TB6:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32124,7 +32127,7 @@
         <v>W·121</v>
       </c>
       <c r="B53" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C53" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·121\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ K1:13\nTEXT: \nTEXT:W·121\nNEWLINE:ESTOP_LOOP\nNEWLINE:TB6:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32141,7 +32144,7 @@
         <v>W·122</v>
       </c>
       <c r="B54" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C54" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·122\nNEWLINE:MACHINE_ENABLE\nNEWLINE:→ TB7:1\nTEXT: \nTEXT:W·122\nNEWLINE:MACHINE_ENABLE\nNEWLINE:PB1:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32158,7 +32161,7 @@
         <v>W·123</v>
       </c>
       <c r="B55" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C55" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·123\nNEWLINE:MACHINE_ENABLE\nNEWLINE:→ K1:14\nTEXT: \nTEXT:W·123\nNEWLINE:MACHINE_ENABLE\nNEWLINE:TB7:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32175,7 +32178,7 @@
         <v>W·124</v>
       </c>
       <c r="B56" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C56" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·124\nNEWLINE:MACHINE_ENABLE\nNEWLINE:→ K1:A1\nTEXT: \nTEXT:W·124\nNEWLINE:MACHINE_ENABLE\nNEWLINE:TB7:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32192,7 +32195,7 @@
         <v>W·125</v>
       </c>
       <c r="B57" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C57" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·125\nNEWLINE:MACHINE_ENABLE\nNEWLINE:→ PL4:X1\nTEXT: \nTEXT:W·125\nNEWLINE:MACHINE_ENABLE\nNEWLINE:TB7:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32209,7 +32212,7 @@
         <v>W·151</v>
       </c>
       <c r="B58" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C58" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·151\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P12:8\nTEXT: \nTEXT:W·151\nNEWLINE:ESTOP_LOOP\nNEWLINE:P7:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32226,7 +32229,7 @@
         <v>W·152</v>
       </c>
       <c r="B59" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C59" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·152\nNEWLINE:24V_LOGIC\nNEWLINE:→ P12:7\nTEXT: \nTEXT:W·152\nNEWLINE:24V_LOGIC\nNEWLINE:P7:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32243,7 +32246,7 @@
         <v>W·153</v>
       </c>
       <c r="B60" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C60" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·153\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ P12:6\nTEXT: \nTEXT:W·153\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:P7:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32260,7 +32263,7 @@
         <v>W·154</v>
       </c>
       <c r="B61" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C61" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·154\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P12:5\nTEXT: \nTEXT:W·154\nNEWLINE:ESTOP_LOOP\nNEWLINE:P7:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32277,7 +32280,7 @@
         <v>W·155</v>
       </c>
       <c r="B62" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C62" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·155\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ S2:21\nTEXT: \nTEXT:W·155\nNEWLINE:ESTOP_LOOP\nNEWLINE:J12:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32294,7 +32297,7 @@
         <v>W·156</v>
       </c>
       <c r="B63" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C63" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·156\nNEWLINE:24V_LOGIC\nNEWLINE:→ S2:13\nTEXT: \nTEXT:W·156\nNEWLINE:24V_LOGIC\nNEWLINE:J12:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32311,7 +32314,7 @@
         <v>W·157</v>
       </c>
       <c r="B64" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C64" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·157\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ J12:6\nTEXT: \nTEXT:W·157\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:PL2:X2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32328,7 +32331,7 @@
         <v>W·158</v>
       </c>
       <c r="B65" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C65" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·158\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J12:5\nTEXT: \nTEXT:W·158\nNEWLINE:ESTOP_LOOP\nNEWLINE:S2:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32345,7 +32348,7 @@
         <v>W·159</v>
       </c>
       <c r="B66" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C66" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·159\nNEWLINE:24V_LOGIC\nNEWLINE:→ PL2:X1\nTEXT: \nTEXT:W·159\nNEWLINE:24V_LOGIC\nNEWLINE:S2:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32362,7 +32365,7 @@
         <v>W·161</v>
       </c>
       <c r="B67" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C67" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·161\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P12:4\nTEXT: \nTEXT:W·161\nNEWLINE:ESTOP_LOOP\nNEWLINE:P7:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32379,7 +32382,7 @@
         <v>W·162</v>
       </c>
       <c r="B68" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C68" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·162\nNEWLINE:24V_LOGIC\nNEWLINE:→ P12:3\nTEXT: \nTEXT:W·162\nNEWLINE:24V_LOGIC\nNEWLINE:P7:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32396,7 +32399,7 @@
         <v>W·163</v>
       </c>
       <c r="B69" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C69" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·163\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ P12:2\nTEXT: \nTEXT:W·163\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:P7:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32413,7 +32416,7 @@
         <v>W·164</v>
       </c>
       <c r="B70" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C70" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·164\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P12:1\nTEXT: \nTEXT:W·164\nNEWLINE:ESTOP_LOOP\nNEWLINE:P7:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32430,7 +32433,7 @@
         <v>W·165</v>
       </c>
       <c r="B71" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C71" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·165\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J13:4\nTEXT: \nTEXT:W·165\nNEWLINE:ESTOP_LOOP\nNEWLINE:P12:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32447,7 +32450,7 @@
         <v>W·166</v>
       </c>
       <c r="B72" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C72" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·166\nNEWLINE:24V_LOGIC\nNEWLINE:→ J13:3\nTEXT: \nTEXT:W·166\nNEWLINE:24V_LOGIC\nNEWLINE:P12:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32464,7 +32467,7 @@
         <v>W·167</v>
       </c>
       <c r="B73" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C73" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·167\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ J13:2\nTEXT: \nTEXT:W·167\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:P12:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32481,7 +32484,7 @@
         <v>W·168</v>
       </c>
       <c r="B74" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C74" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·168\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J13:1\nTEXT: \nTEXT:W·168\nNEWLINE:ESTOP_LOOP\nNEWLINE:P12:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32498,7 +32501,7 @@
         <v>W·169</v>
       </c>
       <c r="B75" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C75" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·169\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P17:4\nTEXT: \nTEXT:W·169\nNEWLINE:ESTOP_LOOP\nNEWLINE:P13:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32515,7 +32518,7 @@
         <v>W·170</v>
       </c>
       <c r="B76" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C76" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·170\nNEWLINE:24V_LOGIC\nNEWLINE:→ P17:3\nTEXT: \nTEXT:W·170\nNEWLINE:24V_LOGIC\nNEWLINE:P13:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32532,7 +32535,7 @@
         <v>W·171</v>
       </c>
       <c r="B77" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C77" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·171\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ P17:2\nTEXT: \nTEXT:W·171\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:P13:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32549,7 +32552,7 @@
         <v>W·172</v>
       </c>
       <c r="B78" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C78" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·172\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ P17:1\nTEXT: \nTEXT:W·172\nNEWLINE:ESTOP_LOOP\nNEWLINE:P13:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32566,7 +32569,7 @@
         <v>W·173</v>
       </c>
       <c r="B79" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C79" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·173\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ S3:21\nTEXT: \nTEXT:W·173\nNEWLINE:ESTOP_LOOP\nNEWLINE:J17:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32583,7 +32586,7 @@
         <v>W·174</v>
       </c>
       <c r="B80" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C80" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·174\nNEWLINE:24V_LOGIC\nNEWLINE:→ S3:13\nTEXT: \nTEXT:W·174\nNEWLINE:24V_LOGIC\nNEWLINE:J17:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32600,7 +32603,7 @@
         <v>W·175</v>
       </c>
       <c r="B81" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C81" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·175\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:→ J17:2\nTEXT: \nTEXT:W·175\nNEWLINE:ESTOP_INDICATOR\nNEWLINE:PL3:X2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32617,7 +32620,7 @@
         <v>W·176</v>
       </c>
       <c r="B82" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C82" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·176\nNEWLINE:ESTOP_LOOP\nNEWLINE:→ J17:1\nTEXT: \nTEXT:W·176\nNEWLINE:ESTOP_LOOP\nNEWLINE:S3:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32634,7 +32637,7 @@
         <v>W·177</v>
       </c>
       <c r="B83" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C83" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·177\nNEWLINE:24V_LOGIC\nNEWLINE:→ PL3:X1\nTEXT: \nTEXT:W·177\nNEWLINE:24V_LOGIC\nNEWLINE:S3:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32651,7 +32654,7 @@
         <v>W·201</v>
       </c>
       <c r="B84" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C84" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·201\nNEWLINE:24V_LOGIC\nNEWLINE:→ TB11:1\nTEXT: \nTEXT:W·201\nNEWLINE:24V_LOGIC\nNEWLINE:PS4:V+1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32668,7 +32671,7 @@
         <v>W·202</v>
       </c>
       <c r="B85" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C85" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·202\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB11:13\nTEXT: \nTEXT:W·202\nNEWLINE:0V_LOGIC\nNEWLINE:PS4:V-1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32685,7 +32688,7 @@
         <v>W·203</v>
       </c>
       <c r="B86" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C86" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·203\nNEWLINE:24V_LOGIC\nNEWLINE:→ MESA:TB3:22\nTEXT: \nTEXT:W·203\nNEWLINE:24V_LOGIC\nNEWLINE:TB11:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32702,7 +32705,7 @@
         <v>W·204</v>
       </c>
       <c r="B87" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C87" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·204\nNEWLINE:0V_LOGIC\nNEWLINE:→ MESA:TB3:24\nTEXT: \nTEXT:W·204\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32719,7 +32722,7 @@
         <v>W·205</v>
       </c>
       <c r="B88" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C88" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·205\nNEWLINE:24V_LOGIC\nNEWLINE:→ MESA:TB1:5\nTEXT: \nTEXT:W·205\nNEWLINE:24V_LOGIC\nNEWLINE:TB11:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32736,7 +32739,7 @@
         <v>W·206</v>
       </c>
       <c r="B89" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C89" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·206\nNEWLINE:0V_LOGIC\nNEWLINE:→ MESA:TB1:8\nTEXT: \nTEXT:W·206\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32753,7 +32756,7 @@
         <v>W·207</v>
       </c>
       <c r="B90" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C90" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·207\nNEWLINE:FAN_PWR\nNEWLINE:→ FANS1:1\nTEXT: \nTEXT:W·207\nNEWLINE:FAN_PWR\nNEWLINE:TB11:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32770,7 +32773,7 @@
         <v>W·208</v>
       </c>
       <c r="B91" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C91" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·208\nNEWLINE:0V_LOGIC\nNEWLINE:→ FANS1:2\nTEXT: \nTEXT:W·208\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32787,7 +32790,7 @@
         <v>W·209</v>
       </c>
       <c r="B92" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C92" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·209\nNEWLINE:24V_LOGIC\nNEWLINE:→ J2:1\nTEXT: \nTEXT:W·209\nNEWLINE:24V_LOGIC\nNEWLINE:TB11:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32804,7 +32807,7 @@
         <v>W·210</v>
       </c>
       <c r="B93" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C93" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·210\nNEWLINE:0V_LOGIC\nNEWLINE:→ J2:2\nTEXT: \nTEXT:W·210\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32821,7 +32824,7 @@
         <v>W·211</v>
       </c>
       <c r="B94" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C94" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·211\nNEWLINE:24V_LOGIC\nNEWLINE:→ TI1:V+\nTEXT: \nTEXT:W·211\nNEWLINE:24V_LOGIC\nNEWLINE:TB11:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32838,7 +32841,7 @@
         <v>W·212</v>
       </c>
       <c r="B95" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C95" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·212\nNEWLINE:0V_LOGIC\nNEWLINE:→ TI1:V-\nTEXT: \nTEXT:W·212\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32855,7 +32858,7 @@
         <v>W·213</v>
       </c>
       <c r="B96" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C96" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·213\nNEWLINE:24V_LOGIC\nNEWLINE:→ J4:2\nTEXT: \nTEXT:W·213\nNEWLINE:24V_LOGIC\nNEWLINE:MESA:TB6:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32872,7 +32875,7 @@
         <v>W·214</v>
       </c>
       <c r="B97" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C97" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·214\nNEWLINE:0V_LOGIC\nNEWLINE:→ J4:1\nTEXT: \nTEXT:W·214\nNEWLINE:0V_LOGIC\nNEWLINE:TB11:24→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32889,7 +32892,7 @@
         <v>W·215</v>
       </c>
       <c r="B98" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C98" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·215\nNEWLINE:TI1_VSENSE\nNEWLINE:→ TI1:SIG\nTEXT: \nTEXT:W·215\nNEWLINE:TI1_VSENSE\nNEWLINE:MESA:TB6:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32906,7 +32909,7 @@
         <v>W·301</v>
       </c>
       <c r="B99" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C99" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·301\nNEWLINE:24V_LOGIC\nNEWLINE:→ P10:2\nTEXT: \nTEXT:W·301\nNEWLINE:24V_LOGIC\nNEWLINE:P2:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32923,7 +32926,7 @@
         <v>W·302</v>
       </c>
       <c r="B100" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C100" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·302\nNEWLINE:0V_LOGIC\nNEWLINE:→ P10:1\nTEXT: \nTEXT:W·302\nNEWLINE:0V_LOGIC\nNEWLINE:P2:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32940,7 +32943,7 @@
         <v>W·303</v>
       </c>
       <c r="B101" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C101" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·303\nNEWLINE:24V_LOGIC\nNEWLINE:→ TB51:1\nTEXT: \nTEXT:W·303\nNEWLINE:24V_LOGIC\nNEWLINE:J10:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32957,7 +32960,7 @@
         <v>W·304</v>
       </c>
       <c r="B102" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C102" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·304\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB52:1\nTEXT: \nTEXT:W·304\nNEWLINE:0V_LOGIC\nNEWLINE:J10:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32974,7 +32977,7 @@
         <v>W·305</v>
       </c>
       <c r="B103" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C103" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·305\nNEWLINE:24V_LOGIC\nNEWLINE:→ J21:1\nTEXT: \nTEXT:W·305\nNEWLINE:24V_LOGIC\nNEWLINE:TB51:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -32991,7 +32994,7 @@
         <v>W·306</v>
       </c>
       <c r="B104" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C104" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·306\nNEWLINE:0V_LOGIC\nNEWLINE:→ J21:2\nTEXT: \nTEXT:W·306\nNEWLINE:0V_LOGIC\nNEWLINE:TB52:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33008,7 +33011,7 @@
         <v>W·307</v>
       </c>
       <c r="B105" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C105" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·307\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS1\nTEXT: \nTEXT:W·307\nNEWLINE:LIMIT_PWR\nNEWLINE:TB51:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33025,7 +33028,7 @@
         <v>W·308</v>
       </c>
       <c r="B106" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C106" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·308\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS1\nTEXT: \nTEXT:W·308\nNEWLINE:LIMIT_GND\nNEWLINE:TB52:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33042,7 +33045,7 @@
         <v>W·309</v>
       </c>
       <c r="B107" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C107" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·309\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS2\nTEXT: \nTEXT:W·309\nNEWLINE:LIMIT_PWR\nNEWLINE:TB51:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33059,7 +33062,7 @@
         <v>W·310</v>
       </c>
       <c r="B108" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C108" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·310\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS2\nTEXT: \nTEXT:W·310\nNEWLINE:LIMIT_GND\nNEWLINE:TB52:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33076,7 +33079,7 @@
         <v>W·311</v>
       </c>
       <c r="B109" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C109" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·311\nNEWLINE:LIMIT_PWR\nNEWLINE:→ HS1\nTEXT: \nTEXT:W·311\nNEWLINE:LIMIT_PWR\nNEWLINE:TB51:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33093,7 +33096,7 @@
         <v>W·312</v>
       </c>
       <c r="B110" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C110" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·312\nNEWLINE:LIMIT_GND\nNEWLINE:→ HS1\nTEXT: \nTEXT:W·312\nNEWLINE:LIMIT_GND\nNEWLINE:TB52:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33110,7 +33113,7 @@
         <v>W·313</v>
       </c>
       <c r="B111" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C111" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·313\nNEWLINE:LIMIT_PWR\nNEWLINE:→ HS2\nTEXT: \nTEXT:W·313\nNEWLINE:LIMIT_PWR\nNEWLINE:TB51:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33127,7 +33130,7 @@
         <v>W·314</v>
       </c>
       <c r="B112" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C112" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·314\nNEWLINE:LIMIT_GND\nNEWLINE:→ HS2\nTEXT: \nTEXT:W·314\nNEWLINE:LIMIT_GND\nNEWLINE:TB52:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33144,7 +33147,7 @@
         <v>W·315</v>
       </c>
       <c r="B113" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C113" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·315\nNEWLINE:PROBE_PWR\nNEWLINE:→ TP1\nTEXT: \nTEXT:W·315\nNEWLINE:PROBE_PWR\nNEWLINE:TB51:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33161,7 +33164,7 @@
         <v>W·317</v>
       </c>
       <c r="B114" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C114" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·317\nNEWLINE:24V_LOGIC\nNEWLINE:→ P20:2\nTEXT: \nTEXT:W·317\nNEWLINE:24V_LOGIC\nNEWLINE:P21:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33178,7 +33181,7 @@
         <v>W·318</v>
       </c>
       <c r="B115" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C115" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·318\nNEWLINE:0V_LOGIC\nNEWLINE:→ P20:1\nTEXT: \nTEXT:W·318\nNEWLINE:0V_LOGIC\nNEWLINE:P21:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33195,7 +33198,7 @@
         <v>W·319</v>
       </c>
       <c r="B116" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C116" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·319\nNEWLINE:24V_LOGIC\nNEWLINE:→ TB53:1\nTEXT: \nTEXT:W·319\nNEWLINE:24V_LOGIC\nNEWLINE:J20:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33212,7 +33215,7 @@
         <v>W·320</v>
       </c>
       <c r="B117" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C117" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·320\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB54:1\nTEXT: \nTEXT:W·320\nNEWLINE:0V_LOGIC\nNEWLINE:J20:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33229,7 +33232,7 @@
         <v>W·321</v>
       </c>
       <c r="B118" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C118" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·321\nNEWLINE:24V_LOGIC\nNEWLINE:→ J25:1\nTEXT: \nTEXT:W·321\nNEWLINE:24V_LOGIC\nNEWLINE:TB53:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33246,7 +33249,7 @@
         <v>W·322</v>
       </c>
       <c r="B119" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C119" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·322\nNEWLINE:0V_LOGIC\nNEWLINE:→ J25:2\nTEXT: \nTEXT:W·322\nNEWLINE:0V_LOGIC\nNEWLINE:TB54:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33263,7 +33266,7 @@
         <v>W·323</v>
       </c>
       <c r="B120" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C120" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·323\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS3\nTEXT: \nTEXT:W·323\nNEWLINE:LIMIT_PWR\nNEWLINE:TB53:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33280,7 +33283,7 @@
         <v>W·324</v>
       </c>
       <c r="B121" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C121" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·324\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS3\nTEXT: \nTEXT:W·324\nNEWLINE:LIMIT_GND\nNEWLINE:TB54:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33297,7 +33300,7 @@
         <v>W·325</v>
       </c>
       <c r="B122" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C122" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·325\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS4\nTEXT: \nTEXT:W·325\nNEWLINE:LIMIT_PWR\nNEWLINE:TB53:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33314,7 +33317,7 @@
         <v>W·326</v>
       </c>
       <c r="B123" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C123" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·326\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS4\nTEXT: \nTEXT:W·326\nNEWLINE:LIMIT_GND\nNEWLINE:TB54:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33331,7 +33334,7 @@
         <v>W·327</v>
       </c>
       <c r="B124" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C124" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·327\nNEWLINE:LIMIT_PWR\nNEWLINE:→ HS3\nTEXT: \nTEXT:W·327\nNEWLINE:LIMIT_PWR\nNEWLINE:TB53:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33348,7 +33351,7 @@
         <v>W·328</v>
       </c>
       <c r="B125" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C125" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·328\nNEWLINE:LIMIT_GND\nNEWLINE:→ HS3\nTEXT: \nTEXT:W·328\nNEWLINE:LIMIT_GND\nNEWLINE:TB54:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33365,7 +33368,7 @@
         <v>W·329</v>
       </c>
       <c r="B126" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C126" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·329\nNEWLINE:24V_LOGIC\nNEWLINE:→ P29:2\nTEXT: \nTEXT:W·329\nNEWLINE:24V_LOGIC\nNEWLINE:P25:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33382,7 +33385,7 @@
         <v>W·330</v>
       </c>
       <c r="B127" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C127" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·330\nNEWLINE:0V_LOGIC\nNEWLINE:→ P29:1\nTEXT: \nTEXT:W·330\nNEWLINE:0V_LOGIC\nNEWLINE:P25:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33399,7 +33402,7 @@
         <v>W·331</v>
       </c>
       <c r="B128" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C128" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·331\nNEWLINE:24V_LOGIC\nNEWLINE:→ TB57:1\nTEXT: \nTEXT:W·331\nNEWLINE:24V_LOGIC\nNEWLINE:J29:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33416,7 +33419,7 @@
         <v>W·332</v>
       </c>
       <c r="B129" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C129" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·332\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB58:1\nTEXT: \nTEXT:W·332\nNEWLINE:0V_LOGIC\nNEWLINE:J29:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33433,7 +33436,7 @@
         <v>W·333</v>
       </c>
       <c r="B130" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C130" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·333\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS5\nTEXT: \nTEXT:W·333\nNEWLINE:LIMIT_PWR\nNEWLINE:TB57:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33450,7 +33453,7 @@
         <v>W·334</v>
       </c>
       <c r="B131" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C131" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·334\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS5\nTEXT: \nTEXT:W·334\nNEWLINE:LIMIT_GND\nNEWLINE:TB58:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33467,7 +33470,7 @@
         <v>W·335</v>
       </c>
       <c r="B132" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C132" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·335\nNEWLINE:LIMIT_PWR\nNEWLINE:→ LS6\nTEXT: \nTEXT:W·335\nNEWLINE:LIMIT_PWR\nNEWLINE:TB57:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33484,7 +33487,7 @@
         <v>W·336</v>
       </c>
       <c r="B133" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C133" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·336\nNEWLINE:LIMIT_GND\nNEWLINE:→ LS6\nTEXT: \nTEXT:W·336\nNEWLINE:LIMIT_GND\nNEWLINE:TB58:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33501,7 +33504,7 @@
         <v>W·337</v>
       </c>
       <c r="B134" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C134" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·337\nNEWLINE:LIMIT_PWR\nNEWLINE:→ HS4\nTEXT: \nTEXT:W·337\nNEWLINE:LIMIT_PWR\nNEWLINE:TB57:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33518,7 +33521,7 @@
         <v>W·338</v>
       </c>
       <c r="B135" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C135" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·338\nNEWLINE:LIMIT_GND\nNEWLINE:→ HS4\nTEXT: \nTEXT:W·338\nNEWLINE:LIMIT_GND\nNEWLINE:TB58:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33535,7 +33538,7 @@
         <v>W·391</v>
       </c>
       <c r="B136" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C136" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·391\nNEWLINE:24V_LOGIC\nNEWLINE:→ K2\nTEXT: \nTEXT:W·391\nNEWLINE:24V_LOGIC\nNEWLINE:P4:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33552,7 +33555,7 @@
         <v>W·392</v>
       </c>
       <c r="B137" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C137" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·392\nNEWLINE:0V_LOGIC\nNEWLINE:→ K2\nTEXT: \nTEXT:W·392\nNEWLINE:0V_LOGIC\nNEWLINE:P4:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33569,7 +33572,7 @@
         <v>W·401</v>
       </c>
       <c r="B138" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C138" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·401\nNEWLINE:48V_LOGIC\nNEWLINE:→ J8:2\nTEXT: \nTEXT:W·401\nNEWLINE:48V_LOGIC\nNEWLINE:PS5:V+1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33586,7 +33589,7 @@
         <v>W·402</v>
       </c>
       <c r="B139" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C139" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·402\nNEWLINE:0V_LOGIC\nNEWLINE:→ J8:1\nTEXT: \nTEXT:W·402\nNEWLINE:0V_LOGIC\nNEWLINE:PS5:V-1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33603,7 +33606,7 @@
         <v>W·403</v>
       </c>
       <c r="B140" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C140" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·403\nNEWLINE:48V_LOGIC\nNEWLINE:→ J8:4\nTEXT: \nTEXT:W·403\nNEWLINE:48V_LOGIC\nNEWLINE:PS6:V+1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33620,7 +33623,7 @@
         <v>W·404</v>
       </c>
       <c r="B141" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C141" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·404\nNEWLINE:0V_LOGIC\nNEWLINE:→ J8:3\nTEXT: \nTEXT:W·404\nNEWLINE:0V_LOGIC\nNEWLINE:PS6:V-1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33637,7 +33640,7 @@
         <v>W·405</v>
       </c>
       <c r="B142" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C142" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·405\nNEWLINE:48V_LOGIC\nNEWLINE:→ SD2:DC+\nTEXT: \nTEXT:W·405\nNEWLINE:48V_LOGIC\nNEWLINE:PS6:V+2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33654,7 +33657,7 @@
         <v>W·406</v>
       </c>
       <c r="B143" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C143" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·406\nNEWLINE:0V_LOGIC\nNEWLINE:→ SD2:DC-\nTEXT: \nTEXT:W·406\nNEWLINE:0V_LOGIC\nNEWLINE:PS6:V-2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33671,7 +33674,7 @@
         <v>W·451</v>
       </c>
       <c r="B144" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C144" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·451\nNEWLINE:48V_LOGIC\nNEWLINE:→ P18:2\nTEXT: \nTEXT:W·451\nNEWLINE:48V_LOGIC\nNEWLINE:P8:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33688,7 +33691,7 @@
         <v>W·452</v>
       </c>
       <c r="B145" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C145" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·452\nNEWLINE:0V_LOGIC\nNEWLINE:→ P18:1\nTEXT: \nTEXT:W·452\nNEWLINE:0V_LOGIC\nNEWLINE:P8:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33705,7 +33708,7 @@
         <v>W·453</v>
       </c>
       <c r="B146" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C146" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·453\nNEWLINE:48V_LOGIC\nNEWLINE:→ P18:4\nTEXT: \nTEXT:W·453\nNEWLINE:48V_LOGIC\nNEWLINE:P8:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33722,7 +33725,7 @@
         <v>W·454</v>
       </c>
       <c r="B147" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C147" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·454\nNEWLINE:0V_LOGIC\nNEWLINE:→ P18:3\nTEXT: \nTEXT:W·454\nNEWLINE:0V_LOGIC\nNEWLINE:P8:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33739,7 +33742,7 @@
         <v>W·455</v>
       </c>
       <c r="B148" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C148" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·455\nNEWLINE:48V_LOGIC\nNEWLINE:→ J15:1\nTEXT: \nTEXT:W·455\nNEWLINE:48V_LOGIC\nNEWLINE:J18:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33756,7 +33759,7 @@
         <v>W·456</v>
       </c>
       <c r="B149" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C149" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·456\nNEWLINE:0V_LOGIC\nNEWLINE:→ J15:2\nTEXT: \nTEXT:W·456\nNEWLINE:0V_LOGIC\nNEWLINE:J18:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33773,7 +33776,7 @@
         <v>W·457</v>
       </c>
       <c r="B150" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C150" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·457\nNEWLINE:48V_LOGIC\nNEWLINE:→ J15:4\nTEXT: \nTEXT:W·457\nNEWLINE:48V_LOGIC\nNEWLINE:J18:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33790,7 +33793,7 @@
         <v>W·458</v>
       </c>
       <c r="B151" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C151" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·458\nNEWLINE:0V_LOGIC\nNEWLINE:→ J15:3\nTEXT: \nTEXT:W·458\nNEWLINE:0V_LOGIC\nNEWLINE:J18:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33807,7 +33810,7 @@
         <v>W·459</v>
       </c>
       <c r="B152" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C152" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·459\nNEWLINE:48V_LOGIC\nNEWLINE:→ P20:4\nTEXT: \nTEXT:W·459\nNEWLINE:48V_LOGIC\nNEWLINE:P15:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33824,7 +33827,7 @@
         <v>W·460</v>
       </c>
       <c r="B153" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C153" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·460\nNEWLINE:0V_LOGIC\nNEWLINE:→ P20:3\nTEXT: \nTEXT:W·460\nNEWLINE:0V_LOGIC\nNEWLINE:P15:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33841,7 +33844,7 @@
         <v>W·461</v>
       </c>
       <c r="B154" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C154" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·461\nNEWLINE:48V_LOGIC\nNEWLINE:→ P29:4\nTEXT: \nTEXT:W·461\nNEWLINE:48V_LOGIC\nNEWLINE:P15:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33858,7 +33861,7 @@
         <v>W·462</v>
       </c>
       <c r="B155" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C155" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·462\nNEWLINE:0V_LOGIC\nNEWLINE:→ P29:3\nTEXT: \nTEXT:W·462\nNEWLINE:0V_LOGIC\nNEWLINE:P15:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33875,7 +33878,7 @@
         <v>W·463</v>
       </c>
       <c r="B156" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C156" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·463\nNEWLINE:48V_LOGIC\nNEWLINE:→ TB55:1\nTEXT: \nTEXT:W·463\nNEWLINE:48V_LOGIC\nNEWLINE:J20:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33892,7 +33895,7 @@
         <v>W·464</v>
       </c>
       <c r="B157" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C157" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·464\nNEWLINE:0V_LOGIC\nNEWLINE:→ TB56:1\nTEXT: \nTEXT:W·464\nNEWLINE:0V_LOGIC\nNEWLINE:J20:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33909,7 +33912,7 @@
         <v>W·465</v>
       </c>
       <c r="B158" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C158" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·465\nNEWLINE:STEP_IO_PWR\nNEWLINE:→ IM1:VDC+\nTEXT: \nTEXT:W·465\nNEWLINE:STEP_IO_PWR\nNEWLINE:TB55:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33926,7 +33929,7 @@
         <v>W·466</v>
       </c>
       <c r="B159" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C159" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·466\nNEWLINE:STEP_IO_GND\nNEWLINE:→ IM1:GND\nTEXT: \nTEXT:W·466\nNEWLINE:STEP_IO_GND\nNEWLINE:TB56:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33943,7 +33946,7 @@
         <v>W·467</v>
       </c>
       <c r="B160" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C160" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·467\nNEWLINE:STEP_IO_PWR\nNEWLINE:→ IM2:VDC+\nTEXT: \nTEXT:W·467\nNEWLINE:STEP_IO_PWR\nNEWLINE:TB55:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33960,7 +33963,7 @@
         <v>W·468</v>
       </c>
       <c r="B161" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C161" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·468\nNEWLINE:STEP_IO_GND\nNEWLINE:→ IM2:GND\nTEXT: \nTEXT:W·468\nNEWLINE:STEP_IO_GND\nNEWLINE:TB56:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33977,7 +33980,7 @@
         <v>W·473</v>
       </c>
       <c r="B162" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C162" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·473\nNEWLINE:STEP_IO_PWR\nNEWLINE:→ IM3:VDC+\nTEXT: \nTEXT:W·473\nNEWLINE:STEP_IO_PWR\nNEWLINE:J29:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -33994,7 +33997,7 @@
         <v>W·474</v>
       </c>
       <c r="B163" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C163" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·474\nNEWLINE:STEP_IO_GND\nNEWLINE:→ IM3:GND\nTEXT: \nTEXT:W·474\nNEWLINE:STEP_IO_GND\nNEWLINE:J29:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34011,7 +34014,7 @@
         <v>W·501</v>
       </c>
       <c r="B164" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C164" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·501\nNEWLINE:SPINDLE_RS+\nNEWLINE:→ J5:2\nTEXT: \nTEXT:W·501\nNEWLINE:SPINDLE_RS+\nNEWLINE:MESA:TB3:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34028,7 +34031,7 @@
         <v>W·502</v>
       </c>
       <c r="B165" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C165" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·502\nNEWLINE:SPINDLE_RS-\nNEWLINE:→ J5:1\nTEXT: \nTEXT:W·502\nNEWLINE:SPINDLE_RS-\nNEWLINE:MESA:TB3:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34045,7 +34048,7 @@
         <v>W·503</v>
       </c>
       <c r="B166" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C166" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·503\nNEWLINE:Y1_STEP-\nNEWLINE:→ J1:1\nTEXT: \nTEXT:W·503\nNEWLINE:Y1_STEP-\nNEWLINE:MESA:TB2:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34062,7 +34065,7 @@
         <v>W·504</v>
       </c>
       <c r="B167" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C167" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·504\nNEWLINE:Y1_STEP+\nNEWLINE:→ J1:2\nTEXT: \nTEXT:W·504\nNEWLINE:Y1_STEP+\nNEWLINE:MESA:TB2:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34079,7 +34082,7 @@
         <v>W·505</v>
       </c>
       <c r="B168" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C168" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·505\nNEWLINE:Y1_DIR-\nNEWLINE:→ J1:3\nTEXT: \nTEXT:W·505\nNEWLINE:Y1_DIR-\nNEWLINE:MESA:TB2:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34096,7 +34099,7 @@
         <v>W·506</v>
       </c>
       <c r="B169" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C169" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·506\nNEWLINE:Y1_DIR+\nNEWLINE:→ J1:4\nTEXT: \nTEXT:W·506\nNEWLINE:Y1_DIR+\nNEWLINE:MESA:TB2:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34113,7 +34116,7 @@
         <v>W·507</v>
       </c>
       <c r="B170" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C170" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·507\nNEWLINE:Y2_STEP-\nNEWLINE:→ J1:5\nTEXT: \nTEXT:W·507\nNEWLINE:Y2_STEP-\nNEWLINE:MESA:TB2:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34130,7 +34133,7 @@
         <v>W·508</v>
       </c>
       <c r="B171" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C171" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·508\nNEWLINE:Y2_STEP+\nNEWLINE:→ J1:6\nTEXT: \nTEXT:W·508\nNEWLINE:Y2_STEP+\nNEWLINE:MESA:TB2:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34147,7 +34150,7 @@
         <v>W·509</v>
       </c>
       <c r="B172" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C172" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·509\nNEWLINE:Y2_DIR-\nNEWLINE:→ J1:7\nTEXT: \nTEXT:W·509\nNEWLINE:Y2_DIR-\nNEWLINE:MESA:TB2:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34164,7 +34167,7 @@
         <v>W·510</v>
       </c>
       <c r="B173" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C173" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·510\nNEWLINE:Y2_DIR+\nNEWLINE:→ J1:8\nTEXT: \nTEXT:W·510\nNEWLINE:Y2_DIR+\nNEWLINE:MESA:TB2:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34181,7 +34184,7 @@
         <v>W·511</v>
       </c>
       <c r="B174" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C174" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·511\nNEWLINE:X_STEP-\nNEWLINE:→ J1:9\nTEXT: \nTEXT:W·511\nNEWLINE:X_STEP-\nNEWLINE:MESA:TB2:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34198,7 +34201,7 @@
         <v>W·512</v>
       </c>
       <c r="B175" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C175" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·512\nNEWLINE:X_STEP+\nNEWLINE:→ J1:10\nTEXT: \nTEXT:W·512\nNEWLINE:X_STEP+\nNEWLINE:MESA:TB2:15→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34215,7 +34218,7 @@
         <v>W·513</v>
       </c>
       <c r="B176" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C176" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·513\nNEWLINE:X_DIR-\nNEWLINE:→ J1:11\nTEXT: \nTEXT:W·513\nNEWLINE:X_DIR-\nNEWLINE:MESA:TB2:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34232,7 +34235,7 @@
         <v>W·514</v>
       </c>
       <c r="B177" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C177" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·514\nNEWLINE:X_DIR+\nNEWLINE:→ J1:12\nTEXT: \nTEXT:W·514\nNEWLINE:X_DIR+\nNEWLINE:MESA:TB2:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34249,7 +34252,7 @@
         <v>W·515</v>
       </c>
       <c r="B178" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C178" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·515\nNEWLINE:Z_STEP-\nNEWLINE:→ SD1:PUL-\nTEXT: \nTEXT:W·515\nNEWLINE:Z_STEP-\nNEWLINE:MESA:TB2:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34266,7 +34269,7 @@
         <v>W·516</v>
       </c>
       <c r="B179" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C179" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·516\nNEWLINE:Z_STEP+\nNEWLINE:→ SD1:PUL+\nTEXT: \nTEXT:W·516\nNEWLINE:Z_STEP+\nNEWLINE:MESA:TB2:21→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34283,7 +34286,7 @@
         <v>W·517</v>
       </c>
       <c r="B180" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C180" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·517\nNEWLINE:Z_DIR-\nNEWLINE:→ SD1:DIR-\nTEXT: \nTEXT:W·517\nNEWLINE:Z_DIR-\nNEWLINE:MESA:TB2:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34300,7 +34303,7 @@
         <v>W·518</v>
       </c>
       <c r="B181" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C181" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·518\nNEWLINE:Z_DIR+\nNEWLINE:→ SD1:DIR+\nTEXT: \nTEXT:W·518\nNEWLINE:Z_DIR+\nNEWLINE:MESA:TB2:23→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34317,7 +34320,7 @@
         <v>W·519</v>
       </c>
       <c r="B182" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C182" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·519\nNEWLINE:Z_A+\nNEWLINE:→ J3:8\nTEXT: \nTEXT:W·519\nNEWLINE:Z_A+\nNEWLINE:SD1:A+→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34334,7 +34337,7 @@
         <v>W·520</v>
       </c>
       <c r="B183" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C183" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·520\nNEWLINE:Z_A-\nNEWLINE:→ J3:7\nTEXT: \nTEXT:W·520\nNEWLINE:Z_A-\nNEWLINE:SD1:A-→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34351,7 +34354,7 @@
         <v>W·521</v>
       </c>
       <c r="B184" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C184" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·521\nNEWLINE:Z_B+\nNEWLINE:→ J3:6\nTEXT: \nTEXT:W·521\nNEWLINE:Z_B+\nNEWLINE:SD1:B+→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34368,7 +34371,7 @@
         <v>W·522</v>
       </c>
       <c r="B185" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C185" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·522\nNEWLINE:Z_B-\nNEWLINE:→ J3:5\nTEXT: \nTEXT:W·522\nNEWLINE:Z_B-\nNEWLINE:SD1:B-→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34385,7 +34388,7 @@
         <v>W·551</v>
       </c>
       <c r="B186" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C186" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·551\nNEWLINE:Y_MIN\nNEWLINE:→ J1:13\nTEXT: \nTEXT:W·551\nNEWLINE:Y_MIN\nNEWLINE:MESA:TB6:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34402,7 +34405,7 @@
         <v>W·552</v>
       </c>
       <c r="B187" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C187" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·552\nNEWLINE:Y_MAX\nNEWLINE:→ J1:14\nTEXT: \nTEXT:W·552\nNEWLINE:Y_MAX\nNEWLINE:MESA:TB6:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34419,7 +34422,7 @@
         <v>W·553</v>
       </c>
       <c r="B188" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C188" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·553\nNEWLINE:Y1_HOME\nNEWLINE:→ J1:15\nTEXT: \nTEXT:W·553\nNEWLINE:Y1_HOME\nNEWLINE:MESA:TB6:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34436,7 +34439,7 @@
         <v>W·554</v>
       </c>
       <c r="B189" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C189" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·554\nNEWLINE:Y2_HOME\nNEWLINE:→ J1:16\nTEXT: \nTEXT:W·554\nNEWLINE:Y2_HOME\nNEWLINE:MESA:TB6:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34453,7 +34456,7 @@
         <v>W·555</v>
       </c>
       <c r="B190" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C190" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·555\nNEWLINE:X_MIN\nNEWLINE:→ J1:17\nTEXT: \nTEXT:W·555\nNEWLINE:X_MIN\nNEWLINE:MESA:TB6:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34470,7 +34473,7 @@
         <v>W·556</v>
       </c>
       <c r="B191" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C191" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·556\nNEWLINE:X_MAX\nNEWLINE:→ J1:18\nTEXT: \nTEXT:W·556\nNEWLINE:X_MAX\nNEWLINE:MESA:TB6:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34487,7 +34490,7 @@
         <v>W·557</v>
       </c>
       <c r="B192" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C192" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·557\nNEWLINE:X_HOME\nNEWLINE:→ J1:19\nTEXT: \nTEXT:W·557\nNEWLINE:X_HOME\nNEWLINE:MESA:TB6:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34504,7 +34507,7 @@
         <v>W·558</v>
       </c>
       <c r="B193" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C193" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·558\nNEWLINE:Z_MIN\nNEWLINE:→ J1:20\nTEXT: \nTEXT:W·558\nNEWLINE:Z_MIN\nNEWLINE:MESA:TB6:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34521,7 +34524,7 @@
         <v>W·559</v>
       </c>
       <c r="B194" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C194" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·559\nNEWLINE:Z_MAX\nNEWLINE:→ J1:21\nTEXT: \nTEXT:W·559\nNEWLINE:Z_MAX\nNEWLINE:MESA:TB6:13→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34538,7 +34541,7 @@
         <v>W·560</v>
       </c>
       <c r="B195" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C195" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·560\nNEWLINE:Z_HOME\nNEWLINE:→ J1:22\nTEXT: \nTEXT:W·560\nNEWLINE:Z_HOME\nNEWLINE:MESA:TB6:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34555,7 +34558,7 @@
         <v>W·561</v>
       </c>
       <c r="B196" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C196" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·561\nNEWLINE:PROBE_IN\nNEWLINE:→ J1:23\nTEXT: \nTEXT:W·561\nNEWLINE:PROBE_IN\nNEWLINE:MESA:TB6:15→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34572,7 +34575,7 @@
         <v>W·563</v>
       </c>
       <c r="B197" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C197" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·563\nNEWLINE:FAN_PWM\nNEWLINE:→ FANS1:PWM\nTEXT: \nTEXT:W·563\nNEWLINE:FAN_PWM\nNEWLINE:MESA:TB6:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34589,7 +34592,7 @@
         <v>W·595</v>
       </c>
       <c r="B198" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C198" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·595\nNEWLINE:USB_HID\nNEWLINE:→ J39:USB1\nTEXT: \nTEXT:W·595\nNEWLINE:USB_HID\nNEWLINE:CPU1:USB1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34606,7 +34609,7 @@
         <v>W·596</v>
       </c>
       <c r="B199" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C199" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·596\nNEWLINE:USB_USER\nNEWLINE:→ J38:USB1\nTEXT: \nTEXT:W·596\nNEWLINE:USB_USER\nNEWLINE:CPU1:USB2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34623,7 +34626,7 @@
         <v>W·597</v>
       </c>
       <c r="B200" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C200" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·597\nNEWLINE:MONITOR\nNEWLINE:→ J37:HDMI\nTEXT: \nTEXT:W·597\nNEWLINE:MONITOR\nNEWLINE:CPU1:DP→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34640,7 +34643,7 @@
         <v>W·598</v>
       </c>
       <c r="B201" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C201" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·598\nNEWLINE:WIFI_EXT\nNEWLINE:→ RF1:1\nTEXT: \nTEXT:W·598\nNEWLINE:WIFI_EXT\nNEWLINE:CPU1:RF→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34657,7 +34660,7 @@
         <v>W·599</v>
       </c>
       <c r="B202" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C202" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·599\nNEWLINE:ETH_MESA\nNEWLINE:→ MESA:ETH\nTEXT: \nTEXT:W·599\nNEWLINE:ETH_MESA\nNEWLINE:CPU1:ETH→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34674,7 +34677,7 @@
         <v>W·603</v>
       </c>
       <c r="B203" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C203" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·603\nNEWLINE:Z_A+\nNEWLINE:→ P11:8\nTEXT: \nTEXT:W·603\nNEWLINE:Z_A+\nNEWLINE:P3:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34691,7 +34694,7 @@
         <v>W·604</v>
       </c>
       <c r="B204" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C204" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·604\nNEWLINE:Z_A-\nNEWLINE:→ P11:7\nTEXT: \nTEXT:W·604\nNEWLINE:Z_A-\nNEWLINE:P3:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34708,7 +34711,7 @@
         <v>W·605</v>
       </c>
       <c r="B205" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C205" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·605\nNEWLINE:Z_B+\nNEWLINE:→ P11:6\nTEXT: \nTEXT:W·605\nNEWLINE:Z_B+\nNEWLINE:P3:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34725,7 +34728,7 @@
         <v>W·606</v>
       </c>
       <c r="B206" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C206" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·606\nNEWLINE:Z_B-\nNEWLINE:→ P11:5\nTEXT: \nTEXT:W·606\nNEWLINE:Z_B-\nNEWLINE:P3:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34742,7 +34745,7 @@
         <v>W·607</v>
       </c>
       <c r="B207" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C207" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·607\nNEWLINE:Z_A+\nNEWLINE:→ J18:1\nTEXT: \nTEXT:W·607\nNEWLINE:Z_A+\nNEWLINE:J11:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34759,7 +34762,7 @@
         <v>W·608</v>
       </c>
       <c r="B208" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C208" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·608\nNEWLINE:Z_A-\nNEWLINE:→ J18:2\nTEXT: \nTEXT:W·608\nNEWLINE:Z_A-\nNEWLINE:J11:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34776,7 +34779,7 @@
         <v>W·609</v>
       </c>
       <c r="B209" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C209" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·609\nNEWLINE:Z_B+\nNEWLINE:→ J18:3\nTEXT: \nTEXT:W·609\nNEWLINE:Z_B+\nNEWLINE:J11:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34793,7 +34796,7 @@
         <v>W·610</v>
       </c>
       <c r="B210" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C210" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·610\nNEWLINE:Z_B-\nNEWLINE:→ J18:4\nTEXT: \nTEXT:W·610\nNEWLINE:Z_B-\nNEWLINE:J11:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34810,7 +34813,7 @@
         <v>W·611</v>
       </c>
       <c r="B211" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C211" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·611\nNEWLINE:Z_A+\nNEWLINE:→ P30:8\nTEXT: \nTEXT:W·611\nNEWLINE:Z_A+\nNEWLINE:P16:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34827,7 +34830,7 @@
         <v>W·612</v>
       </c>
       <c r="B212" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C212" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·612\nNEWLINE:Z_A-\nNEWLINE:→ P30:7\nTEXT: \nTEXT:W·612\nNEWLINE:Z_A-\nNEWLINE:P16:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34844,7 +34847,7 @@
         <v>W·613</v>
       </c>
       <c r="B213" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C213" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·613\nNEWLINE:Z_B+\nNEWLINE:→ P30:6\nTEXT: \nTEXT:W·613\nNEWLINE:Z_B+\nNEWLINE:P16:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34861,7 +34864,7 @@
         <v>W·614</v>
       </c>
       <c r="B214" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C214" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·614\nNEWLINE:Z_B-\nNEWLINE:→ P30:5\nTEXT: \nTEXT:W·614\nNEWLINE:Z_B-\nNEWLINE:P16:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34878,7 +34881,7 @@
         <v>W·623</v>
       </c>
       <c r="B215" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C215" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·623\nNEWLINE:Z_A+\nNEWLINE:→ SM1\nTEXT: \nTEXT:W·623\nNEWLINE:Z_A+\nNEWLINE:J30:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34895,7 +34898,7 @@
         <v>W·624</v>
       </c>
       <c r="B216" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C216" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·624\nNEWLINE:Z_A-\nNEWLINE:→ SM1\nTEXT: \nTEXT:W·624\nNEWLINE:Z_A-\nNEWLINE:J30:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34912,7 +34915,7 @@
         <v>W·625</v>
       </c>
       <c r="B217" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C217" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·625\nNEWLINE:Z_B+\nNEWLINE:→ SM1\nTEXT: \nTEXT:W·625\nNEWLINE:Z_B+\nNEWLINE:J30:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34929,7 +34932,7 @@
         <v>W·626</v>
       </c>
       <c r="B218" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C218" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·626\nNEWLINE:Z_B-\nNEWLINE:→ SM1\nTEXT: \nTEXT:W·626\nNEWLINE:Z_B-\nNEWLINE:J30:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34946,7 +34949,7 @@
         <v>W·627</v>
       </c>
       <c r="B219" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C219" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·627\nNEWLINE:SPINDLE_U\nNEWLINE:→ M1:1\nTEXT: \nTEXT:W·627\nNEWLINE:SPINDLE_U\nNEWLINE:VFD1:U→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34963,7 +34966,7 @@
         <v>W·628</v>
       </c>
       <c r="B220" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C220" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·628\nNEWLINE:SPINDLE_V\nNEWLINE:→ M1:2\nTEXT: \nTEXT:W·628\nNEWLINE:SPINDLE_V\nNEWLINE:VFD1:V→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34980,7 +34983,7 @@
         <v>W·629</v>
       </c>
       <c r="B221" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C221" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·629\nNEWLINE:SPINDLE_W\nNEWLINE:→ M1:3\nTEXT: \nTEXT:W·629\nNEWLINE:SPINDLE_W\nNEWLINE:VFD1:W→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -34997,7 +35000,7 @@
         <v>W·641</v>
       </c>
       <c r="B222" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C222" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·641\nNEWLINE:Y1_STEP-\nNEWLINE:→ P9:1\nTEXT: \nTEXT:W·641\nNEWLINE:Y1_STEP-\nNEWLINE:P1:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35014,7 +35017,7 @@
         <v>W·642</v>
       </c>
       <c r="B223" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C223" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·642\nNEWLINE:Y1_STEP+\nNEWLINE:→ P9:2\nTEXT: \nTEXT:W·642\nNEWLINE:Y1_STEP+\nNEWLINE:P1:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35031,7 +35034,7 @@
         <v>W·643</v>
       </c>
       <c r="B224" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C224" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·643\nNEWLINE:Y1_DIR-\nNEWLINE:→ P9:3\nTEXT: \nTEXT:W·643\nNEWLINE:Y1_DIR-\nNEWLINE:P1:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35048,7 +35051,7 @@
         <v>W·644</v>
       </c>
       <c r="B225" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C225" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·644\nNEWLINE:Y1_DIR+\nNEWLINE:→ P9:4\nTEXT: \nTEXT:W·644\nNEWLINE:Y1_DIR+\nNEWLINE:P1:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35065,7 +35068,7 @@
         <v>W·645</v>
       </c>
       <c r="B226" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C226" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·645\nNEWLINE:Y2_STEP-\nNEWLINE:→ P9:5\nTEXT: \nTEXT:W·645\nNEWLINE:Y2_STEP-\nNEWLINE:P1:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35082,7 +35085,7 @@
         <v>W·646</v>
       </c>
       <c r="B227" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C227" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·646\nNEWLINE:Y2_STEP+\nNEWLINE:→ P9:6\nTEXT: \nTEXT:W·646\nNEWLINE:Y2_STEP+\nNEWLINE:P1:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35099,7 +35102,7 @@
         <v>W·647</v>
       </c>
       <c r="B228" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C228" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·647\nNEWLINE:Y2_DIR-\nNEWLINE:→ P9:7\nTEXT: \nTEXT:W·647\nNEWLINE:Y2_DIR-\nNEWLINE:P1:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35116,7 +35119,7 @@
         <v>W·648</v>
       </c>
       <c r="B229" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C229" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·648\nNEWLINE:Y2_DIR+\nNEWLINE:→ P9:8\nTEXT: \nTEXT:W·648\nNEWLINE:Y2_DIR+\nNEWLINE:P1:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35133,7 +35136,7 @@
         <v>W·649</v>
       </c>
       <c r="B230" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C230" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·649\nNEWLINE:X_STEP-\nNEWLINE:→ P9:9\nTEXT: \nTEXT:W·649\nNEWLINE:X_STEP-\nNEWLINE:P1:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35150,7 +35153,7 @@
         <v>W·650</v>
       </c>
       <c r="B231" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C231" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·650\nNEWLINE:X_STEP+\nNEWLINE:→ P9:10\nTEXT: \nTEXT:W·650\nNEWLINE:X_STEP+\nNEWLINE:P1:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35167,7 +35170,7 @@
         <v>W·651</v>
       </c>
       <c r="B232" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C232" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·651\nNEWLINE:X_DIR-\nNEWLINE:→ P9:11\nTEXT: \nTEXT:W·651\nNEWLINE:X_DIR-\nNEWLINE:P1:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35184,7 +35187,7 @@
         <v>W·652</v>
       </c>
       <c r="B233" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C233" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·652\nNEWLINE:X_DIR+\nNEWLINE:→ P9:12\nTEXT: \nTEXT:W·652\nNEWLINE:X_DIR+\nNEWLINE:P1:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35201,7 +35204,7 @@
         <v>W·653</v>
       </c>
       <c r="B234" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C234" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·653\nNEWLINE:Y1_STEP-\nNEWLINE:→ J14:1\nTEXT: \nTEXT:W·653\nNEWLINE:Y1_STEP-\nNEWLINE:J9:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35218,7 +35221,7 @@
         <v>W·654</v>
       </c>
       <c r="B235" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C235" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·654\nNEWLINE:Y1_STEP+\nNEWLINE:→ J14:2\nTEXT: \nTEXT:W·654\nNEWLINE:Y1_STEP+\nNEWLINE:J9:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35235,7 +35238,7 @@
         <v>W·655</v>
       </c>
       <c r="B236" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C236" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·655\nNEWLINE:Y1_DIR-\nNEWLINE:→ J14:3\nTEXT: \nTEXT:W·655\nNEWLINE:Y1_DIR-\nNEWLINE:J9:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35252,7 +35255,7 @@
         <v>W·656</v>
       </c>
       <c r="B237" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C237" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·656\nNEWLINE:Y1_DIR+\nNEWLINE:→ J14:4\nTEXT: \nTEXT:W·656\nNEWLINE:Y1_DIR+\nNEWLINE:J9:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35269,7 +35272,7 @@
         <v>W·657</v>
       </c>
       <c r="B238" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C238" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·657\nNEWLINE:Y2_STEP-\nNEWLINE:→ J14:5\nTEXT: \nTEXT:W·657\nNEWLINE:Y2_STEP-\nNEWLINE:J9:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35286,7 +35289,7 @@
         <v>W·658</v>
       </c>
       <c r="B239" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C239" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·658\nNEWLINE:Y2_STEP+\nNEWLINE:→ J14:6\nTEXT: \nTEXT:W·658\nNEWLINE:Y2_STEP+\nNEWLINE:J9:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35303,7 +35306,7 @@
         <v>W·659</v>
       </c>
       <c r="B240" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C240" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·659\nNEWLINE:Y2_DIR-\nNEWLINE:→ J14:7\nTEXT: \nTEXT:W·659\nNEWLINE:Y2_DIR-\nNEWLINE:J9:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35320,7 +35323,7 @@
         <v>W·660</v>
       </c>
       <c r="B241" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C241" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·660\nNEWLINE:Y2_DIR+\nNEWLINE:→ J14:8\nTEXT: \nTEXT:W·660\nNEWLINE:Y2_DIR+\nNEWLINE:J9:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35337,7 +35340,7 @@
         <v>W·661</v>
       </c>
       <c r="B242" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C242" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·661\nNEWLINE:X_STEP-\nNEWLINE:→ J14:9\nTEXT: \nTEXT:W·661\nNEWLINE:X_STEP-\nNEWLINE:J9:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35354,7 +35357,7 @@
         <v>W·662</v>
       </c>
       <c r="B243" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C243" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·662\nNEWLINE:X_STEP+\nNEWLINE:→ J14:10\nTEXT: \nTEXT:W·662\nNEWLINE:X_STEP+\nNEWLINE:J9:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35371,7 +35374,7 @@
         <v>W·663</v>
       </c>
       <c r="B244" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C244" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·663\nNEWLINE:X_DIR-\nNEWLINE:→ J14:11\nTEXT: \nTEXT:W·663\nNEWLINE:X_DIR-\nNEWLINE:J9:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35388,7 +35391,7 @@
         <v>W·664</v>
       </c>
       <c r="B245" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C245" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·664\nNEWLINE:X_DIR+\nNEWLINE:→ J14:12\nTEXT: \nTEXT:W·664\nNEWLINE:X_DIR+\nNEWLINE:J9:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35405,7 +35408,7 @@
         <v>W·665</v>
       </c>
       <c r="B246" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C246" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·665\nNEWLINE:Y1_STEP-\nNEWLINE:→ P19:1\nTEXT: \nTEXT:W·665\nNEWLINE:Y1_STEP-\nNEWLINE:P14:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35422,7 +35425,7 @@
         <v>W·666</v>
       </c>
       <c r="B247" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C247" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·666\nNEWLINE:Y1_STEP+\nNEWLINE:→ P19:2\nTEXT: \nTEXT:W·666\nNEWLINE:Y1_STEP+\nNEWLINE:P14:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35439,7 +35442,7 @@
         <v>W·667</v>
       </c>
       <c r="B248" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C248" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·667\nNEWLINE:Y1_DIR-\nNEWLINE:→ P19:3\nTEXT: \nTEXT:W·667\nNEWLINE:Y1_DIR-\nNEWLINE:P14:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35456,7 +35459,7 @@
         <v>W·668</v>
       </c>
       <c r="B249" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C249" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·668\nNEWLINE:Y1_DIR+\nNEWLINE:→ P19:4\nTEXT: \nTEXT:W·668\nNEWLINE:Y1_DIR+\nNEWLINE:P14:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35473,7 +35476,7 @@
         <v>W·669</v>
       </c>
       <c r="B250" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C250" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·669\nNEWLINE:Y2_STEP-\nNEWLINE:→ P19:5\nTEXT: \nTEXT:W·669\nNEWLINE:Y2_STEP-\nNEWLINE:P14:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35490,7 +35493,7 @@
         <v>W·670</v>
       </c>
       <c r="B251" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C251" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·670\nNEWLINE:Y2_STEP+\nNEWLINE:→ P19:6\nTEXT: \nTEXT:W·670\nNEWLINE:Y2_STEP+\nNEWLINE:P14:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35507,7 +35510,7 @@
         <v>W·671</v>
       </c>
       <c r="B252" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C252" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·671\nNEWLINE:Y2_DIR-\nNEWLINE:→ P19:7\nTEXT: \nTEXT:W·671\nNEWLINE:Y2_DIR-\nNEWLINE:P14:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35524,7 +35527,7 @@
         <v>W·672</v>
       </c>
       <c r="B253" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C253" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·672\nNEWLINE:Y2_DIR+\nNEWLINE:→ P19:8\nTEXT: \nTEXT:W·672\nNEWLINE:Y2_DIR+\nNEWLINE:P14:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35541,7 +35544,7 @@
         <v>W·673</v>
       </c>
       <c r="B254" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C254" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·673\nNEWLINE:X_STEP-\nNEWLINE:→ P19:9\nTEXT: \nTEXT:W·673\nNEWLINE:X_STEP-\nNEWLINE:P14:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35558,7 +35561,7 @@
         <v>W·674</v>
       </c>
       <c r="B255" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C255" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·674\nNEWLINE:X_STEP+\nNEWLINE:→ P19:10\nTEXT: \nTEXT:W·674\nNEWLINE:X_STEP+\nNEWLINE:P14:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35575,7 +35578,7 @@
         <v>W·675</v>
       </c>
       <c r="B256" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C256" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·675\nNEWLINE:X_DIR-\nNEWLINE:→ P19:11\nTEXT: \nTEXT:W·675\nNEWLINE:X_DIR-\nNEWLINE:P14:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35592,7 +35595,7 @@
         <v>W·676</v>
       </c>
       <c r="B257" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C257" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·676\nNEWLINE:X_DIR+\nNEWLINE:→ P19:12\nTEXT: \nTEXT:W·676\nNEWLINE:X_DIR+\nNEWLINE:P14:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35609,7 +35612,7 @@
         <v>W·677</v>
       </c>
       <c r="B258" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C258" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·677\nNEWLINE:Y1_STEP-\nNEWLINE:→ IM1:PUL-\nTEXT: \nTEXT:W·677\nNEWLINE:Y1_STEP-\nNEWLINE:J19:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35626,7 +35629,7 @@
         <v>W·678</v>
       </c>
       <c r="B259" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C259" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·678\nNEWLINE:Y1_STEP+\nNEWLINE:→ IM1:PUL+\nTEXT: \nTEXT:W·678\nNEWLINE:Y1_STEP+\nNEWLINE:J19:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35643,7 +35646,7 @@
         <v>W·679</v>
       </c>
       <c r="B260" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C260" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·679\nNEWLINE:Y1_DIR-\nNEWLINE:→ IM1:DIR-\nTEXT: \nTEXT:W·679\nNEWLINE:Y1_DIR-\nNEWLINE:J19:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35660,7 +35663,7 @@
         <v>W·680</v>
       </c>
       <c r="B261" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C261" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·680\nNEWLINE:Y1_DIR+\nNEWLINE:→ IM1:DIR+\nTEXT: \nTEXT:W·680\nNEWLINE:Y1_DIR+\nNEWLINE:J19:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35677,7 +35680,7 @@
         <v>W·681</v>
       </c>
       <c r="B262" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C262" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·681\nNEWLINE:Y2_STEP-\nNEWLINE:→ IM2:PUL-\nTEXT: \nTEXT:W·681\nNEWLINE:Y2_STEP-\nNEWLINE:J19:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35694,7 +35697,7 @@
         <v>W·682</v>
       </c>
       <c r="B263" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C263" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·682\nNEWLINE:Y2_STEP+\nNEWLINE:→ IM2:PUL+\nTEXT: \nTEXT:W·682\nNEWLINE:Y2_STEP+\nNEWLINE:J19:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35711,7 +35714,7 @@
         <v>W·683</v>
       </c>
       <c r="B264" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C264" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·683\nNEWLINE:Y2_DIR-\nNEWLINE:→ IM2:DIR-\nTEXT: \nTEXT:W·683\nNEWLINE:Y2_DIR-\nNEWLINE:J19:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35728,7 +35731,7 @@
         <v>W·684</v>
       </c>
       <c r="B265" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C265" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·684\nNEWLINE:Y2_DIR+\nNEWLINE:→ IM2:DIR+\nTEXT: \nTEXT:W·684\nNEWLINE:Y2_DIR+\nNEWLINE:J19:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35745,7 +35748,7 @@
         <v>W·685</v>
       </c>
       <c r="B266" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C266" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·685\nNEWLINE:X_STEP-\nNEWLINE:→ J24:1\nTEXT: \nTEXT:W·685\nNEWLINE:X_STEP-\nNEWLINE:J19:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35762,7 +35765,7 @@
         <v>W·686</v>
       </c>
       <c r="B267" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C267" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·686\nNEWLINE:X_STEP+\nNEWLINE:→ J24:2\nTEXT: \nTEXT:W·686\nNEWLINE:X_STEP+\nNEWLINE:J19:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35779,7 +35782,7 @@
         <v>W·687</v>
       </c>
       <c r="B268" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C268" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·687\nNEWLINE:X_DIR-\nNEWLINE:→ J24:3\nTEXT: \nTEXT:W·687\nNEWLINE:X_DIR-\nNEWLINE:J19:11→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35796,7 +35799,7 @@
         <v>W·688</v>
       </c>
       <c r="B269" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C269" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·688\nNEWLINE:X_DIR+\nNEWLINE:→ J24:4\nTEXT: \nTEXT:W·688\nNEWLINE:X_DIR+\nNEWLINE:J19:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35813,7 +35816,7 @@
         <v>W·689</v>
       </c>
       <c r="B270" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C270" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·689\nNEWLINE:X_STEP-\nNEWLINE:→ P28:1\nTEXT: \nTEXT:W·689\nNEWLINE:X_STEP-\nNEWLINE:P24:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35830,7 +35833,7 @@
         <v>W·690</v>
       </c>
       <c r="B271" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C271" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·690\nNEWLINE:X_STEP+\nNEWLINE:→ P28:2\nTEXT: \nTEXT:W·690\nNEWLINE:X_STEP+\nNEWLINE:P24:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35847,7 +35850,7 @@
         <v>W·691</v>
       </c>
       <c r="B272" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C272" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·691\nNEWLINE:X_DIR-\nNEWLINE:→ P28:3\nTEXT: \nTEXT:W·691\nNEWLINE:X_DIR-\nNEWLINE:P24:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35864,7 +35867,7 @@
         <v>W·692</v>
       </c>
       <c r="B273" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C273" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·692\nNEWLINE:X_DIR+\nNEWLINE:→ P28:4\nTEXT: \nTEXT:W·692\nNEWLINE:X_DIR+\nNEWLINE:P24:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35881,7 +35884,7 @@
         <v>W·693</v>
       </c>
       <c r="B274" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C274" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·693\nNEWLINE:X_STEP-\nNEWLINE:→ IM3:PUL-\nTEXT: \nTEXT:W·693\nNEWLINE:X_STEP-\nNEWLINE:J28:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35898,7 +35901,7 @@
         <v>W·694</v>
       </c>
       <c r="B275" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C275" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·694\nNEWLINE:X_STEP+\nNEWLINE:→ IM3:PUL+\nTEXT: \nTEXT:W·694\nNEWLINE:X_STEP+\nNEWLINE:J28:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35915,7 +35918,7 @@
         <v>W·695</v>
       </c>
       <c r="B276" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C276" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·695\nNEWLINE:X_DIR-\nNEWLINE:→ IM3:DIR-\nTEXT: \nTEXT:W·695\nNEWLINE:X_DIR-\nNEWLINE:J28:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35932,7 +35935,7 @@
         <v>W·696</v>
       </c>
       <c r="B277" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C277" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·696\nNEWLINE:X_DIR+\nNEWLINE:→ IM3:DIR+\nTEXT: \nTEXT:W·696\nNEWLINE:X_DIR+\nNEWLINE:J28:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35949,7 +35952,7 @@
         <v>W·701</v>
       </c>
       <c r="B278" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C278" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·701\nNEWLINE:Y_MIN\nNEWLINE:→ P9:13\nTEXT: \nTEXT:W·701\nNEWLINE:Y_MIN\nNEWLINE:P1:13→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35966,7 +35969,7 @@
         <v>W·702</v>
       </c>
       <c r="B279" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C279" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·702\nNEWLINE:Y_MAX\nNEWLINE:→ P9:14\nTEXT: \nTEXT:W·702\nNEWLINE:Y_MAX\nNEWLINE:P1:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -35983,7 +35986,7 @@
         <v>W·703</v>
       </c>
       <c r="B280" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C280" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·703\nNEWLINE:Y1_HOME\nNEWLINE:→ P9:15\nTEXT: \nTEXT:W·703\nNEWLINE:Y1_HOME\nNEWLINE:P1:15→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36000,7 +36003,7 @@
         <v>W·704</v>
       </c>
       <c r="B281" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C281" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·704\nNEWLINE:Y2_HOME\nNEWLINE:→ P9:16\nTEXT: \nTEXT:W·704\nNEWLINE:Y2_HOME\nNEWLINE:P1:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36017,7 +36020,7 @@
         <v>W·705</v>
       </c>
       <c r="B282" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C282" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·705\nNEWLINE:X_MIN\nNEWLINE:→ P9:17\nTEXT: \nTEXT:W·705\nNEWLINE:X_MIN\nNEWLINE:P1:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36034,7 +36037,7 @@
         <v>W·706</v>
       </c>
       <c r="B283" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C283" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·706\nNEWLINE:X_MAX\nNEWLINE:→ P9:18\nTEXT: \nTEXT:W·706\nNEWLINE:X_MAX\nNEWLINE:P1:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36051,7 +36054,7 @@
         <v>W·707</v>
       </c>
       <c r="B284" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C284" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·707\nNEWLINE:X_HOME\nNEWLINE:→ P9:19\nTEXT: \nTEXT:W·707\nNEWLINE:X_HOME\nNEWLINE:P1:19→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36068,7 +36071,7 @@
         <v>W·708</v>
       </c>
       <c r="B285" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C285" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·708\nNEWLINE:Z_MIN\nNEWLINE:→ P9:20\nTEXT: \nTEXT:W·708\nNEWLINE:Z_MIN\nNEWLINE:P1:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36085,7 +36088,7 @@
         <v>W·709</v>
       </c>
       <c r="B286" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C286" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·709\nNEWLINE:Z_MAX\nNEWLINE:→ P9:21\nTEXT: \nTEXT:W·709\nNEWLINE:Z_MAX\nNEWLINE:P1:21→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36102,7 +36105,7 @@
         <v>W·710</v>
       </c>
       <c r="B287" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C287" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·710\nNEWLINE:Z_HOME\nNEWLINE:→ P9:22\nTEXT: \nTEXT:W·710\nNEWLINE:Z_HOME\nNEWLINE:P1:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36119,7 +36122,7 @@
         <v>W·711</v>
       </c>
       <c r="B288" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C288" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·711\nNEWLINE:PROBE_IN\nNEWLINE:→ P9:23\nTEXT: \nTEXT:W·711\nNEWLINE:PROBE_IN\nNEWLINE:P1:23→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36136,7 +36139,7 @@
         <v>W·712</v>
       </c>
       <c r="B289" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C289" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·712\nNEWLINE:Y_MIN\nNEWLINE:→ LS1\nTEXT: \nTEXT:W·712\nNEWLINE:Y_MIN\nNEWLINE:J9:13→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36153,7 +36156,7 @@
         <v>W·713</v>
       </c>
       <c r="B290" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C290" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·713\nNEWLINE:Y_MAX\nNEWLINE:→ LS2\nTEXT: \nTEXT:W·713\nNEWLINE:Y_MAX\nNEWLINE:J9:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36170,7 +36173,7 @@
         <v>W·714</v>
       </c>
       <c r="B291" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C291" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·714\nNEWLINE:Y1_HOME\nNEWLINE:→ HS1\nTEXT: \nTEXT:W·714\nNEWLINE:Y1_HOME\nNEWLINE:J9:15→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36187,7 +36190,7 @@
         <v>W·715</v>
       </c>
       <c r="B292" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C292" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·715\nNEWLINE:Y2_HOME\nNEWLINE:→ HS2\nTEXT: \nTEXT:W·715\nNEWLINE:Y2_HOME\nNEWLINE:J9:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36204,7 +36207,7 @@
         <v>W·716</v>
       </c>
       <c r="B293" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C293" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·716\nNEWLINE:X_MIN\nNEWLINE:→ J14:17\nTEXT: \nTEXT:W·716\nNEWLINE:X_MIN\nNEWLINE:J9:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36221,7 +36224,7 @@
         <v>W·717</v>
       </c>
       <c r="B294" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C294" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·717\nNEWLINE:X_MAX\nNEWLINE:→ J14:18\nTEXT: \nTEXT:W·717\nNEWLINE:X_MAX\nNEWLINE:J9:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36238,7 +36241,7 @@
         <v>W·718</v>
       </c>
       <c r="B295" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C295" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·718\nNEWLINE:X_HOME\nNEWLINE:→ J14:19\nTEXT: \nTEXT:W·718\nNEWLINE:X_HOME\nNEWLINE:J9:19→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36255,7 +36258,7 @@
         <v>W·719</v>
       </c>
       <c r="B296" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C296" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·719\nNEWLINE:Z_MIN\nNEWLINE:→ J14:20\nTEXT: \nTEXT:W·719\nNEWLINE:Z_MIN\nNEWLINE:J9:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36272,7 +36275,7 @@
         <v>W·720</v>
       </c>
       <c r="B297" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C297" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·720\nNEWLINE:Z_MAX\nNEWLINE:→ J14:21\nTEXT: \nTEXT:W·720\nNEWLINE:Z_MAX\nNEWLINE:J9:21→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36289,7 +36292,7 @@
         <v>W·721</v>
       </c>
       <c r="B298" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C298" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·721\nNEWLINE:Z_HOME\nNEWLINE:→ J14:22\nTEXT: \nTEXT:W·721\nNEWLINE:Z_HOME\nNEWLINE:J9:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36306,7 +36309,7 @@
         <v>W·722</v>
       </c>
       <c r="B299" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C299" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·722\nNEWLINE:PROBE_IN\nNEWLINE:→ TP1\nTEXT: \nTEXT:W·722\nNEWLINE:PROBE_IN\nNEWLINE:J9:23→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36323,7 +36326,7 @@
         <v>W·723</v>
       </c>
       <c r="B300" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C300" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·723\nNEWLINE:X_MIN\nNEWLINE:→ P19:17\nTEXT: \nTEXT:W·723\nNEWLINE:X_MIN\nNEWLINE:P14:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36340,7 +36343,7 @@
         <v>W·724</v>
       </c>
       <c r="B301" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C301" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·724\nNEWLINE:X_MAX\nNEWLINE:→ P19:18\nTEXT: \nTEXT:W·724\nNEWLINE:X_MAX\nNEWLINE:P14:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36357,7 +36360,7 @@
         <v>W·725</v>
       </c>
       <c r="B302" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C302" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·725\nNEWLINE:X_HOME\nNEWLINE:→ P19:19\nTEXT: \nTEXT:W·725\nNEWLINE:X_HOME\nNEWLINE:P14:19→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36374,7 +36377,7 @@
         <v>W·726</v>
       </c>
       <c r="B303" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C303" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·726\nNEWLINE:Z_MIN\nNEWLINE:→ P19:20\nTEXT: \nTEXT:W·726\nNEWLINE:Z_MIN\nNEWLINE:P14:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36391,7 +36394,7 @@
         <v>W·727</v>
       </c>
       <c r="B304" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C304" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·727\nNEWLINE:Z_MAX\nNEWLINE:→ P19:21\nTEXT: \nTEXT:W·727\nNEWLINE:Z_MAX\nNEWLINE:P14:21→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36408,7 +36411,7 @@
         <v>W·728</v>
       </c>
       <c r="B305" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C305" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·728\nNEWLINE:Z_HOME\nNEWLINE:→ P19:22\nTEXT: \nTEXT:W·728\nNEWLINE:Z_HOME\nNEWLINE:P14:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36425,7 +36428,7 @@
         <v>W·729</v>
       </c>
       <c r="B306" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C306" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·729\nNEWLINE:X_MIN\nNEWLINE:→ LS3\nTEXT: \nTEXT:W·729\nNEWLINE:X_MIN\nNEWLINE:J19:17→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36442,7 +36445,7 @@
         <v>W·730</v>
       </c>
       <c r="B307" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C307" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·730\nNEWLINE:X_MAX\nNEWLINE:→ LS4\nTEXT: \nTEXT:W·730\nNEWLINE:X_MAX\nNEWLINE:J19:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36459,7 +36462,7 @@
         <v>W·731</v>
       </c>
       <c r="B308" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C308" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·731\nNEWLINE:X_HOME\nNEWLINE:→ HS3\nTEXT: \nTEXT:W·731\nNEWLINE:X_HOME\nNEWLINE:J19:19→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36476,7 +36479,7 @@
         <v>W·732</v>
       </c>
       <c r="B309" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C309" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·732\nNEWLINE:Z_MIN\nNEWLINE:→ J24:5\nTEXT: \nTEXT:W·732\nNEWLINE:Z_MIN\nNEWLINE:J19:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36493,7 +36496,7 @@
         <v>W·733</v>
       </c>
       <c r="B310" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C310" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·733\nNEWLINE:Z_MAX\nNEWLINE:→ J24:6\nTEXT: \nTEXT:W·733\nNEWLINE:Z_MAX\nNEWLINE:J19:21→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36510,7 +36513,7 @@
         <v>W·734</v>
       </c>
       <c r="B311" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C311" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·734\nNEWLINE:Z_HOME\nNEWLINE:→ J24:7\nTEXT: \nTEXT:W·734\nNEWLINE:Z_HOME\nNEWLINE:J19:22→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36527,7 +36530,7 @@
         <v>W·735</v>
       </c>
       <c r="B312" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C312" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·735\nNEWLINE:Z_MIN\nNEWLINE:→ P28:5\nTEXT: \nTEXT:W·735\nNEWLINE:Z_MIN\nNEWLINE:P24:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36544,7 +36547,7 @@
         <v>W·736</v>
       </c>
       <c r="B313" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C313" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·736\nNEWLINE:Z_MAX\nNEWLINE:→ P28:6\nTEXT: \nTEXT:W·736\nNEWLINE:Z_MAX\nNEWLINE:P24:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36561,7 +36564,7 @@
         <v>W·737</v>
       </c>
       <c r="B314" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C314" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·737\nNEWLINE:Z_HOME\nNEWLINE:→ P28:7\nTEXT: \nTEXT:W·737\nNEWLINE:Z_HOME\nNEWLINE:P24:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36578,7 +36581,7 @@
         <v>W·738</v>
       </c>
       <c r="B315" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C315" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·738\nNEWLINE:Z_MIN\nNEWLINE:→ LS5:5\nTEXT: \nTEXT:W·738\nNEWLINE:Z_MIN\nNEWLINE:J28:5→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36595,7 +36598,7 @@
         <v>W·739</v>
       </c>
       <c r="B316" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C316" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·739\nNEWLINE:Z_MAX\nNEWLINE:→ LS6:6\nTEXT: \nTEXT:W·739\nNEWLINE:Z_MAX\nNEWLINE:J28:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36612,7 +36615,7 @@
         <v>W·740</v>
       </c>
       <c r="B317" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C317" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·740\nNEWLINE:Z_HOME\nNEWLINE:→ HS4:7\nTEXT: \nTEXT:W·740\nNEWLINE:Z_HOME\nNEWLINE:J28:7→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36629,7 +36632,7 @@
         <v>W·901</v>
       </c>
       <c r="B318" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C318" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·901\nNEWLINE:PE\nNEWLINE:→ TB1:1\nTEXT: \nTEXT:W·901\nNEWLINE:PE\nNEWLINE:P0:PE→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36646,7 +36649,7 @@
         <v>W·902</v>
       </c>
       <c r="B319" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C319" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·902\nNEWLINE:PE\nNEWLINE:→ TB4:1\nTEXT: \nTEXT:W·902\nNEWLINE:PE\nNEWLINE:TB1:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36663,7 +36666,7 @@
         <v>W·911</v>
       </c>
       <c r="B320" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C320" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·911\nNEWLINE:PE\nNEWLINE:→ F1:PE\nTEXT: \nTEXT:W·911\nNEWLINE:PE\nNEWLINE:TB4:3→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36680,7 +36683,7 @@
         <v>W·912</v>
       </c>
       <c r="B321" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C321" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·912\nNEWLINE:PE\nNEWLINE:→ PS5:GND\nTEXT: \nTEXT:W·912\nNEWLINE:PE\nNEWLINE:TB4:18→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36697,7 +36700,7 @@
         <v>W·913</v>
       </c>
       <c r="B322" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C322" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·913\nNEWLINE:PE\nNEWLINE:→ PS6:GND\nTEXT: \nTEXT:W·913\nNEWLINE:PE\nNEWLINE:TB4:16→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36714,7 +36717,7 @@
         <v>W·914</v>
       </c>
       <c r="B323" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C323" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·914\nNEWLINE:PE\nNEWLINE:→ PS4:GND\nTEXT: \nTEXT:W·914\nNEWLINE:PE\nNEWLINE:TB4:14→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36731,7 +36734,7 @@
         <v>W·915</v>
       </c>
       <c r="B324" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C324" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·915\nNEWLINE:PE\nNEWLINE:→ J6:2\nTEXT: \nTEXT:W·915\nNEWLINE:PE\nNEWLINE:TB4:12→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36748,7 +36751,7 @@
         <v>W·916</v>
       </c>
       <c r="B325" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C325" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·916\nNEWLINE:PE\nNEWLINE:→ J6:1\nTEXT: \nTEXT:W·916\nNEWLINE:PE\nNEWLINE:TB4:10→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36765,7 +36768,7 @@
         <v>W·917</v>
       </c>
       <c r="B326" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C326" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·917\nNEWLINE:PE\nNEWLINE:→ J1:GND\nTEXT: \nTEXT:W·917\nNEWLINE:PE\nNEWLINE:TB4:8→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36782,7 +36785,7 @@
         <v>W·918</v>
       </c>
       <c r="B327" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C327" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·918\nNEWLINE:PE\nNEWLINE:→ P40:PE\nTEXT: \nTEXT:W·918\nNEWLINE:PE\nNEWLINE:TB4:6→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36799,7 +36802,7 @@
         <v>W·919</v>
       </c>
       <c r="B328" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C328" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·919\nNEWLINE:PE\nNEWLINE:→ J35:PE\nTEXT: \nTEXT:W·919\nNEWLINE:PE\nNEWLINE:TB4:4→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36816,7 +36819,7 @@
         <v>W·920</v>
       </c>
       <c r="B329" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C329" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·920\nNEWLINE:PE\nNEWLINE:→ MESA:FRAME:FR1\nTEXT: \nTEXT:W·920\nNEWLINE:PE\nNEWLINE:TB4:20→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36833,7 +36836,7 @@
         <v>W·951</v>
       </c>
       <c r="B330" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C330" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·951\nNEWLINE:PE\nNEWLINE:→ VFD1:GND\nTEXT: \nTEXT:W·951\nNEWLINE:PE\nNEWLINE:P6:2→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36850,7 +36853,7 @@
         <v>W·952</v>
       </c>
       <c r="B331" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C331" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·952\nNEWLINE:PE\nNEWLINE:→ M1:4\nTEXT: \nTEXT:W·952\nNEWLINE:PE\nNEWLINE:P6:1→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36867,7 +36870,7 @@
         <v>W·953</v>
       </c>
       <c r="B332" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C332" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·953\nNEWLINE:PE\nNEWLINE:→ P9:GND\nTEXT: \nTEXT:W·953\nNEWLINE:PE\nNEWLINE:P1:GND→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36884,7 +36887,7 @@
         <v>W·954</v>
       </c>
       <c r="B333" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C333" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·954\nNEWLINE:PE\nNEWLINE:→ J14:GND\nTEXT: \nTEXT:W·954\nNEWLINE:PE\nNEWLINE:J9:GND→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36901,7 +36904,7 @@
         <v>W·955</v>
       </c>
       <c r="B334" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C334" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·955\nNEWLINE:PE\nNEWLINE:→ P19:GND\nTEXT: \nTEXT:W·955\nNEWLINE:PE\nNEWLINE:P14:GND→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36918,7 +36921,7 @@
         <v>W·956</v>
       </c>
       <c r="B335" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C335" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·956\nNEWLINE:PE\nNEWLINE:→ J24:9\nTEXT: \nTEXT:W·956\nNEWLINE:PE\nNEWLINE:J19:GND→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36935,7 +36938,7 @@
         <v>W·957</v>
       </c>
       <c r="B336" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C336" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·957\nNEWLINE:PE\nNEWLINE:→ P28:9\nTEXT: \nTEXT:W·957\nNEWLINE:PE\nNEWLINE:P24:9→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
@@ -36952,7 +36955,7 @@
         <v>W·961</v>
       </c>
       <c r="B337" t="s" s="46">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C337" t="str" s="47">
         <v>printf '%b' "LABELLE-LABEL-SPEC-VERSION:1\nTEXT:W·961\nNEWLINE:PE\nNEWLINE:→ J36:PE\nTEXT: \nTEXT:W·961\nNEWLINE:PE\nNEWLINE:P35:PE→\n" | $HOME/.local/bin/labelle --output printer --style bold --batch</v>
